--- a/artfynd/A 55408-2024 artfynd.xlsx
+++ b/artfynd/A 55408-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122822850</v>
+        <v>122822680</v>
       </c>
       <c r="B2" t="n">
-        <v>5489</v>
+        <v>78499</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101410</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528902</v>
+        <v>528888</v>
       </c>
       <c r="R2" t="n">
-        <v>6998601</v>
+        <v>6998655</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,9 +748,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På kolad ved på tallhögstubbe</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122822680</v>
+        <v>122823006</v>
       </c>
       <c r="B3" t="n">
-        <v>78499</v>
+        <v>79843</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,37 +808,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528888</v>
+        <v>528861</v>
       </c>
       <c r="R3" t="n">
-        <v>6998655</v>
+        <v>6998604</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,26 +870,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På kolad ved på tallhögstubbe</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -878,26 +883,51 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122823006</v>
+        <v>122820739</v>
       </c>
       <c r="B4" t="n">
-        <v>79843</v>
+        <v>77699</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,42 +940,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528861</v>
+        <v>528795</v>
       </c>
       <c r="R4" t="n">
-        <v>6998604</v>
+        <v>6998791</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,11 +997,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -985,51 +1025,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122820739</v>
+        <v>122822781</v>
       </c>
       <c r="B5" t="n">
-        <v>77699</v>
+        <v>79879</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,25 +1053,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228579</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528795</v>
+        <v>528877</v>
       </c>
       <c r="R5" t="n">
-        <v>6998791</v>
+        <v>6998634</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,12 +1126,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,10 +1158,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122822781</v>
+        <v>122819522</v>
       </c>
       <c r="B6" t="n">
-        <v>79879</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,38 +1170,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528877</v>
+        <v>528843</v>
       </c>
       <c r="R6" t="n">
-        <v>6998634</v>
+        <v>6998616</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,24 +1236,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,19 +1258,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122819522</v>
+        <v>122819030</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1305,10 +1315,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528843</v>
+        <v>528811</v>
       </c>
       <c r="R7" t="n">
-        <v>6998616</v>
+        <v>6998709</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1372,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122819030</v>
+        <v>122822818</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>79843</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,27 +1398,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1417,10 +1427,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528811</v>
+        <v>528919</v>
       </c>
       <c r="R8" t="n">
-        <v>6998709</v>
+        <v>6998644</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,7 +1467,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På två gamla grovbarkade sälgar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,6 +1478,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1484,10 +1519,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122822818</v>
+        <v>122819677</v>
       </c>
       <c r="B9" t="n">
-        <v>79843</v>
+        <v>79844</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1500,39 +1535,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528919</v>
+        <v>528904</v>
       </c>
       <c r="R9" t="n">
-        <v>6998644</v>
+        <v>6998685</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1567,11 +1597,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På två gamla grovbarkade sälgar.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1580,31 +1605,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1621,10 +1621,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122819677</v>
+        <v>122819608</v>
       </c>
       <c r="B10" t="n">
-        <v>79844</v>
+        <v>78762</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1637,37 +1637,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528904</v>
+        <v>528807</v>
       </c>
       <c r="R10" t="n">
-        <v>6998685</v>
+        <v>6998706</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1699,6 +1704,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Relativt ymnigt på många granar. Fertila bålar finns här.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1707,6 +1717,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1723,10 +1758,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122819608</v>
+        <v>122820150</v>
       </c>
       <c r="B11" t="n">
-        <v>78762</v>
+        <v>79018</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1735,46 +1770,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6459</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528807</v>
+        <v>528898</v>
       </c>
       <c r="R11" t="n">
-        <v>6998706</v>
+        <v>6998770</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1801,14 +1831,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Relativt ymnigt på många granar. Fertila bålar finns här.</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1819,51 +1859,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122820024</v>
+        <v>122819182</v>
       </c>
       <c r="B12" t="n">
-        <v>57589</v>
+        <v>90936</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1872,47 +1887,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103031</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528891</v>
+        <v>528836</v>
       </c>
       <c r="R12" t="n">
-        <v>6998690</v>
+        <v>6998668</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1971,10 +1977,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122820150</v>
+        <v>122819697</v>
       </c>
       <c r="B13" t="n">
-        <v>79018</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1983,41 +1989,46 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6459</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528898</v>
+        <v>528891</v>
       </c>
       <c r="R13" t="n">
-        <v>6998770</v>
+        <v>6998754</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2046,7 +2057,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2056,12 +2067,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>Äldre ringhack på gammal levande tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2088,10 +2099,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122819182</v>
+        <v>122821939</v>
       </c>
       <c r="B14" t="n">
-        <v>90936</v>
+        <v>78762</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2104,37 +2115,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528836</v>
+        <v>528796</v>
       </c>
       <c r="R14" t="n">
-        <v>6998668</v>
+        <v>6998791</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2161,9 +2181,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2178,22 +2208,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122819697</v>
+        <v>122822259</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>78762</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2206,27 +2236,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2235,13 +2265,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528891</v>
+        <v>528831</v>
       </c>
       <c r="R15" t="n">
-        <v>6998754</v>
+        <v>6998741</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2270,7 +2300,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2280,12 +2310,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gammal levande tall</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2300,22 +2330,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122821939</v>
+        <v>122822120</v>
       </c>
       <c r="B16" t="n">
-        <v>78762</v>
+        <v>79843</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2328,46 +2358,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528796</v>
+        <v>528832</v>
       </c>
       <c r="R16" t="n">
-        <v>6998791</v>
+        <v>6998742</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2394,19 +2415,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>12:42</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2421,22 +2432,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122822259</v>
+        <v>122819081</v>
       </c>
       <c r="B17" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2449,42 +2460,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528831</v>
+        <v>528837</v>
       </c>
       <c r="R17" t="n">
-        <v>6998741</v>
+        <v>6998667</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2511,24 +2522,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2543,22 +2544,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122822120</v>
+        <v>122820176</v>
       </c>
       <c r="B18" t="n">
-        <v>79843</v>
+        <v>57631</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2571,34 +2572,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528832</v>
+        <v>528888</v>
       </c>
       <c r="R18" t="n">
-        <v>6998742</v>
+        <v>6998720</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2657,10 +2658,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122819081</v>
+        <v>122822761</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
+        <v>79843</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2673,39 +2674,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528837</v>
+        <v>528879</v>
       </c>
       <c r="R19" t="n">
-        <v>6998667</v>
+        <v>6998619</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2735,14 +2731,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2757,22 +2763,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122820539</v>
+        <v>122822436</v>
       </c>
       <c r="B20" t="n">
-        <v>90940</v>
+        <v>78499</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2785,42 +2791,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528851</v>
+        <v>528840</v>
       </c>
       <c r="R20" t="n">
-        <v>6998721</v>
+        <v>6998787</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2847,11 +2848,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På kolad ved på tallstubbe</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2860,51 +2876,26 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122820176</v>
+        <v>122820232</v>
       </c>
       <c r="B21" t="n">
-        <v>57631</v>
+        <v>77709</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2917,34 +2908,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528888</v>
+        <v>528897</v>
       </c>
       <c r="R21" t="n">
-        <v>6998720</v>
+        <v>6998766</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2974,9 +2965,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2991,22 +2997,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122819947</v>
+        <v>122819987</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
+        <v>79878</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3015,57 +3021,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528893</v>
+        <v>528883</v>
       </c>
       <c r="R22" t="n">
-        <v>6998687</v>
+        <v>6998770</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3095,9 +3082,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3112,22 +3114,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122822761</v>
+        <v>122819701</v>
       </c>
       <c r="B23" t="n">
-        <v>79843</v>
+        <v>78762</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3140,37 +3142,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528879</v>
+        <v>528843</v>
       </c>
       <c r="R23" t="n">
-        <v>6998619</v>
+        <v>6998744</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3197,24 +3199,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På sälglåga</t>
+          <t>Rikligt på många granar.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3225,26 +3217,51 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122822436</v>
+        <v>122819010</v>
       </c>
       <c r="B24" t="n">
-        <v>78499</v>
+        <v>57478</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3257,37 +3274,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528840</v>
+        <v>528818</v>
       </c>
       <c r="R24" t="n">
-        <v>6998787</v>
+        <v>6998712</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3314,24 +3336,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På kolad ved på tallstubbe</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3346,22 +3358,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122820232</v>
+        <v>122822075</v>
       </c>
       <c r="B25" t="n">
-        <v>77709</v>
+        <v>74675</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3370,38 +3382,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>314</v>
+        <v>6428</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528897</v>
+        <v>528829</v>
       </c>
       <c r="R25" t="n">
-        <v>6998766</v>
+        <v>6998747</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3431,24 +3443,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3463,22 +3460,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122819987</v>
+        <v>122822228</v>
       </c>
       <c r="B26" t="n">
-        <v>79878</v>
+        <v>57631</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3487,38 +3484,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6463</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528883</v>
+        <v>528846</v>
       </c>
       <c r="R26" t="n">
-        <v>6998770</v>
+        <v>6998743</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3548,24 +3554,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3580,22 +3571,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122819701</v>
+        <v>122819626</v>
       </c>
       <c r="B27" t="n">
-        <v>78762</v>
+        <v>79843</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3608,21 +3599,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3632,13 +3623,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528843</v>
+        <v>528907</v>
       </c>
       <c r="R27" t="n">
-        <v>6998744</v>
+        <v>6998684</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3672,7 +3663,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Rikligt på många granar.</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3683,31 +3674,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3724,10 +3690,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122819010</v>
+        <v>122819526</v>
       </c>
       <c r="B28" t="n">
-        <v>57478</v>
+        <v>90940</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3740,39 +3706,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528818</v>
+        <v>528875</v>
       </c>
       <c r="R28" t="n">
-        <v>6998712</v>
+        <v>6998691</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3802,14 +3763,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3824,22 +3795,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122822228</v>
+        <v>122819870</v>
       </c>
       <c r="B29" t="n">
-        <v>57631</v>
+        <v>79843</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3852,46 +3823,46 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528846</v>
+        <v>528902</v>
       </c>
       <c r="R29" t="n">
-        <v>6998743</v>
+        <v>6998729</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3918,9 +3889,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På björklåga</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3935,22 +3921,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122822075</v>
+        <v>122819919</v>
       </c>
       <c r="B30" t="n">
-        <v>74675</v>
+        <v>74854</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3959,38 +3945,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6428</v>
+        <v>492</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528829</v>
+        <v>528873</v>
       </c>
       <c r="R30" t="n">
-        <v>6998747</v>
+        <v>6998728</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4020,9 +4006,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På bark i hålighet vid basen av gammal björkhögstubbe</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4037,22 +4038,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122819626</v>
+        <v>122820365</v>
       </c>
       <c r="B31" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4065,37 +4066,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528907</v>
+        <v>528893</v>
       </c>
       <c r="R31" t="n">
-        <v>6998684</v>
+        <v>6998757</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4122,14 +4128,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>På gammal tall, äldre ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4144,19 +4160,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122819526</v>
+        <v>122822373</v>
       </c>
       <c r="B32" t="n">
         <v>90940</v>
@@ -4196,13 +4212,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528875</v>
+        <v>528856</v>
       </c>
       <c r="R32" t="n">
-        <v>6998691</v>
+        <v>6998762</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4231,7 +4247,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4241,12 +4257,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4261,22 +4277,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122819870</v>
+        <v>122822354</v>
       </c>
       <c r="B33" t="n">
-        <v>79843</v>
+        <v>91112</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4289,46 +4305,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>1588</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528902</v>
+        <v>528838</v>
       </c>
       <c r="R33" t="n">
-        <v>6998729</v>
+        <v>6998736</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4355,24 +4362,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>11:29</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>11:29</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På björklåga</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4387,22 +4379,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122819919</v>
+        <v>122819041</v>
       </c>
       <c r="B34" t="n">
-        <v>74854</v>
+        <v>57478</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4411,38 +4403,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528873</v>
+        <v>528830</v>
       </c>
       <c r="R34" t="n">
-        <v>6998728</v>
+        <v>6998687</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4472,24 +4469,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På bark i hålighet vid basen av gammal björkhögstubbe</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4504,22 +4491,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122820365</v>
+        <v>122819213</v>
       </c>
       <c r="B35" t="n">
-        <v>57478</v>
+        <v>79843</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4532,42 +4519,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528893</v>
+        <v>528849</v>
       </c>
       <c r="R35" t="n">
-        <v>6998757</v>
+        <v>6998626</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4596,7 +4578,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4606,12 +4588,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På gammal tall, äldre ringhack</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4626,19 +4608,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122820461</v>
+        <v>122819055</v>
       </c>
       <c r="B36" t="n">
         <v>57478</v>
@@ -4674,27 +4656,22 @@
       <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528854</v>
+        <v>528843</v>
       </c>
       <c r="R36" t="n">
-        <v>6998728</v>
+        <v>6998681</v>
       </c>
       <c r="S36" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4728,7 +4705,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska ringhack längs ca 3 m på en granstam i barrnaturskog med revir för tretåig hackspett i höga livsmiljövärden.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4739,31 +4716,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4780,10 +4732,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122822373</v>
+        <v>122820570</v>
       </c>
       <c r="B37" t="n">
-        <v>90940</v>
+        <v>57478</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4796,37 +4748,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528856</v>
+        <v>528842</v>
       </c>
       <c r="R37" t="n">
-        <v>6998762</v>
+        <v>6998786</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4853,24 +4810,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4885,22 +4832,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122819041</v>
+        <v>122819057</v>
       </c>
       <c r="B38" t="n">
-        <v>57478</v>
+        <v>78762</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4913,42 +4860,46 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
         <v>528830</v>
       </c>
       <c r="R38" t="n">
-        <v>6998687</v>
+        <v>6998611</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4975,14 +4926,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt på gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4997,22 +4958,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122822354</v>
+        <v>122820550</v>
       </c>
       <c r="B39" t="n">
-        <v>91112</v>
+        <v>57478</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5025,34 +4986,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1588</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528838</v>
+        <v>528843</v>
       </c>
       <c r="R39" t="n">
-        <v>6998736</v>
+        <v>6998785</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5085,6 +5051,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5111,10 +5082,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122819213</v>
+        <v>122819726</v>
       </c>
       <c r="B40" t="n">
-        <v>79843</v>
+        <v>57589</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5123,38 +5094,47 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>103031</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528849</v>
+        <v>528900</v>
       </c>
       <c r="R40" t="n">
-        <v>6998626</v>
+        <v>6998697</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5184,24 +5164,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>10:57</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>10:57</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5216,22 +5181,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122819055</v>
+        <v>122819597</v>
       </c>
       <c r="B41" t="n">
-        <v>57478</v>
+        <v>82549</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5244,39 +5209,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528843</v>
+        <v>528869</v>
       </c>
       <c r="R41" t="n">
-        <v>6998681</v>
+        <v>6998649</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5306,14 +5266,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5328,22 +5298,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122820570</v>
+        <v>122820115</v>
       </c>
       <c r="B42" t="n">
-        <v>57478</v>
+        <v>74855</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5356,39 +5326,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528842</v>
+        <v>528898</v>
       </c>
       <c r="R42" t="n">
-        <v>6998786</v>
+        <v>6998773</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5418,14 +5383,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På ved på gammal levande sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5440,22 +5415,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122819057</v>
+        <v>122822290</v>
       </c>
       <c r="B43" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5468,46 +5443,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528830</v>
+        <v>528824</v>
       </c>
       <c r="R43" t="n">
-        <v>6998611</v>
+        <v>6998724</v>
       </c>
       <c r="S43" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5534,24 +5505,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>10:51</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>10:51</t>
-        </is>
-      </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Rikligt på gamla granar i gammal granskog</t>
+          <t>Äldre ringhack på en hackspettsbearbetad död gran.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5562,26 +5523,51 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122820550</v>
+        <v>122820141</v>
       </c>
       <c r="B44" t="n">
-        <v>57478</v>
+        <v>90940</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5594,39 +5580,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528843</v>
+        <v>528888</v>
       </c>
       <c r="R44" t="n">
-        <v>6998785</v>
+        <v>6998720</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5659,11 +5640,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5690,10 +5666,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122819726</v>
+        <v>122821953</v>
       </c>
       <c r="B45" t="n">
-        <v>57589</v>
+        <v>57478</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5702,20 +5678,20 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5723,14 +5699,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5739,10 +5711,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528900</v>
+        <v>528813</v>
       </c>
       <c r="R45" t="n">
-        <v>6998697</v>
+        <v>6998760</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5775,6 +5747,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5801,10 +5778,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122819597</v>
+        <v>122822197</v>
       </c>
       <c r="B46" t="n">
-        <v>82549</v>
+        <v>95893</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5817,34 +5794,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1312</v>
+        <v>53</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528869</v>
+        <v>528847</v>
       </c>
       <c r="R46" t="n">
-        <v>6998649</v>
+        <v>6998739</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5874,24 +5851,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5906,22 +5868,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122820115</v>
+        <v>122819825</v>
       </c>
       <c r="B47" t="n">
-        <v>74855</v>
+        <v>74675</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5930,38 +5892,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>308</v>
+        <v>6428</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528898</v>
+        <v>528895</v>
       </c>
       <c r="R47" t="n">
-        <v>6998773</v>
+        <v>6998697</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5991,24 +5953,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På ved på gammal levande sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6023,22 +5970,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122822290</v>
+        <v>122819543</v>
       </c>
       <c r="B48" t="n">
-        <v>57478</v>
+        <v>74849</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6047,46 +5994,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528824</v>
+        <v>528863</v>
       </c>
       <c r="R48" t="n">
-        <v>6998724</v>
+        <v>6998680</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6113,14 +6055,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en hackspettsbearbetad död gran.</t>
+          <t>På ved på björkhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6131,51 +6083,26 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122820141</v>
+        <v>122820558</v>
       </c>
       <c r="B49" t="n">
-        <v>90940</v>
+        <v>74863</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6188,37 +6115,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528888</v>
+        <v>528878</v>
       </c>
       <c r="R49" t="n">
-        <v>6998720</v>
+        <v>6998770</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6245,9 +6172,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6262,22 +6204,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122819825</v>
+        <v>122819960</v>
       </c>
       <c r="B50" t="n">
-        <v>74675</v>
+        <v>57478</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6286,38 +6228,62 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6428</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>528895</v>
+        <v>528893</v>
       </c>
       <c r="R50" t="n">
-        <v>6998697</v>
+        <v>6998687</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6352,6 +6318,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Rätt så skygg hane av tretåig hackspett i barrnaturskog med mycket höga livsmiljövärden för tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6360,6 +6331,16 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskog med höga naturvärden.</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6376,10 +6357,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122819543</v>
+        <v>122820024</v>
       </c>
       <c r="B51" t="n">
-        <v>74849</v>
+        <v>57589</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6392,37 +6373,53 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>306</v>
+        <v>103031</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>528863</v>
+        <v>528891</v>
       </c>
       <c r="R51" t="n">
-        <v>6998680</v>
+        <v>6998690</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6449,24 +6446,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På ved på björkhögstubbe i gammal granskog</t>
+          <t>Tre lavskrikor i naturskog med höga naturvärden.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6477,26 +6464,36 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>Flerskiktad hänglavsrik barrnaturskog med höga naturvärden.</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122820558</v>
+        <v>122822850</v>
       </c>
       <c r="B52" t="n">
-        <v>74863</v>
+        <v>5489</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6509,37 +6506,46 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>101410</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>528878</v>
+        <v>528902</v>
       </c>
       <c r="R52" t="n">
-        <v>6998770</v>
+        <v>6998601</v>
       </c>
       <c r="S52" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6566,54 +6572,50 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Gammal flerskiktad naturskogsartad kontinuitetsskog.</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122822197</v>
+        <v>122820461</v>
       </c>
       <c r="B53" t="n">
-        <v>95893</v>
+        <v>57478</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6626,37 +6628,47 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>528847</v>
+        <v>528854</v>
       </c>
       <c r="R53" t="n">
-        <v>6998739</v>
+        <v>6998728</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6688,6 +6700,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Färska ringhack längs ca 3 m på en granstam i barrnaturskog med revir för tretåig hackspett i höga livsmiljövärden.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6696,6 +6713,31 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6712,10 +6754,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122821953</v>
+        <v>122820539</v>
       </c>
       <c r="B54" t="n">
-        <v>57478</v>
+        <v>90940</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6728,42 +6770,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>528813</v>
+        <v>528851</v>
       </c>
       <c r="R54" t="n">
-        <v>6998760</v>
+        <v>6998721</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6795,11 +6837,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6808,6 +6845,31 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">

--- a/artfynd/A 55408-2024 artfynd.xlsx
+++ b/artfynd/A 55408-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122822680</v>
+        <v>122819677</v>
       </c>
       <c r="B2" t="n">
-        <v>78499</v>
+        <v>79848</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528888</v>
+        <v>528904</v>
       </c>
       <c r="R2" t="n">
-        <v>6998655</v>
+        <v>6998685</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,24 +748,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På kolad ved på tallhögstubbe</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122823006</v>
+        <v>122819919</v>
       </c>
       <c r="B3" t="n">
-        <v>79843</v>
+        <v>74854</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,46 +789,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>492</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528861</v>
+        <v>528873</v>
       </c>
       <c r="R3" t="n">
-        <v>6998604</v>
+        <v>6998728</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,11 +850,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På bark i hålighet vid basen av gammal björkhögstubbe</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -883,51 +878,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122820739</v>
+        <v>122819870</v>
       </c>
       <c r="B4" t="n">
-        <v>77699</v>
+        <v>79847</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,37 +910,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528795</v>
+        <v>528902</v>
       </c>
       <c r="R4" t="n">
-        <v>6998791</v>
+        <v>6998729</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,12 +988,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På björklåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,22 +1008,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122822781</v>
+        <v>122822373</v>
       </c>
       <c r="B5" t="n">
-        <v>79879</v>
+        <v>90944</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,25 +1032,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1081,13 +1060,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528877</v>
+        <v>528856</v>
       </c>
       <c r="R5" t="n">
-        <v>6998634</v>
+        <v>6998762</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1116,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,12 +1105,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122819522</v>
+        <v>122819543</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>74849</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1170,46 +1149,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528843</v>
+        <v>528863</v>
       </c>
       <c r="R6" t="n">
-        <v>6998616</v>
+        <v>6998680</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1236,14 +1210,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På ved på björkhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,22 +1242,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122819030</v>
+        <v>122819825</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>74675</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,43 +1266,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6428</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528811</v>
+        <v>528895</v>
       </c>
       <c r="R7" t="n">
-        <v>6998709</v>
+        <v>6998697</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1351,11 +1330,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,10 +1356,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122822818</v>
+        <v>122820558</v>
       </c>
       <c r="B8" t="n">
-        <v>79843</v>
+        <v>74863</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,42 +1372,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528919</v>
+        <v>528878</v>
       </c>
       <c r="R8" t="n">
-        <v>6998644</v>
+        <v>6998770</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1460,14 +1429,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På två gamla grovbarkade sälgar.</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,51 +1457,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122819677</v>
+        <v>122819726</v>
       </c>
       <c r="B9" t="n">
-        <v>79844</v>
+        <v>57589</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1531,38 +1485,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>103031</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528904</v>
+        <v>528900</v>
       </c>
       <c r="R9" t="n">
-        <v>6998685</v>
+        <v>6998697</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1621,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122819608</v>
+        <v>122819055</v>
       </c>
       <c r="B10" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1637,27 +1600,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1666,13 +1629,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528807</v>
+        <v>528843</v>
       </c>
       <c r="R10" t="n">
-        <v>6998706</v>
+        <v>6998681</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1706,7 +1669,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Relativt ymnigt på många granar. Fertila bålar finns här.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1717,31 +1680,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1758,10 +1696,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122820150</v>
+        <v>122819182</v>
       </c>
       <c r="B11" t="n">
-        <v>79018</v>
+        <v>90940</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1770,41 +1708,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6459</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528898</v>
+        <v>528836</v>
       </c>
       <c r="R11" t="n">
-        <v>6998770</v>
+        <v>6998668</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1831,24 +1769,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1863,22 +1786,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122819182</v>
+        <v>122819213</v>
       </c>
       <c r="B12" t="n">
-        <v>90936</v>
+        <v>79847</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1891,34 +1814,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528836</v>
+        <v>528849</v>
       </c>
       <c r="R12" t="n">
-        <v>6998668</v>
+        <v>6998626</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1948,9 +1871,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1965,22 +1903,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122819697</v>
+        <v>122822228</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1993,39 +1931,43 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528891</v>
+        <v>528846</v>
       </c>
       <c r="R13" t="n">
-        <v>6998754</v>
+        <v>6998743</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2055,24 +1997,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gammal levande tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2087,22 +2014,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122821939</v>
+        <v>122822120</v>
       </c>
       <c r="B14" t="n">
-        <v>78762</v>
+        <v>79847</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2115,46 +2042,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528796</v>
+        <v>528832</v>
       </c>
       <c r="R14" t="n">
-        <v>6998791</v>
+        <v>6998742</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2181,19 +2099,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2208,22 +2116,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122822259</v>
+        <v>122820570</v>
       </c>
       <c r="B15" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2236,42 +2144,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528831</v>
+        <v>528842</v>
       </c>
       <c r="R15" t="n">
-        <v>6998741</v>
+        <v>6998786</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2298,24 +2206,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2330,22 +2228,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122822120</v>
+        <v>122820739</v>
       </c>
       <c r="B16" t="n">
-        <v>79843</v>
+        <v>77699</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2358,34 +2256,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528832</v>
+        <v>528795</v>
       </c>
       <c r="R16" t="n">
-        <v>6998742</v>
+        <v>6998791</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2415,9 +2313,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2432,22 +2345,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122819081</v>
+        <v>122822436</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>78503</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2460,42 +2373,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528837</v>
+        <v>528840</v>
       </c>
       <c r="R17" t="n">
-        <v>6998667</v>
+        <v>6998787</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2522,14 +2430,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På kolad ved på tallstubbe</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2544,22 +2462,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122820176</v>
+        <v>122822680</v>
       </c>
       <c r="B18" t="n">
-        <v>57631</v>
+        <v>78503</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2572,34 +2490,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
         <v>528888</v>
       </c>
       <c r="R18" t="n">
-        <v>6998720</v>
+        <v>6998655</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2629,9 +2547,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På kolad ved på tallhögstubbe</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2646,22 +2579,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122822761</v>
+        <v>122822354</v>
       </c>
       <c r="B19" t="n">
-        <v>79843</v>
+        <v>91116</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2674,34 +2607,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>1588</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528879</v>
+        <v>528838</v>
       </c>
       <c r="R19" t="n">
-        <v>6998619</v>
+        <v>6998736</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2731,24 +2664,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2763,22 +2681,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122822436</v>
+        <v>122819701</v>
       </c>
       <c r="B20" t="n">
-        <v>78499</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2791,37 +2709,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528840</v>
+        <v>528843</v>
       </c>
       <c r="R20" t="n">
-        <v>6998787</v>
+        <v>6998744</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2848,24 +2766,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På kolad ved på tallstubbe</t>
+          <t>Rikligt på många granar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2876,26 +2784,51 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122820232</v>
+        <v>122819522</v>
       </c>
       <c r="B21" t="n">
-        <v>77709</v>
+        <v>57478</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2908,34 +2841,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>314</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528897</v>
+        <v>528843</v>
       </c>
       <c r="R21" t="n">
-        <v>6998766</v>
+        <v>6998616</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2965,24 +2903,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2997,22 +2925,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122819987</v>
+        <v>122819697</v>
       </c>
       <c r="B22" t="n">
-        <v>79878</v>
+        <v>57478</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3021,38 +2949,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528883</v>
+        <v>528891</v>
       </c>
       <c r="R22" t="n">
-        <v>6998770</v>
+        <v>6998754</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3084,7 +3017,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3094,12 +3027,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På sälglåga</t>
+          <t>Äldre ringhack på gammal levande tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3114,22 +3047,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122819701</v>
+        <v>122819010</v>
       </c>
       <c r="B23" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3142,37 +3075,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528843</v>
+        <v>528818</v>
       </c>
       <c r="R23" t="n">
-        <v>6998744</v>
+        <v>6998712</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3206,7 +3144,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Rikligt på många granar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3217,31 +3155,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3258,7 +3171,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122819010</v>
+        <v>122819030</v>
       </c>
       <c r="B24" t="n">
         <v>57478</v>
@@ -3303,10 +3216,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528818</v>
+        <v>528811</v>
       </c>
       <c r="R24" t="n">
-        <v>6998712</v>
+        <v>6998709</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3370,10 +3283,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122822075</v>
+        <v>122823006</v>
       </c>
       <c r="B25" t="n">
-        <v>74675</v>
+        <v>79847</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3382,41 +3295,46 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6428</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528829</v>
+        <v>528861</v>
       </c>
       <c r="R25" t="n">
-        <v>6998747</v>
+        <v>6998604</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3456,6 +3374,31 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3472,10 +3415,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122822228</v>
+        <v>122819626</v>
       </c>
       <c r="B26" t="n">
-        <v>57631</v>
+        <v>79847</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3488,43 +3431,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528846</v>
+        <v>528907</v>
       </c>
       <c r="R26" t="n">
-        <v>6998743</v>
+        <v>6998684</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3557,6 +3491,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3583,10 +3522,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122819626</v>
+        <v>122822197</v>
       </c>
       <c r="B27" t="n">
-        <v>79843</v>
+        <v>95901</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3599,21 +3538,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3623,10 +3562,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528907</v>
+        <v>528847</v>
       </c>
       <c r="R27" t="n">
-        <v>6998684</v>
+        <v>6998739</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3659,11 +3598,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3690,10 +3624,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122819526</v>
+        <v>122819987</v>
       </c>
       <c r="B28" t="n">
-        <v>90940</v>
+        <v>79882</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3702,25 +3636,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3730,10 +3664,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528875</v>
+        <v>528883</v>
       </c>
       <c r="R28" t="n">
-        <v>6998691</v>
+        <v>6998770</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3765,7 +3699,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3775,12 +3709,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3807,10 +3741,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122819870</v>
+        <v>122822075</v>
       </c>
       <c r="B29" t="n">
-        <v>79843</v>
+        <v>74675</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3819,50 +3753,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6428</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528902</v>
+        <v>528829</v>
       </c>
       <c r="R29" t="n">
-        <v>6998729</v>
+        <v>6998747</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3889,24 +3814,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>11:29</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>11:29</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På björklåga</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3921,22 +3831,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122819919</v>
+        <v>122822290</v>
       </c>
       <c r="B30" t="n">
-        <v>74854</v>
+        <v>57478</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3945,38 +3855,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528873</v>
+        <v>528824</v>
       </c>
       <c r="R30" t="n">
-        <v>6998728</v>
+        <v>6998724</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4006,24 +3921,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På bark i hålighet vid basen av gammal björkhögstubbe</t>
+          <t>Äldre ringhack på en hackspettsbearbetad död gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4034,23 +3939,48 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122820365</v>
+        <v>122819081</v>
       </c>
       <c r="B31" t="n">
         <v>57478</v>
@@ -4091,17 +4021,17 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528893</v>
+        <v>528837</v>
       </c>
       <c r="R31" t="n">
-        <v>6998757</v>
+        <v>6998667</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4128,24 +4058,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gammal tall, äldre ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4160,22 +4080,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122822373</v>
+        <v>122819057</v>
       </c>
       <c r="B32" t="n">
-        <v>90940</v>
+        <v>78766</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4188,34 +4108,43 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528856</v>
+        <v>528830</v>
       </c>
       <c r="R32" t="n">
-        <v>6998762</v>
+        <v>6998611</v>
       </c>
       <c r="S32" t="n">
         <v>8</v>
@@ -4247,7 +4176,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4257,12 +4186,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>Rikligt på gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4289,10 +4218,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122822354</v>
+        <v>122822781</v>
       </c>
       <c r="B33" t="n">
-        <v>91112</v>
+        <v>79883</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4301,38 +4230,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1588</v>
+        <v>6464</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528838</v>
+        <v>528877</v>
       </c>
       <c r="R33" t="n">
-        <v>6998736</v>
+        <v>6998634</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4362,9 +4291,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4379,22 +4323,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122819041</v>
+        <v>122820115</v>
       </c>
       <c r="B34" t="n">
-        <v>57478</v>
+        <v>74855</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4407,39 +4351,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528830</v>
+        <v>528898</v>
       </c>
       <c r="R34" t="n">
-        <v>6998687</v>
+        <v>6998773</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4469,14 +4408,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På ved på gammal levande sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4491,22 +4440,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122819213</v>
+        <v>122819597</v>
       </c>
       <c r="B35" t="n">
-        <v>79843</v>
+        <v>82553</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4519,21 +4468,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4543,10 +4492,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528849</v>
+        <v>528869</v>
       </c>
       <c r="R35" t="n">
-        <v>6998626</v>
+        <v>6998649</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4578,7 +4527,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4588,12 +4537,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4608,22 +4557,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122819055</v>
+        <v>122821939</v>
       </c>
       <c r="B36" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4636,42 +4585,46 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528843</v>
+        <v>528796</v>
       </c>
       <c r="R36" t="n">
-        <v>6998681</v>
+        <v>6998791</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4698,14 +4651,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4720,22 +4678,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122820570</v>
+        <v>122820176</v>
       </c>
       <c r="B37" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4748,39 +4706,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528842</v>
+        <v>528888</v>
       </c>
       <c r="R37" t="n">
-        <v>6998786</v>
+        <v>6998720</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4813,11 +4766,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4844,10 +4792,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122819057</v>
+        <v>122820141</v>
       </c>
       <c r="B38" t="n">
-        <v>78762</v>
+        <v>90944</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4860,46 +4808,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528830</v>
+        <v>528888</v>
       </c>
       <c r="R38" t="n">
-        <v>6998611</v>
+        <v>6998720</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4926,24 +4865,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>10:51</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>10:51</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Rikligt på gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4958,12 +4882,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5082,10 +5006,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122819726</v>
+        <v>122820232</v>
       </c>
       <c r="B40" t="n">
-        <v>57589</v>
+        <v>77709</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5094,47 +5018,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103031</v>
+        <v>314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Kremp.) A.F.W.Schmidt</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528900</v>
+        <v>528897</v>
       </c>
       <c r="R40" t="n">
-        <v>6998697</v>
+        <v>6998766</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5164,9 +5079,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5181,22 +5111,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122819597</v>
+        <v>122822818</v>
       </c>
       <c r="B41" t="n">
-        <v>82549</v>
+        <v>79847</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5209,34 +5139,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528869</v>
+        <v>528919</v>
       </c>
       <c r="R41" t="n">
-        <v>6998649</v>
+        <v>6998644</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5266,24 +5201,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På två gamla grovbarkade sälgar.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5294,26 +5219,51 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122820115</v>
+        <v>122819608</v>
       </c>
       <c r="B42" t="n">
-        <v>74855</v>
+        <v>78766</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5326,37 +5276,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528898</v>
+        <v>528807</v>
       </c>
       <c r="R42" t="n">
-        <v>6998773</v>
+        <v>6998706</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5383,24 +5338,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På ved på gammal levande sälg i gammal granskog</t>
+          <t>Relativt ymnigt på många granar. Fertila bålar finns här.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5411,23 +5356,48 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122822290</v>
+        <v>122821953</v>
       </c>
       <c r="B43" t="n">
         <v>57478</v>
@@ -5468,14 +5438,14 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528824</v>
+        <v>528813</v>
       </c>
       <c r="R43" t="n">
-        <v>6998724</v>
+        <v>6998760</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5512,7 +5482,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en hackspettsbearbetad död gran.</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5523,31 +5493,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5564,10 +5509,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122820141</v>
+        <v>122822259</v>
       </c>
       <c r="B44" t="n">
-        <v>90940</v>
+        <v>78766</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5580,37 +5525,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528888</v>
+        <v>528831</v>
       </c>
       <c r="R44" t="n">
-        <v>6998720</v>
+        <v>6998741</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5637,9 +5587,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5654,22 +5619,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122821953</v>
+        <v>122822761</v>
       </c>
       <c r="B45" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5682,39 +5647,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528813</v>
+        <v>528879</v>
       </c>
       <c r="R45" t="n">
-        <v>6998760</v>
+        <v>6998619</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5744,14 +5704,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5766,22 +5736,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122822197</v>
+        <v>122820150</v>
       </c>
       <c r="B46" t="n">
-        <v>95893</v>
+        <v>79022</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5790,41 +5760,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>53</v>
+        <v>6459</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528847</v>
+        <v>528898</v>
       </c>
       <c r="R46" t="n">
-        <v>6998739</v>
+        <v>6998770</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5851,9 +5821,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5868,22 +5853,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122819825</v>
+        <v>122819041</v>
       </c>
       <c r="B47" t="n">
-        <v>74675</v>
+        <v>57478</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5892,38 +5877,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6428</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528895</v>
+        <v>528830</v>
       </c>
       <c r="R47" t="n">
-        <v>6998697</v>
+        <v>6998687</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5956,6 +5946,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5982,10 +5977,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122819543</v>
+        <v>122820365</v>
       </c>
       <c r="B48" t="n">
-        <v>74849</v>
+        <v>57478</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5994,38 +5989,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>306</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528863</v>
+        <v>528893</v>
       </c>
       <c r="R48" t="n">
-        <v>6998680</v>
+        <v>6998757</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6057,7 +6057,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På ved på björkhögstubbe i gammal granskog</t>
+          <t>På gammal tall, äldre ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6099,10 +6099,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122820558</v>
+        <v>122819526</v>
       </c>
       <c r="B49" t="n">
-        <v>74863</v>
+        <v>90944</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6115,21 +6115,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6139,13 +6139,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528878</v>
+        <v>528875</v>
       </c>
       <c r="R49" t="n">
-        <v>6998770</v>
+        <v>6998691</v>
       </c>
       <c r="S49" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6216,10 +6216,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122819960</v>
+        <v>122820024</v>
       </c>
       <c r="B50" t="n">
-        <v>57478</v>
+        <v>57589</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6228,20 +6228,20 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -6251,19 +6251,11 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -6280,10 +6272,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>528893</v>
+        <v>528891</v>
       </c>
       <c r="R50" t="n">
-        <v>6998687</v>
+        <v>6998690</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6320,7 +6312,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Rätt så skygg hane av tretåig hackspett i barrnaturskog med mycket höga livsmiljövärden för tretåig hackspett.</t>
+          <t>Tre lavskrikor i naturskog med höga naturvärden.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6339,7 +6331,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Kontinuitetsskog med höga naturvärden.</t>
+          <t>Flerskiktad hänglavsrik barrnaturskog med höga naturvärden.</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6357,10 +6349,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122820024</v>
+        <v>122819915</v>
       </c>
       <c r="B51" t="n">
-        <v>57589</v>
+        <v>57478</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6369,20 +6361,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -6392,14 +6384,18 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -6413,10 +6409,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>528891</v>
+        <v>528893</v>
       </c>
       <c r="R51" t="n">
-        <v>6998690</v>
+        <v>6998687</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6453,7 +6449,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Tre lavskrikor i naturskog med höga naturvärden.</t>
+          <t>Födosökande hona och hane av tretåig hackspett i skog med höga till mycket höga livsmiljövärden.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6472,7 +6468,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Flerskiktad hänglavsrik barrnaturskog med höga naturvärden.</t>
+          <t>Flerskiktad barrnaturskog med höga naturvärden.</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6612,10 +6608,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122820461</v>
+        <v>122820539</v>
       </c>
       <c r="B53" t="n">
-        <v>57478</v>
+        <v>90944</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6628,47 +6624,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>528854</v>
+        <v>528851</v>
       </c>
       <c r="R53" t="n">
-        <v>6998728</v>
+        <v>6998721</v>
       </c>
       <c r="S53" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6700,11 +6691,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Färska ringhack längs ca 3 m på en granstam i barrnaturskog med revir för tretåig hackspett i höga livsmiljövärden.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6731,12 +6717,12 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6754,10 +6740,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122820539</v>
+        <v>122820461</v>
       </c>
       <c r="B54" t="n">
-        <v>90940</v>
+        <v>57478</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6770,42 +6756,47 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>528851</v>
+        <v>528854</v>
       </c>
       <c r="R54" t="n">
-        <v>6998721</v>
+        <v>6998728</v>
       </c>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6837,6 +6828,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Färska ringhack längs ca 3 m på en granstam i barrnaturskog med revir för tretåig hackspett i höga livsmiljövärden.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6863,12 +6859,12 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>

--- a/artfynd/A 55408-2024 artfynd.xlsx
+++ b/artfynd/A 55408-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122819677</v>
+        <v>122819870</v>
       </c>
       <c r="B2" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528904</v>
+        <v>528902</v>
       </c>
       <c r="R2" t="n">
-        <v>6998685</v>
+        <v>6998729</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,9 +757,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På björklåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,22 +789,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122819919</v>
+        <v>122819677</v>
       </c>
       <c r="B3" t="n">
-        <v>74854</v>
+        <v>79848</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +813,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>492</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528873</v>
+        <v>528904</v>
       </c>
       <c r="R3" t="n">
-        <v>6998728</v>
+        <v>6998685</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,24 +874,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På bark i hålighet vid basen av gammal björkhögstubbe</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,22 +891,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122819870</v>
+        <v>122819919</v>
       </c>
       <c r="B4" t="n">
-        <v>79847</v>
+        <v>74854</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -906,50 +915,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>492</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528902</v>
+        <v>528873</v>
       </c>
       <c r="R4" t="n">
-        <v>6998729</v>
+        <v>6998728</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,12 +988,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På björklåga</t>
+          <t>På bark i hålighet vid basen av gammal björkhögstubbe</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,12 +1008,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1696,10 +1696,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122819182</v>
+        <v>122822228</v>
       </c>
       <c r="B11" t="n">
-        <v>90940</v>
+        <v>57631</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1712,34 +1712,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528836</v>
+        <v>528846</v>
       </c>
       <c r="R11" t="n">
-        <v>6998668</v>
+        <v>6998743</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1798,10 +1807,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122819213</v>
+        <v>122819182</v>
       </c>
       <c r="B12" t="n">
-        <v>79847</v>
+        <v>90940</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1814,34 +1823,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528849</v>
+        <v>528836</v>
       </c>
       <c r="R12" t="n">
-        <v>6998626</v>
+        <v>6998668</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1871,24 +1880,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:57</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>10:57</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1903,22 +1897,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122822228</v>
+        <v>122819213</v>
       </c>
       <c r="B13" t="n">
-        <v>57631</v>
+        <v>79847</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1931,43 +1925,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528846</v>
+        <v>528849</v>
       </c>
       <c r="R13" t="n">
-        <v>6998743</v>
+        <v>6998626</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1997,9 +1982,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2014,12 +2014,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -3415,10 +3415,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122819626</v>
+        <v>122822197</v>
       </c>
       <c r="B26" t="n">
-        <v>79847</v>
+        <v>95901</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3431,21 +3431,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3455,10 +3455,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528907</v>
+        <v>528847</v>
       </c>
       <c r="R26" t="n">
-        <v>6998684</v>
+        <v>6998739</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3491,11 +3491,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3522,10 +3517,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122822197</v>
+        <v>122819626</v>
       </c>
       <c r="B27" t="n">
-        <v>95901</v>
+        <v>79847</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3538,21 +3533,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3562,10 +3557,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528847</v>
+        <v>528907</v>
       </c>
       <c r="R27" t="n">
-        <v>6998739</v>
+        <v>6998684</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3598,6 +3593,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3843,10 +3843,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122822290</v>
+        <v>122822781</v>
       </c>
       <c r="B30" t="n">
-        <v>57478</v>
+        <v>79883</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3855,43 +3855,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528824</v>
+        <v>528877</v>
       </c>
       <c r="R30" t="n">
-        <v>6998724</v>
+        <v>6998634</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3921,14 +3916,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en hackspettsbearbetad död gran.</t>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3939,48 +3944,23 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122819081</v>
+        <v>122822290</v>
       </c>
       <c r="B31" t="n">
         <v>57478</v>
@@ -4025,10 +4005,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528837</v>
+        <v>528824</v>
       </c>
       <c r="R31" t="n">
-        <v>6998667</v>
+        <v>6998724</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4065,7 +4045,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre ringhack på en hackspettsbearbetad död gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4076,6 +4056,31 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4092,10 +4097,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122819057</v>
+        <v>122819081</v>
       </c>
       <c r="B32" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4108,46 +4113,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528830</v>
+        <v>528837</v>
       </c>
       <c r="R32" t="n">
-        <v>6998611</v>
+        <v>6998667</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4174,24 +4175,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>10:51</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>10:51</t>
-        </is>
-      </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Rikligt på gamla granar i gammal granskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4206,22 +4197,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122822781</v>
+        <v>122819057</v>
       </c>
       <c r="B33" t="n">
-        <v>79883</v>
+        <v>78766</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4230,41 +4221,50 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528877</v>
+        <v>528830</v>
       </c>
       <c r="R33" t="n">
-        <v>6998634</v>
+        <v>6998611</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+          <t>Rikligt på gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 55408-2024 artfynd.xlsx
+++ b/artfynd/A 55408-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY54"/>
+  <dimension ref="A1:AY55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122819870</v>
+        <v>122822197</v>
       </c>
       <c r="B2" t="n">
-        <v>79847</v>
+        <v>95901</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,46 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528902</v>
+        <v>528847</v>
       </c>
       <c r="R2" t="n">
-        <v>6998729</v>
+        <v>6998739</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,24 +748,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:29</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:29</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På björklåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122819677</v>
+        <v>122819213</v>
       </c>
       <c r="B3" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528904</v>
+        <v>528849</v>
       </c>
       <c r="R3" t="n">
-        <v>6998685</v>
+        <v>6998626</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,9 +850,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,22 +882,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122819919</v>
+        <v>122819030</v>
       </c>
       <c r="B4" t="n">
-        <v>74854</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,38 +906,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528873</v>
+        <v>528811</v>
       </c>
       <c r="R4" t="n">
-        <v>6998728</v>
+        <v>6998709</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,24 +972,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På bark i hålighet vid basen av gammal björkhögstubbe</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,22 +994,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122822373</v>
+        <v>122822120</v>
       </c>
       <c r="B5" t="n">
-        <v>90944</v>
+        <v>79847</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,37 +1022,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528856</v>
+        <v>528832</v>
       </c>
       <c r="R5" t="n">
-        <v>6998762</v>
+        <v>6998742</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,24 +1079,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,22 +1096,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122819543</v>
+        <v>122820232</v>
       </c>
       <c r="B6" t="n">
-        <v>74849</v>
+        <v>77709</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,25 +1120,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1177,13 +1148,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528863</v>
+        <v>528897</v>
       </c>
       <c r="R6" t="n">
-        <v>6998680</v>
+        <v>6998766</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,12 +1193,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På ved på björkhögstubbe i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122819825</v>
+        <v>122819919</v>
       </c>
       <c r="B7" t="n">
-        <v>74675</v>
+        <v>74854</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,38 +1237,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6428</v>
+        <v>492</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528895</v>
+        <v>528873</v>
       </c>
       <c r="R7" t="n">
-        <v>6998697</v>
+        <v>6998728</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,9 +1298,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På bark i hålighet vid basen av gammal björkhögstubbe</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,12 +1330,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1473,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122819726</v>
+        <v>122821953</v>
       </c>
       <c r="B9" t="n">
-        <v>57589</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,20 +1471,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1506,14 +1492,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1522,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528900</v>
+        <v>528813</v>
       </c>
       <c r="R9" t="n">
-        <v>6998697</v>
+        <v>6998760</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1558,6 +1540,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122819055</v>
+        <v>122822680</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>78503</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,39 +1587,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528843</v>
+        <v>528888</v>
       </c>
       <c r="R10" t="n">
-        <v>6998681</v>
+        <v>6998655</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1662,14 +1644,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På kolad ved på tallhögstubbe</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1684,22 +1676,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122822228</v>
+        <v>122819597</v>
       </c>
       <c r="B11" t="n">
-        <v>57631</v>
+        <v>82553</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1712,43 +1704,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528846</v>
+        <v>528869</v>
       </c>
       <c r="R11" t="n">
-        <v>6998743</v>
+        <v>6998649</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1778,9 +1761,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,22 +1793,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122819182</v>
+        <v>122820141</v>
       </c>
       <c r="B12" t="n">
-        <v>90940</v>
+        <v>90944</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1823,21 +1821,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1847,10 +1845,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528836</v>
+        <v>528888</v>
       </c>
       <c r="R12" t="n">
-        <v>6998668</v>
+        <v>6998720</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1909,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122819213</v>
+        <v>122819522</v>
       </c>
       <c r="B13" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1925,34 +1923,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528849</v>
+        <v>528843</v>
       </c>
       <c r="R13" t="n">
-        <v>6998626</v>
+        <v>6998616</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1982,24 +1985,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>10:57</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>10:57</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2014,22 +2007,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122822120</v>
+        <v>122819987</v>
       </c>
       <c r="B14" t="n">
-        <v>79847</v>
+        <v>79882</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2038,38 +2031,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528832</v>
+        <v>528883</v>
       </c>
       <c r="R14" t="n">
-        <v>6998742</v>
+        <v>6998770</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2099,9 +2092,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2116,22 +2124,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122820570</v>
+        <v>122822373</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>90944</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2144,42 +2152,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528842</v>
+        <v>528856</v>
       </c>
       <c r="R15" t="n">
-        <v>6998786</v>
+        <v>6998762</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2206,14 +2209,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2228,22 +2241,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122820739</v>
+        <v>122822228</v>
       </c>
       <c r="B16" t="n">
-        <v>77699</v>
+        <v>57631</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2256,34 +2269,43 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228579</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528795</v>
+        <v>528846</v>
       </c>
       <c r="R16" t="n">
-        <v>6998791</v>
+        <v>6998743</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2313,24 +2335,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2345,22 +2352,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122822436</v>
+        <v>122822259</v>
       </c>
       <c r="B17" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2373,34 +2380,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528840</v>
+        <v>528831</v>
       </c>
       <c r="R17" t="n">
-        <v>6998787</v>
+        <v>6998741</v>
       </c>
       <c r="S17" t="n">
         <v>7</v>
@@ -2432,7 +2444,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2442,12 +2454,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På kolad ved på tallstubbe</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2474,10 +2486,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122822680</v>
+        <v>122819057</v>
       </c>
       <c r="B18" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2490,37 +2502,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528888</v>
+        <v>528830</v>
       </c>
       <c r="R18" t="n">
-        <v>6998655</v>
+        <v>6998611</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2549,7 +2570,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2559,12 +2580,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På kolad ved på tallhögstubbe</t>
+          <t>Rikligt på gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2591,10 +2612,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122822354</v>
+        <v>122819726</v>
       </c>
       <c r="B19" t="n">
-        <v>91116</v>
+        <v>57589</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2603,38 +2624,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1588</v>
+        <v>103031</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528838</v>
+        <v>528900</v>
       </c>
       <c r="R19" t="n">
-        <v>6998736</v>
+        <v>6998697</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2693,10 +2723,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122819701</v>
+        <v>122822354</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>91116</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2709,21 +2739,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1588</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2733,13 +2763,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528843</v>
+        <v>528838</v>
       </c>
       <c r="R20" t="n">
-        <v>6998744</v>
+        <v>6998736</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2771,11 +2801,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Rikligt på många granar.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2784,31 +2809,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2825,10 +2825,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122819522</v>
+        <v>122819526</v>
       </c>
       <c r="B21" t="n">
-        <v>57478</v>
+        <v>90944</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2841,39 +2841,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528843</v>
+        <v>528875</v>
       </c>
       <c r="R21" t="n">
-        <v>6998616</v>
+        <v>6998691</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2903,14 +2898,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2925,22 +2930,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122819697</v>
+        <v>122819608</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2953,42 +2958,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528891</v>
+        <v>528807</v>
       </c>
       <c r="R22" t="n">
-        <v>6998754</v>
+        <v>6998706</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3015,24 +3020,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gammal levande tall</t>
+          <t>Relativt ymnigt på många granar. Fertila bålar finns här.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3043,26 +3038,51 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122819010</v>
+        <v>122819543</v>
       </c>
       <c r="B23" t="n">
-        <v>57478</v>
+        <v>74849</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3071,46 +3091,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528818</v>
+        <v>528863</v>
       </c>
       <c r="R23" t="n">
-        <v>6998712</v>
+        <v>6998680</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3137,14 +3152,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På ved på björkhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3159,22 +3184,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122819030</v>
+        <v>122822075</v>
       </c>
       <c r="B24" t="n">
-        <v>57478</v>
+        <v>74675</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3183,43 +3208,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6428</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528811</v>
+        <v>528829</v>
       </c>
       <c r="R24" t="n">
-        <v>6998709</v>
+        <v>6998747</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3252,11 +3272,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3283,10 +3298,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122823006</v>
+        <v>122819182</v>
       </c>
       <c r="B25" t="n">
-        <v>79847</v>
+        <v>90940</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3299,42 +3314,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528861</v>
+        <v>528836</v>
       </c>
       <c r="R25" t="n">
-        <v>6998604</v>
+        <v>6998668</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3374,31 +3384,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3415,10 +3400,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122822197</v>
+        <v>122819701</v>
       </c>
       <c r="B26" t="n">
-        <v>95901</v>
+        <v>78766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3431,21 +3416,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3455,13 +3440,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528847</v>
+        <v>528843</v>
       </c>
       <c r="R26" t="n">
-        <v>6998739</v>
+        <v>6998744</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3493,6 +3478,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt på många granar.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3501,6 +3491,31 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3517,10 +3532,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122819626</v>
+        <v>122822436</v>
       </c>
       <c r="B27" t="n">
-        <v>79847</v>
+        <v>78503</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3533,37 +3548,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528907</v>
+        <v>528840</v>
       </c>
       <c r="R27" t="n">
-        <v>6998684</v>
+        <v>6998787</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3590,14 +3605,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>På kolad ved på tallstubbe</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3612,22 +3637,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122819987</v>
+        <v>122819081</v>
       </c>
       <c r="B28" t="n">
-        <v>79882</v>
+        <v>57478</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3636,38 +3661,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528883</v>
+        <v>528837</v>
       </c>
       <c r="R28" t="n">
-        <v>6998770</v>
+        <v>6998667</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3697,24 +3727,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På sälglåga</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3729,22 +3749,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122822075</v>
+        <v>122822761</v>
       </c>
       <c r="B29" t="n">
-        <v>74675</v>
+        <v>79847</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3753,38 +3773,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6428</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528829</v>
+        <v>528879</v>
       </c>
       <c r="R29" t="n">
-        <v>6998747</v>
+        <v>6998619</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3814,9 +3834,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3831,22 +3866,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122822781</v>
+        <v>122819677</v>
       </c>
       <c r="B30" t="n">
-        <v>79883</v>
+        <v>79848</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3855,38 +3890,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528877</v>
+        <v>528904</v>
       </c>
       <c r="R30" t="n">
-        <v>6998634</v>
+        <v>6998685</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3916,24 +3951,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3948,19 +3968,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122822290</v>
+        <v>122819010</v>
       </c>
       <c r="B31" t="n">
         <v>57478</v>
@@ -4005,10 +4025,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528824</v>
+        <v>528818</v>
       </c>
       <c r="R31" t="n">
-        <v>6998724</v>
+        <v>6998712</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4045,7 +4065,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en hackspettsbearbetad död gran.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4056,31 +4076,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4097,10 +4092,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122819081</v>
+        <v>122820739</v>
       </c>
       <c r="B32" t="n">
-        <v>57478</v>
+        <v>77699</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4113,39 +4108,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528837</v>
+        <v>528795</v>
       </c>
       <c r="R32" t="n">
-        <v>6998667</v>
+        <v>6998791</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4175,14 +4165,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4197,19 +4197,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122819057</v>
+        <v>122821939</v>
       </c>
       <c r="B33" t="n">
         <v>78766</v>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4258,10 +4258,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528830</v>
+        <v>528796</v>
       </c>
       <c r="R33" t="n">
-        <v>6998611</v>
+        <v>6998791</v>
       </c>
       <c r="S33" t="n">
         <v>8</v>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4303,12 +4303,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:51</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Rikligt på gamla granar i gammal granskog</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4323,22 +4318,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122820115</v>
+        <v>122819697</v>
       </c>
       <c r="B34" t="n">
-        <v>74855</v>
+        <v>57478</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4351,34 +4346,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528898</v>
+        <v>528891</v>
       </c>
       <c r="R34" t="n">
-        <v>6998773</v>
+        <v>6998754</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4410,7 +4410,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På ved på gammal levande sälg i gammal granskog</t>
+          <t>Äldre ringhack på gammal levande tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4452,10 +4452,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122819597</v>
+        <v>122822818</v>
       </c>
       <c r="B35" t="n">
-        <v>82553</v>
+        <v>79847</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4468,34 +4468,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528869</v>
+        <v>528919</v>
       </c>
       <c r="R35" t="n">
-        <v>6998649</v>
+        <v>6998644</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4525,24 +4530,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På två gamla grovbarkade sälgar.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4553,26 +4548,51 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122821939</v>
+        <v>122820365</v>
       </c>
       <c r="B36" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4585,31 +4605,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4618,13 +4634,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528796</v>
+        <v>528893</v>
       </c>
       <c r="R36" t="n">
-        <v>6998791</v>
+        <v>6998757</v>
       </c>
       <c r="S36" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4653,7 +4669,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4663,7 +4679,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På gammal tall, äldre ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4678,22 +4699,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122820176</v>
+        <v>122823006</v>
       </c>
       <c r="B37" t="n">
-        <v>57631</v>
+        <v>79847</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4706,37 +4727,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528888</v>
+        <v>528861</v>
       </c>
       <c r="R37" t="n">
-        <v>6998720</v>
+        <v>6998604</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4776,6 +4802,31 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4792,10 +4843,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122820141</v>
+        <v>122819041</v>
       </c>
       <c r="B38" t="n">
-        <v>90944</v>
+        <v>57478</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4808,34 +4859,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528888</v>
+        <v>528830</v>
       </c>
       <c r="R38" t="n">
-        <v>6998720</v>
+        <v>6998687</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4868,6 +4924,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5006,10 +5067,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122820232</v>
+        <v>122820176</v>
       </c>
       <c r="B40" t="n">
-        <v>77709</v>
+        <v>57631</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5022,34 +5083,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>314</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528897</v>
+        <v>528888</v>
       </c>
       <c r="R40" t="n">
-        <v>6998766</v>
+        <v>6998720</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5079,24 +5140,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5111,19 +5157,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122822818</v>
+        <v>122819870</v>
       </c>
       <c r="B41" t="n">
         <v>79847</v>
@@ -5156,25 +5202,29 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528919</v>
+        <v>528902</v>
       </c>
       <c r="R41" t="n">
-        <v>6998644</v>
+        <v>6998729</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5201,14 +5251,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På två gamla grovbarkade sälgar.</t>
+          <t>På björklåga</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5219,51 +5279,26 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122819608</v>
+        <v>122819055</v>
       </c>
       <c r="B42" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5276,27 +5311,27 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5305,13 +5340,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528807</v>
+        <v>528843</v>
       </c>
       <c r="R42" t="n">
-        <v>6998706</v>
+        <v>6998681</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5345,7 +5380,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Relativt ymnigt på många granar. Fertila bålar finns här.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5356,31 +5391,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5397,10 +5407,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122821953</v>
+        <v>122820115</v>
       </c>
       <c r="B43" t="n">
-        <v>57478</v>
+        <v>74855</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5413,39 +5423,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528813</v>
+        <v>528898</v>
       </c>
       <c r="R43" t="n">
-        <v>6998760</v>
+        <v>6998773</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5475,14 +5480,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>På ved på gammal levande sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5497,22 +5512,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122822259</v>
+        <v>122819825</v>
       </c>
       <c r="B44" t="n">
-        <v>78766</v>
+        <v>74675</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5521,46 +5536,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528831</v>
+        <v>528895</v>
       </c>
       <c r="R44" t="n">
-        <v>6998741</v>
+        <v>6998697</v>
       </c>
       <c r="S44" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5587,24 +5597,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5619,22 +5614,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122822761</v>
+        <v>122822290</v>
       </c>
       <c r="B45" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5647,34 +5642,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528879</v>
+        <v>528824</v>
       </c>
       <c r="R45" t="n">
-        <v>6998619</v>
+        <v>6998724</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5704,24 +5704,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På sälglåga</t>
+          <t>Äldre ringhack på en hackspettsbearbetad död gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5732,26 +5722,51 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122820150</v>
+        <v>122819626</v>
       </c>
       <c r="B46" t="n">
-        <v>79022</v>
+        <v>79847</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5760,41 +5775,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6459</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528898</v>
+        <v>528907</v>
       </c>
       <c r="R46" t="n">
-        <v>6998770</v>
+        <v>6998684</v>
       </c>
       <c r="S46" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5821,24 +5836,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5853,22 +5858,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122819041</v>
+        <v>122820150</v>
       </c>
       <c r="B47" t="n">
-        <v>57478</v>
+        <v>79022</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5877,46 +5882,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6459</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528830</v>
+        <v>528898</v>
       </c>
       <c r="R47" t="n">
-        <v>6998687</v>
+        <v>6998770</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5943,14 +5943,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5965,19 +5975,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122820365</v>
+        <v>122820570</v>
       </c>
       <c r="B48" t="n">
         <v>57478</v>
@@ -6013,22 +6023,22 @@
       <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528893</v>
+        <v>528842</v>
       </c>
       <c r="R48" t="n">
-        <v>6998757</v>
+        <v>6998786</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6055,24 +6065,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På gammal tall, äldre ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6087,22 +6087,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122819526</v>
+        <v>122822781</v>
       </c>
       <c r="B49" t="n">
-        <v>90944</v>
+        <v>79883</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6111,25 +6111,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6139,10 +6139,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528875</v>
+        <v>528877</v>
       </c>
       <c r="R49" t="n">
-        <v>6998691</v>
+        <v>6998634</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6174,7 +6174,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6204,22 +6204,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122820024</v>
+        <v>122822850</v>
       </c>
       <c r="B50" t="n">
-        <v>57589</v>
+        <v>5489</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6228,54 +6228,47 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103031</v>
+        <v>101410</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>528891</v>
+        <v>528902</v>
       </c>
       <c r="R50" t="n">
-        <v>6998690</v>
+        <v>6998601</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6310,17 +6303,13 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Tre lavskrikor i naturskog med höga naturvärden.</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6331,7 +6320,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Flerskiktad hänglavsrik barrnaturskog med höga naturvärden.</t>
+          <t>Gammal flerskiktad naturskogsartad kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6349,7 +6338,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122819915</v>
+        <v>122819960</v>
       </c>
       <c r="B51" t="n">
         <v>57478</v>
@@ -6384,18 +6373,22 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -6449,7 +6442,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Födosökande hona och hane av tretåig hackspett i skog med höga till mycket höga livsmiljövärden.</t>
+          <t>Rätt så skygg hane av tretåig hackspett i barrnaturskog med mycket höga livsmiljövärden för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6468,7 +6461,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Flerskiktad barrnaturskog med höga naturvärden.</t>
+          <t>Kontinuitetsskog med höga naturvärden.</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6486,10 +6479,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122822850</v>
+        <v>122820024</v>
       </c>
       <c r="B52" t="n">
-        <v>5489</v>
+        <v>57589</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6498,47 +6491,54 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>101410</v>
+        <v>103031</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>528902</v>
+        <v>528891</v>
       </c>
       <c r="R52" t="n">
-        <v>6998601</v>
+        <v>6998690</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6573,13 +6573,17 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Tre lavskrikor i naturskog med höga naturvärden.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6590,7 +6594,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Gammal flerskiktad naturskogsartad kontinuitetsskog.</t>
+          <t>Flerskiktad hänglavsrik barrnaturskog med höga naturvärden.</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6608,10 +6612,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122820539</v>
+        <v>122820461</v>
       </c>
       <c r="B53" t="n">
-        <v>90944</v>
+        <v>57478</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6624,42 +6628,47 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>528851</v>
+        <v>528854</v>
       </c>
       <c r="R53" t="n">
-        <v>6998721</v>
+        <v>6998728</v>
       </c>
       <c r="S53" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6691,6 +6700,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Färska ringhack längs ca 3 m på en granstam i barrnaturskog med revir för tretåig hackspett i höga livsmiljövärden.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6717,12 +6731,12 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6740,10 +6754,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122820461</v>
+        <v>122820539</v>
       </c>
       <c r="B54" t="n">
-        <v>57478</v>
+        <v>90944</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6756,47 +6770,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>528854</v>
+        <v>528851</v>
       </c>
       <c r="R54" t="n">
-        <v>6998728</v>
+        <v>6998721</v>
       </c>
       <c r="S54" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6828,11 +6837,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Färska ringhack längs ca 3 m på en granstam i barrnaturskog med revir för tretåig hackspett i höga livsmiljövärden.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6859,12 +6863,12 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6879,6 +6883,127 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>122819853</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79044</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>1816</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Luddig stiftdynlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Micarea hedlundii</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Coppins</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>528876</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6998733</v>
+      </c>
+      <c r="S55" t="n">
+        <v>8</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>På bark i hålighet vid basen av gammal grov björkhögstubbe. Konidiesporer 4-6 my långa.</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55408-2024 artfynd.xlsx
+++ b/artfynd/A 55408-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122822197</v>
+        <v>122821939</v>
       </c>
       <c r="B2" t="n">
-        <v>95901</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528847</v>
+        <v>528796</v>
       </c>
       <c r="R2" t="n">
-        <v>6998739</v>
+        <v>6998791</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,9 +757,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,22 +784,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122819213</v>
+        <v>122822680</v>
       </c>
       <c r="B3" t="n">
-        <v>79847</v>
+        <v>78503</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +812,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528849</v>
+        <v>528888</v>
       </c>
       <c r="R3" t="n">
-        <v>6998626</v>
+        <v>6998655</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,12 +881,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På kolad ved på tallhögstubbe</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,19 +901,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122819030</v>
+        <v>122821953</v>
       </c>
       <c r="B4" t="n">
         <v>57478</v>
@@ -935,14 +954,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528811</v>
+        <v>528813</v>
       </c>
       <c r="R4" t="n">
-        <v>6998709</v>
+        <v>6998760</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +998,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,7 +1025,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122822120</v>
+        <v>122822761</v>
       </c>
       <c r="B5" t="n">
         <v>79847</v>
@@ -1042,14 +1061,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528832</v>
+        <v>528879</v>
       </c>
       <c r="R5" t="n">
-        <v>6998742</v>
+        <v>6998619</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,9 +1098,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,22 +1130,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122820232</v>
+        <v>122819213</v>
       </c>
       <c r="B6" t="n">
-        <v>77709</v>
+        <v>79847</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1124,21 +1158,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>314</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1148,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528897</v>
+        <v>528849</v>
       </c>
       <c r="R6" t="n">
-        <v>6998766</v>
+        <v>6998626</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,12 +1227,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1213,22 +1247,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122819919</v>
+        <v>122820176</v>
       </c>
       <c r="B7" t="n">
-        <v>74854</v>
+        <v>57631</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,38 +1271,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>492</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528873</v>
+        <v>528888</v>
       </c>
       <c r="R7" t="n">
-        <v>6998728</v>
+        <v>6998720</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1298,24 +1332,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På bark i hålighet vid basen av gammal björkhögstubbe</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1330,22 +1349,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122820558</v>
+        <v>122820115</v>
       </c>
       <c r="B8" t="n">
-        <v>74863</v>
+        <v>74855</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1358,21 +1377,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,13 +1401,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528878</v>
+        <v>528898</v>
       </c>
       <c r="R8" t="n">
-        <v>6998770</v>
+        <v>6998773</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1417,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1427,12 +1446,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På ved på gammal levande sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,22 +1466,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122821953</v>
+        <v>122822781</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>79883</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,43 +1490,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528813</v>
+        <v>528877</v>
       </c>
       <c r="R9" t="n">
-        <v>6998760</v>
+        <v>6998634</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1537,14 +1551,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,22 +1583,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122822680</v>
+        <v>122822259</v>
       </c>
       <c r="B10" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,37 +1611,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528888</v>
+        <v>528831</v>
       </c>
       <c r="R10" t="n">
-        <v>6998655</v>
+        <v>6998741</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1646,7 +1675,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,12 +1685,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På kolad ved på tallhögstubbe</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1676,22 +1705,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122819597</v>
+        <v>122820570</v>
       </c>
       <c r="B11" t="n">
-        <v>82553</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1704,34 +1733,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528869</v>
+        <v>528842</v>
       </c>
       <c r="R11" t="n">
-        <v>6998649</v>
+        <v>6998786</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1761,24 +1795,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1793,22 +1817,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122820141</v>
+        <v>122822354</v>
       </c>
       <c r="B12" t="n">
-        <v>90944</v>
+        <v>91116</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1821,21 +1845,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1588</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1845,10 +1869,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528888</v>
+        <v>528838</v>
       </c>
       <c r="R12" t="n">
-        <v>6998720</v>
+        <v>6998736</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,10 +1931,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122819522</v>
+        <v>122819726</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>57589</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1919,20 +1943,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1940,22 +1964,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528843</v>
+        <v>528900</v>
       </c>
       <c r="R13" t="n">
-        <v>6998616</v>
+        <v>6998697</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1988,11 +2016,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,10 +2042,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122819987</v>
+        <v>122820150</v>
       </c>
       <c r="B14" t="n">
-        <v>79882</v>
+        <v>79022</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2035,21 +2058,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6463</v>
+        <v>6459</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,13 +2082,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528883</v>
+        <v>528898</v>
       </c>
       <c r="R14" t="n">
         <v>6998770</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2094,7 +2117,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,12 +2127,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På sälglåga</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2124,22 +2147,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122822373</v>
+        <v>122819608</v>
       </c>
       <c r="B15" t="n">
-        <v>90944</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2152,37 +2175,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528856</v>
+        <v>528807</v>
       </c>
       <c r="R15" t="n">
-        <v>6998762</v>
+        <v>6998706</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2209,24 +2237,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>Relativt ymnigt på många granar. Fertila bålar finns här.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2237,26 +2255,51 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122822228</v>
+        <v>122819010</v>
       </c>
       <c r="B16" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2269,43 +2312,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528846</v>
+        <v>528818</v>
       </c>
       <c r="R16" t="n">
-        <v>6998743</v>
+        <v>6998712</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2338,6 +2377,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2364,10 +2408,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122822259</v>
+        <v>122819677</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2380,42 +2424,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528831</v>
+        <v>528904</v>
       </c>
       <c r="R17" t="n">
-        <v>6998741</v>
+        <v>6998685</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2442,24 +2481,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2474,22 +2498,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122819057</v>
+        <v>122820558</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2502,46 +2526,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528830</v>
+        <v>528878</v>
       </c>
       <c r="R18" t="n">
-        <v>6998611</v>
+        <v>6998770</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2570,7 +2585,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2580,12 +2595,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt på gamla granar i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2600,22 +2615,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122819726</v>
+        <v>122819526</v>
       </c>
       <c r="B19" t="n">
-        <v>57589</v>
+        <v>90944</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2624,47 +2639,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103031</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528900</v>
+        <v>528875</v>
       </c>
       <c r="R19" t="n">
-        <v>6998697</v>
+        <v>6998691</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2694,9 +2700,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2711,22 +2732,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122822354</v>
+        <v>122819041</v>
       </c>
       <c r="B20" t="n">
-        <v>91116</v>
+        <v>57478</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2739,34 +2760,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1588</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528838</v>
+        <v>528830</v>
       </c>
       <c r="R20" t="n">
-        <v>6998736</v>
+        <v>6998687</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2799,6 +2825,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2825,10 +2856,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122819526</v>
+        <v>122820365</v>
       </c>
       <c r="B21" t="n">
-        <v>90944</v>
+        <v>57478</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2841,37 +2872,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528875</v>
+        <v>528893</v>
       </c>
       <c r="R21" t="n">
-        <v>6998691</v>
+        <v>6998757</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2900,7 +2936,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2910,12 +2946,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På gammal tall, äldre ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2930,22 +2966,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122819608</v>
+        <v>122822075</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>74675</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2954,46 +2990,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528807</v>
+        <v>528829</v>
       </c>
       <c r="R22" t="n">
-        <v>6998706</v>
+        <v>6998747</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3025,11 +3056,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Relativt ymnigt på många granar. Fertila bålar finns här.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3038,31 +3064,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3079,10 +3080,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122819543</v>
+        <v>122819522</v>
       </c>
       <c r="B23" t="n">
-        <v>74849</v>
+        <v>57478</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3091,41 +3092,46 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>306</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528863</v>
+        <v>528843</v>
       </c>
       <c r="R23" t="n">
-        <v>6998680</v>
+        <v>6998616</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3152,24 +3158,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På ved på björkhögstubbe i gammal granskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3184,22 +3180,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122822075</v>
+        <v>122822228</v>
       </c>
       <c r="B24" t="n">
-        <v>74675</v>
+        <v>57631</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3208,38 +3204,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6428</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528829</v>
+        <v>528846</v>
       </c>
       <c r="R24" t="n">
-        <v>6998747</v>
+        <v>6998743</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3298,10 +3303,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122819182</v>
+        <v>122819543</v>
       </c>
       <c r="B25" t="n">
-        <v>90940</v>
+        <v>74849</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3310,41 +3315,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528836</v>
+        <v>528863</v>
       </c>
       <c r="R25" t="n">
-        <v>6998668</v>
+        <v>6998680</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3371,9 +3376,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På ved på björkhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3388,22 +3408,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122819701</v>
+        <v>122819182</v>
       </c>
       <c r="B26" t="n">
-        <v>78766</v>
+        <v>90940</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3416,21 +3436,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3440,13 +3460,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528843</v>
+        <v>528836</v>
       </c>
       <c r="R26" t="n">
-        <v>6998744</v>
+        <v>6998668</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3478,11 +3498,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt på många granar.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3491,31 +3506,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3532,10 +3522,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122822436</v>
+        <v>122819870</v>
       </c>
       <c r="B27" t="n">
-        <v>78503</v>
+        <v>79847</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3548,37 +3538,46 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528840</v>
+        <v>528902</v>
       </c>
       <c r="R27" t="n">
-        <v>6998787</v>
+        <v>6998729</v>
       </c>
       <c r="S27" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3607,7 +3606,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3617,12 +3616,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På kolad ved på tallstubbe</t>
+          <t>På björklåga</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3642,14 +3641,14 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122819081</v>
+        <v>122819697</v>
       </c>
       <c r="B28" t="n">
         <v>57478</v>
@@ -3690,14 +3689,14 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528837</v>
+        <v>528891</v>
       </c>
       <c r="R28" t="n">
-        <v>6998667</v>
+        <v>6998754</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3727,14 +3726,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre ringhack på gammal levande tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3749,22 +3758,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122822761</v>
+        <v>122822290</v>
       </c>
       <c r="B29" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3777,34 +3786,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528879</v>
+        <v>528824</v>
       </c>
       <c r="R29" t="n">
-        <v>6998619</v>
+        <v>6998724</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3834,24 +3848,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På sälglåga</t>
+          <t>Äldre ringhack på en hackspettsbearbetad död gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3862,26 +3866,51 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122819677</v>
+        <v>122819825</v>
       </c>
       <c r="B30" t="n">
-        <v>79848</v>
+        <v>74675</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3890,25 +3919,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>6428</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3918,10 +3947,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528904</v>
+        <v>528895</v>
       </c>
       <c r="R30" t="n">
-        <v>6998685</v>
+        <v>6998697</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3980,10 +4009,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122819010</v>
+        <v>122820141</v>
       </c>
       <c r="B31" t="n">
-        <v>57478</v>
+        <v>90944</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3996,39 +4025,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528818</v>
+        <v>528888</v>
       </c>
       <c r="R31" t="n">
-        <v>6998712</v>
+        <v>6998720</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4061,11 +4085,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4092,10 +4111,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122820739</v>
+        <v>122822818</v>
       </c>
       <c r="B32" t="n">
-        <v>77699</v>
+        <v>79847</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4108,34 +4127,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528795</v>
+        <v>528919</v>
       </c>
       <c r="R32" t="n">
-        <v>6998791</v>
+        <v>6998644</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4165,24 +4189,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På två gamla grovbarkade sälgar.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4193,26 +4207,51 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122821939</v>
+        <v>122820550</v>
       </c>
       <c r="B33" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4225,46 +4264,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528796</v>
+        <v>528843</v>
       </c>
       <c r="R33" t="n">
-        <v>6998791</v>
+        <v>6998785</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4291,19 +4326,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>12:42</t>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4318,22 +4348,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122819697</v>
+        <v>122822197</v>
       </c>
       <c r="B34" t="n">
-        <v>57478</v>
+        <v>95903</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4346,39 +4376,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528891</v>
+        <v>528847</v>
       </c>
       <c r="R34" t="n">
-        <v>6998754</v>
+        <v>6998739</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4408,24 +4433,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gammal levande tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4440,22 +4450,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122822818</v>
+        <v>122822373</v>
       </c>
       <c r="B35" t="n">
-        <v>79847</v>
+        <v>90944</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4468,42 +4478,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528919</v>
+        <v>528856</v>
       </c>
       <c r="R35" t="n">
-        <v>6998644</v>
+        <v>6998762</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4530,14 +4535,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På två gamla grovbarkade sälgar.</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4548,51 +4563,26 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122820365</v>
+        <v>122819701</v>
       </c>
       <c r="B36" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4605,42 +4595,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528893</v>
+        <v>528843</v>
       </c>
       <c r="R36" t="n">
-        <v>6998757</v>
+        <v>6998744</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4667,24 +4652,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På gammal tall, äldre ringhack</t>
+          <t>Rikligt på många granar.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4695,26 +4670,51 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122823006</v>
+        <v>122819919</v>
       </c>
       <c r="B37" t="n">
-        <v>79847</v>
+        <v>74854</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4723,46 +4723,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>492</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528861</v>
+        <v>528873</v>
       </c>
       <c r="R37" t="n">
-        <v>6998604</v>
+        <v>6998728</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4789,11 +4784,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På bark i hålighet vid basen av gammal björkhögstubbe</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4802,48 +4812,23 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122819041</v>
+        <v>122819081</v>
       </c>
       <c r="B38" t="n">
         <v>57478</v>
@@ -4888,10 +4873,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528830</v>
+        <v>528837</v>
       </c>
       <c r="R38" t="n">
-        <v>6998687</v>
+        <v>6998667</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4955,10 +4940,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122820550</v>
+        <v>122822120</v>
       </c>
       <c r="B39" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4971,39 +4956,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528843</v>
+        <v>528832</v>
       </c>
       <c r="R39" t="n">
-        <v>6998785</v>
+        <v>6998742</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5036,11 +5016,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5067,10 +5042,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122820176</v>
+        <v>122819626</v>
       </c>
       <c r="B40" t="n">
-        <v>57631</v>
+        <v>79847</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5083,34 +5058,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528888</v>
+        <v>528907</v>
       </c>
       <c r="R40" t="n">
-        <v>6998720</v>
+        <v>6998684</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5143,6 +5118,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5169,7 +5149,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122819870</v>
+        <v>122823006</v>
       </c>
       <c r="B41" t="n">
         <v>79847</v>
@@ -5202,29 +5182,25 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>bålar</t>
+      <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528902</v>
+        <v>528861</v>
       </c>
       <c r="R41" t="n">
-        <v>6998729</v>
+        <v>6998604</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5251,26 +5227,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>11:29</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>11:29</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På björklåga</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5279,16 +5240,41 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5407,10 +5393,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122820115</v>
+        <v>122819030</v>
       </c>
       <c r="B43" t="n">
-        <v>74855</v>
+        <v>57478</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5423,34 +5409,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528898</v>
+        <v>528811</v>
       </c>
       <c r="R43" t="n">
-        <v>6998773</v>
+        <v>6998709</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5480,24 +5471,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På ved på gammal levande sälg i gammal granskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5512,22 +5493,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122819825</v>
+        <v>122822436</v>
       </c>
       <c r="B44" t="n">
-        <v>74675</v>
+        <v>78503</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5536,41 +5517,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6428</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528895</v>
+        <v>528840</v>
       </c>
       <c r="R44" t="n">
-        <v>6998697</v>
+        <v>6998787</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5597,9 +5578,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På kolad ved på tallstubbe</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5614,22 +5610,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122822290</v>
+        <v>122820232</v>
       </c>
       <c r="B45" t="n">
-        <v>57478</v>
+        <v>77709</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5642,39 +5638,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528824</v>
+        <v>528897</v>
       </c>
       <c r="R45" t="n">
-        <v>6998724</v>
+        <v>6998766</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5704,14 +5695,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en hackspettsbearbetad död gran.</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5722,51 +5723,26 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122819626</v>
+        <v>122819597</v>
       </c>
       <c r="B46" t="n">
-        <v>79847</v>
+        <v>82553</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5779,34 +5755,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528907</v>
+        <v>528869</v>
       </c>
       <c r="R46" t="n">
-        <v>6998684</v>
+        <v>6998649</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5836,14 +5812,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5858,22 +5844,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122820150</v>
+        <v>122819057</v>
       </c>
       <c r="B47" t="n">
-        <v>79022</v>
+        <v>78766</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5882,41 +5868,50 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6459</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528898</v>
+        <v>528830</v>
       </c>
       <c r="R47" t="n">
-        <v>6998770</v>
+        <v>6998611</v>
       </c>
       <c r="S47" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5945,7 +5940,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5955,12 +5950,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>Rikligt på gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5987,10 +5982,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122820570</v>
+        <v>122819987</v>
       </c>
       <c r="B48" t="n">
-        <v>57478</v>
+        <v>79882</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5999,43 +5994,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528842</v>
+        <v>528883</v>
       </c>
       <c r="R48" t="n">
-        <v>6998786</v>
+        <v>6998770</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6065,14 +6055,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6087,22 +6087,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122822781</v>
+        <v>122820739</v>
       </c>
       <c r="B49" t="n">
-        <v>79883</v>
+        <v>77699</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6111,25 +6111,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6464</v>
+        <v>228579</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6139,10 +6139,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528877</v>
+        <v>528795</v>
       </c>
       <c r="R49" t="n">
-        <v>6998634</v>
+        <v>6998791</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6174,7 +6174,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6216,10 +6216,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122822850</v>
+        <v>122819960</v>
       </c>
       <c r="B50" t="n">
-        <v>5489</v>
+        <v>57478</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6232,43 +6232,58 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>101410</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>528902</v>
+        <v>528893</v>
       </c>
       <c r="R50" t="n">
-        <v>6998601</v>
+        <v>6998687</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6303,13 +6318,17 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Rätt så skygg hane av tretåig hackspett i barrnaturskog med mycket höga livsmiljövärden för tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6320,7 +6339,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Gammal flerskiktad naturskogsartad kontinuitetsskog.</t>
+          <t>Kontinuitetsskog med höga naturvärden.</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6338,10 +6357,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122819960</v>
+        <v>122822850</v>
       </c>
       <c r="B51" t="n">
-        <v>57478</v>
+        <v>5489</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6354,58 +6373,43 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>101410</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>528893</v>
+        <v>528902</v>
       </c>
       <c r="R51" t="n">
-        <v>6998687</v>
+        <v>6998601</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6440,17 +6444,13 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Rätt så skygg hane av tretåig hackspett i barrnaturskog med mycket höga livsmiljövärden för tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6461,7 +6461,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Kontinuitetsskog med höga naturvärden.</t>
+          <t>Gammal flerskiktad naturskogsartad kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6612,10 +6612,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122820461</v>
+        <v>122820539</v>
       </c>
       <c r="B53" t="n">
-        <v>57478</v>
+        <v>90944</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6628,47 +6628,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>528854</v>
+        <v>528851</v>
       </c>
       <c r="R53" t="n">
-        <v>6998728</v>
+        <v>6998721</v>
       </c>
       <c r="S53" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6700,11 +6695,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Färska ringhack längs ca 3 m på en granstam i barrnaturskog med revir för tretåig hackspett i höga livsmiljövärden.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6731,12 +6721,12 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6754,10 +6744,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122820539</v>
+        <v>122820461</v>
       </c>
       <c r="B54" t="n">
-        <v>90944</v>
+        <v>57478</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6770,42 +6760,47 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>528851</v>
+        <v>528854</v>
       </c>
       <c r="R54" t="n">
-        <v>6998721</v>
+        <v>6998728</v>
       </c>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6837,6 +6832,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Färska ringhack längs ca 3 m på en granstam i barrnaturskog med revir för tretåig hackspett i höga livsmiljövärden.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6863,12 +6863,12 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>

--- a/artfynd/A 55408-2024 artfynd.xlsx
+++ b/artfynd/A 55408-2024 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122822680</v>
+        <v>122821953</v>
       </c>
       <c r="B3" t="n">
-        <v>78503</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,34 +812,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528888</v>
+        <v>528813</v>
       </c>
       <c r="R3" t="n">
-        <v>6998655</v>
+        <v>6998760</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,24 +874,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På kolad ved på tallhögstubbe</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,22 +896,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122821953</v>
+        <v>122822761</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,39 +924,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528813</v>
+        <v>528879</v>
       </c>
       <c r="R4" t="n">
-        <v>6998760</v>
+        <v>6998619</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,14 +981,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,19 +1013,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122822761</v>
+        <v>122819213</v>
       </c>
       <c r="B5" t="n">
         <v>79847</v>
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528879</v>
+        <v>528849</v>
       </c>
       <c r="R5" t="n">
-        <v>6998619</v>
+        <v>6998626</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På sälglåga</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122819213</v>
+        <v>122822680</v>
       </c>
       <c r="B6" t="n">
-        <v>79847</v>
+        <v>78503</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,21 +1158,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528849</v>
+        <v>528888</v>
       </c>
       <c r="R6" t="n">
-        <v>6998626</v>
+        <v>6998655</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På kolad ved på tallhögstubbe</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,22 +1247,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122820176</v>
+        <v>122820115</v>
       </c>
       <c r="B7" t="n">
-        <v>57631</v>
+        <v>74855</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,34 +1275,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528888</v>
+        <v>528898</v>
       </c>
       <c r="R7" t="n">
-        <v>6998720</v>
+        <v>6998773</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,9 +1332,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På ved på gammal levande sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,22 +1364,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122820115</v>
+        <v>122822781</v>
       </c>
       <c r="B8" t="n">
-        <v>74855</v>
+        <v>79883</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,25 +1388,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>308</v>
+        <v>6464</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1401,10 +1416,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528898</v>
+        <v>528877</v>
       </c>
       <c r="R8" t="n">
-        <v>6998773</v>
+        <v>6998634</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1436,7 +1451,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,12 +1461,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På ved på gammal levande sälg i gammal granskog</t>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,10 +1493,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122822781</v>
+        <v>122820176</v>
       </c>
       <c r="B9" t="n">
-        <v>79883</v>
+        <v>57631</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,38 +1505,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528877</v>
+        <v>528888</v>
       </c>
       <c r="R9" t="n">
-        <v>6998634</v>
+        <v>6998720</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1551,24 +1566,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,12 +1583,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1931,10 +1931,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122819726</v>
+        <v>122820150</v>
       </c>
       <c r="B13" t="n">
-        <v>57589</v>
+        <v>79022</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1947,46 +1947,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103031</v>
+        <v>6459</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528900</v>
+        <v>528898</v>
       </c>
       <c r="R13" t="n">
-        <v>6998697</v>
+        <v>6998770</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2013,9 +2004,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2030,22 +2036,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122820150</v>
+        <v>122819726</v>
       </c>
       <c r="B14" t="n">
-        <v>79022</v>
+        <v>57589</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2058,37 +2064,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6459</v>
+        <v>103031</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528898</v>
+        <v>528900</v>
       </c>
       <c r="R14" t="n">
-        <v>6998770</v>
+        <v>6998697</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2115,24 +2130,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2147,12 +2147,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -3192,10 +3192,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122822228</v>
+        <v>122819543</v>
       </c>
       <c r="B24" t="n">
-        <v>57631</v>
+        <v>74849</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3204,50 +3204,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528846</v>
+        <v>528863</v>
       </c>
       <c r="R24" t="n">
-        <v>6998743</v>
+        <v>6998680</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3274,9 +3265,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På ved på björkhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3291,22 +3297,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122819543</v>
+        <v>122819182</v>
       </c>
       <c r="B25" t="n">
-        <v>74849</v>
+        <v>90940</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3315,41 +3321,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>306</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528863</v>
+        <v>528836</v>
       </c>
       <c r="R25" t="n">
-        <v>6998680</v>
+        <v>6998668</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3376,24 +3382,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På ved på björkhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3408,22 +3399,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122819182</v>
+        <v>122819870</v>
       </c>
       <c r="B26" t="n">
-        <v>90940</v>
+        <v>79847</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3436,37 +3427,46 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528836</v>
+        <v>528902</v>
       </c>
       <c r="R26" t="n">
-        <v>6998668</v>
+        <v>6998729</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3493,9 +3493,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På björklåga</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3510,22 +3525,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122819870</v>
+        <v>122822290</v>
       </c>
       <c r="B27" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3538,46 +3553,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528902</v>
+        <v>528824</v>
       </c>
       <c r="R27" t="n">
-        <v>6998729</v>
+        <v>6998724</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3604,24 +3615,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>11:29</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>11:29</t>
-        </is>
-      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På björklåga</t>
+          <t>Äldre ringhack på en hackspettsbearbetad död gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3632,16 +3633,41 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3770,10 +3796,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122822290</v>
+        <v>122822228</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3786,39 +3812,43 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528824</v>
+        <v>528846</v>
       </c>
       <c r="R29" t="n">
-        <v>6998724</v>
+        <v>6998743</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3853,11 +3883,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på en hackspettsbearbetad död gran.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3866,31 +3891,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -4009,10 +4009,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122820141</v>
+        <v>122822818</v>
       </c>
       <c r="B31" t="n">
-        <v>90944</v>
+        <v>79847</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4025,34 +4025,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528888</v>
+        <v>528919</v>
       </c>
       <c r="R31" t="n">
-        <v>6998720</v>
+        <v>6998644</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4087,6 +4092,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På två gamla grovbarkade sälgar.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4095,6 +4105,31 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4111,10 +4146,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122822818</v>
+        <v>122820550</v>
       </c>
       <c r="B32" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4127,39 +4162,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528919</v>
+        <v>528843</v>
       </c>
       <c r="R32" t="n">
-        <v>6998644</v>
+        <v>6998785</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4196,7 +4231,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På två gamla grovbarkade sälgar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4207,31 +4242,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4248,10 +4258,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122820550</v>
+        <v>122820141</v>
       </c>
       <c r="B33" t="n">
-        <v>57478</v>
+        <v>90944</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4264,39 +4274,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528843</v>
+        <v>528888</v>
       </c>
       <c r="R33" t="n">
-        <v>6998785</v>
+        <v>6998720</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4329,11 +4334,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4828,10 +4828,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122819081</v>
+        <v>122822120</v>
       </c>
       <c r="B38" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4844,39 +4844,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528837</v>
+        <v>528832</v>
       </c>
       <c r="R38" t="n">
-        <v>6998667</v>
+        <v>6998742</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4909,11 +4904,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4940,10 +4930,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122822120</v>
+        <v>122819081</v>
       </c>
       <c r="B39" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4956,34 +4946,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528832</v>
+        <v>528837</v>
       </c>
       <c r="R39" t="n">
-        <v>6998742</v>
+        <v>6998667</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5016,6 +5011,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 55408-2024 artfynd.xlsx
+++ b/artfynd/A 55408-2024 artfynd.xlsx
@@ -1259,10 +1259,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122820115</v>
+        <v>122820176</v>
       </c>
       <c r="B7" t="n">
-        <v>74855</v>
+        <v>57631</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,34 +1275,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>308</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528898</v>
+        <v>528888</v>
       </c>
       <c r="R7" t="n">
-        <v>6998773</v>
+        <v>6998720</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,24 +1332,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På ved på gammal levande sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,22 +1349,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122822781</v>
+        <v>122820115</v>
       </c>
       <c r="B8" t="n">
-        <v>79883</v>
+        <v>74855</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,25 +1373,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1416,10 +1401,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528877</v>
+        <v>528898</v>
       </c>
       <c r="R8" t="n">
-        <v>6998634</v>
+        <v>6998773</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1461,12 +1446,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+          <t>På ved på gammal levande sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1493,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122820176</v>
+        <v>122822781</v>
       </c>
       <c r="B9" t="n">
-        <v>57631</v>
+        <v>79883</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1505,38 +1490,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528888</v>
+        <v>528877</v>
       </c>
       <c r="R9" t="n">
-        <v>6998720</v>
+        <v>6998634</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1566,9 +1551,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,12 +1583,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -2296,10 +2296,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122819010</v>
+        <v>122819677</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2312,39 +2312,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528818</v>
+        <v>528904</v>
       </c>
       <c r="R16" t="n">
-        <v>6998712</v>
+        <v>6998685</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2377,11 +2372,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2408,10 +2398,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122819677</v>
+        <v>122820558</v>
       </c>
       <c r="B17" t="n">
-        <v>79848</v>
+        <v>74863</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2424,37 +2414,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528904</v>
+        <v>528878</v>
       </c>
       <c r="R17" t="n">
-        <v>6998685</v>
+        <v>6998770</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2481,9 +2471,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2498,22 +2503,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122820558</v>
+        <v>122819010</v>
       </c>
       <c r="B18" t="n">
-        <v>74863</v>
+        <v>57478</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2526,37 +2531,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528878</v>
+        <v>528818</v>
       </c>
       <c r="R18" t="n">
-        <v>6998770</v>
+        <v>6998712</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2583,24 +2593,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2615,12 +2615,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2978,10 +2978,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122822075</v>
+        <v>122819522</v>
       </c>
       <c r="B22" t="n">
-        <v>74675</v>
+        <v>57478</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2990,38 +2990,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6428</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528829</v>
+        <v>528843</v>
       </c>
       <c r="R22" t="n">
-        <v>6998747</v>
+        <v>6998616</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3054,6 +3059,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3080,10 +3090,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122819522</v>
+        <v>122822075</v>
       </c>
       <c r="B23" t="n">
-        <v>57478</v>
+        <v>74675</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3092,43 +3102,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6428</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528843</v>
+        <v>528829</v>
       </c>
       <c r="R23" t="n">
-        <v>6998616</v>
+        <v>6998747</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3161,11 +3166,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3192,10 +3192,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122819543</v>
+        <v>122822228</v>
       </c>
       <c r="B24" t="n">
-        <v>74849</v>
+        <v>57631</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3204,41 +3204,50 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>306</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528863</v>
+        <v>528846</v>
       </c>
       <c r="R24" t="n">
-        <v>6998680</v>
+        <v>6998743</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3265,24 +3274,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På ved på björkhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3297,22 +3291,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122819182</v>
+        <v>122819543</v>
       </c>
       <c r="B25" t="n">
-        <v>90940</v>
+        <v>74849</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3321,41 +3315,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528836</v>
+        <v>528863</v>
       </c>
       <c r="R25" t="n">
-        <v>6998668</v>
+        <v>6998680</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3382,9 +3376,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På ved på björkhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3399,22 +3408,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122819870</v>
+        <v>122819182</v>
       </c>
       <c r="B26" t="n">
-        <v>79847</v>
+        <v>90940</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3427,46 +3436,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528902</v>
+        <v>528836</v>
       </c>
       <c r="R26" t="n">
-        <v>6998729</v>
+        <v>6998668</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3493,24 +3493,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>11:29</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>11:29</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På björklåga</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3525,22 +3510,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122822290</v>
+        <v>122819870</v>
       </c>
       <c r="B27" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3553,42 +3538,46 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528824</v>
+        <v>528902</v>
       </c>
       <c r="R27" t="n">
-        <v>6998724</v>
+        <v>6998729</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3615,14 +3604,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en hackspettsbearbetad död gran.</t>
+          <t>På björklåga</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3633,41 +3632,16 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3796,10 +3770,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122822228</v>
+        <v>122822290</v>
       </c>
       <c r="B29" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3812,43 +3786,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528846</v>
+        <v>528824</v>
       </c>
       <c r="R29" t="n">
-        <v>6998743</v>
+        <v>6998724</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3883,6 +3853,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på en hackspettsbearbetad död gran.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3891,6 +3866,31 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -5042,10 +5042,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122819626</v>
+        <v>122822436</v>
       </c>
       <c r="B40" t="n">
-        <v>79847</v>
+        <v>78503</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5058,37 +5058,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528907</v>
+        <v>528840</v>
       </c>
       <c r="R40" t="n">
-        <v>6998684</v>
+        <v>6998787</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5115,14 +5115,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>På kolad ved på tallstubbe</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5137,19 +5147,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122823006</v>
+        <v>122819626</v>
       </c>
       <c r="B41" t="n">
         <v>79847</v>
@@ -5183,24 +5193,19 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528861</v>
+        <v>528907</v>
       </c>
       <c r="R41" t="n">
-        <v>6998604</v>
+        <v>6998684</v>
       </c>
       <c r="S41" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5232,6 +5237,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På björk</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5240,31 +5250,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5281,10 +5266,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122819055</v>
+        <v>122823006</v>
       </c>
       <c r="B42" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5297,27 +5282,27 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5326,13 +5311,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528843</v>
+        <v>528861</v>
       </c>
       <c r="R42" t="n">
-        <v>6998681</v>
+        <v>6998604</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5364,11 +5349,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5377,6 +5357,31 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5393,7 +5398,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122819030</v>
+        <v>122819055</v>
       </c>
       <c r="B43" t="n">
         <v>57478</v>
@@ -5438,10 +5443,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528811</v>
+        <v>528843</v>
       </c>
       <c r="R43" t="n">
-        <v>6998709</v>
+        <v>6998681</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5505,10 +5510,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122822436</v>
+        <v>122819030</v>
       </c>
       <c r="B44" t="n">
-        <v>78503</v>
+        <v>57478</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5521,37 +5526,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528840</v>
+        <v>528811</v>
       </c>
       <c r="R44" t="n">
-        <v>6998787</v>
+        <v>6998709</v>
       </c>
       <c r="S44" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5578,24 +5588,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På kolad ved på tallstubbe</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5610,12 +5610,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>

--- a/artfynd/A 55408-2024 artfynd.xlsx
+++ b/artfynd/A 55408-2024 artfynd.xlsx
@@ -1259,10 +1259,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122820176</v>
+        <v>122820115</v>
       </c>
       <c r="B7" t="n">
-        <v>57631</v>
+        <v>74855</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,34 +1275,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528888</v>
+        <v>528898</v>
       </c>
       <c r="R7" t="n">
-        <v>6998720</v>
+        <v>6998773</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,9 +1332,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På ved på gammal levande sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,22 +1364,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122820115</v>
+        <v>122822781</v>
       </c>
       <c r="B8" t="n">
-        <v>74855</v>
+        <v>79883</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,25 +1388,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>308</v>
+        <v>6464</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1401,10 +1416,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528898</v>
+        <v>528877</v>
       </c>
       <c r="R8" t="n">
-        <v>6998773</v>
+        <v>6998634</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1436,7 +1451,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,12 +1461,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På ved på gammal levande sälg i gammal granskog</t>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,10 +1493,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122822781</v>
+        <v>122820176</v>
       </c>
       <c r="B9" t="n">
-        <v>79883</v>
+        <v>57631</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,38 +1505,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528877</v>
+        <v>528888</v>
       </c>
       <c r="R9" t="n">
-        <v>6998634</v>
+        <v>6998720</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1551,24 +1566,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,12 +1583,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -2296,10 +2296,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122819677</v>
+        <v>122819010</v>
       </c>
       <c r="B16" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2312,34 +2312,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528904</v>
+        <v>528818</v>
       </c>
       <c r="R16" t="n">
-        <v>6998685</v>
+        <v>6998712</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2372,6 +2377,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2398,10 +2408,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122820558</v>
+        <v>122819677</v>
       </c>
       <c r="B17" t="n">
-        <v>74863</v>
+        <v>79848</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2414,37 +2424,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528878</v>
+        <v>528904</v>
       </c>
       <c r="R17" t="n">
-        <v>6998770</v>
+        <v>6998685</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2471,24 +2481,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2503,22 +2498,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122819010</v>
+        <v>122820558</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2531,42 +2526,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528818</v>
+        <v>528878</v>
       </c>
       <c r="R18" t="n">
-        <v>6998712</v>
+        <v>6998770</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2593,14 +2583,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2615,12 +2615,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2978,10 +2978,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122819522</v>
+        <v>122822075</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
+        <v>74675</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2990,43 +2990,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6428</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528843</v>
+        <v>528829</v>
       </c>
       <c r="R22" t="n">
-        <v>6998616</v>
+        <v>6998747</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3059,11 +3054,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3090,10 +3080,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122822075</v>
+        <v>122819522</v>
       </c>
       <c r="B23" t="n">
-        <v>74675</v>
+        <v>57478</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3102,38 +3092,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6428</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528829</v>
+        <v>528843</v>
       </c>
       <c r="R23" t="n">
-        <v>6998747</v>
+        <v>6998616</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3166,6 +3161,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -5042,10 +5042,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122822436</v>
+        <v>122819626</v>
       </c>
       <c r="B40" t="n">
-        <v>78503</v>
+        <v>79847</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5058,37 +5058,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528840</v>
+        <v>528907</v>
       </c>
       <c r="R40" t="n">
-        <v>6998787</v>
+        <v>6998684</v>
       </c>
       <c r="S40" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5115,24 +5115,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På kolad ved på tallstubbe</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5147,19 +5137,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122819626</v>
+        <v>122823006</v>
       </c>
       <c r="B41" t="n">
         <v>79847</v>
@@ -5193,19 +5183,24 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528907</v>
+        <v>528861</v>
       </c>
       <c r="R41" t="n">
-        <v>6998684</v>
+        <v>6998604</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5237,11 +5232,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På björk</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5250,6 +5240,31 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5266,10 +5281,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122823006</v>
+        <v>122819055</v>
       </c>
       <c r="B42" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5282,27 +5297,27 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5311,13 +5326,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528861</v>
+        <v>528843</v>
       </c>
       <c r="R42" t="n">
-        <v>6998604</v>
+        <v>6998681</v>
       </c>
       <c r="S42" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5349,6 +5364,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5357,31 +5377,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5398,7 +5393,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122819055</v>
+        <v>122819030</v>
       </c>
       <c r="B43" t="n">
         <v>57478</v>
@@ -5443,10 +5438,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528843</v>
+        <v>528811</v>
       </c>
       <c r="R43" t="n">
-        <v>6998681</v>
+        <v>6998709</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5510,10 +5505,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122819030</v>
+        <v>122822436</v>
       </c>
       <c r="B44" t="n">
-        <v>57478</v>
+        <v>78503</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5526,42 +5521,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528811</v>
+        <v>528840</v>
       </c>
       <c r="R44" t="n">
-        <v>6998709</v>
+        <v>6998787</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5588,14 +5578,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På kolad ved på tallstubbe</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5610,12 +5610,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>

--- a/artfynd/A 55408-2024 artfynd.xlsx
+++ b/artfynd/A 55408-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122821939</v>
+        <v>122819677</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,46 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528796</v>
+        <v>528904</v>
       </c>
       <c r="R2" t="n">
-        <v>6998791</v>
+        <v>6998685</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,19 +748,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122821953</v>
+        <v>122819608</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,42 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528813</v>
+        <v>528807</v>
       </c>
       <c r="R3" t="n">
-        <v>6998760</v>
+        <v>6998706</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>Relativt ymnigt på många granar. Fertila bålar finns här.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,6 +873,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -908,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122822761</v>
+        <v>122820739</v>
       </c>
       <c r="B4" t="n">
-        <v>79847</v>
+        <v>77699</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,21 +930,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528879</v>
+        <v>528795</v>
       </c>
       <c r="R4" t="n">
-        <v>6998619</v>
+        <v>6998791</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,12 +999,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På sälglåga</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,22 +1019,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122819213</v>
+        <v>122819010</v>
       </c>
       <c r="B5" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,34 +1047,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528849</v>
+        <v>528818</v>
       </c>
       <c r="R5" t="n">
-        <v>6998626</v>
+        <v>6998712</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,24 +1109,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:57</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:57</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,22 +1131,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122822680</v>
+        <v>122820570</v>
       </c>
       <c r="B6" t="n">
-        <v>78503</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,34 +1159,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528888</v>
+        <v>528842</v>
       </c>
       <c r="R6" t="n">
-        <v>6998655</v>
+        <v>6998786</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,24 +1221,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På kolad ved på tallhögstubbe</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,22 +1243,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122820115</v>
+        <v>122819870</v>
       </c>
       <c r="B7" t="n">
-        <v>74855</v>
+        <v>79847</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,37 +1271,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528898</v>
+        <v>528902</v>
       </c>
       <c r="R7" t="n">
-        <v>6998773</v>
+        <v>6998729</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1334,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,12 +1349,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På ved på gammal levande sälg i gammal granskog</t>
+          <t>På björklåga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,22 +1369,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122822781</v>
+        <v>122819697</v>
       </c>
       <c r="B8" t="n">
-        <v>79883</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,38 +1393,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528877</v>
+        <v>528891</v>
       </c>
       <c r="R8" t="n">
-        <v>6998634</v>
+        <v>6998754</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1461,12 +1471,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+          <t>Äldre ringhack på gammal levande tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1493,10 +1503,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122820176</v>
+        <v>122819081</v>
       </c>
       <c r="B9" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1509,34 +1519,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528888</v>
+        <v>528837</v>
       </c>
       <c r="R9" t="n">
-        <v>6998720</v>
+        <v>6998667</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1569,6 +1584,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,10 +1615,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122822259</v>
+        <v>122820232</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>77709</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,42 +1631,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528831</v>
+        <v>528897</v>
       </c>
       <c r="R10" t="n">
-        <v>6998741</v>
+        <v>6998766</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1675,7 +1690,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1685,12 +1700,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1705,22 +1720,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122820570</v>
+        <v>122819182</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>90940</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1733,39 +1748,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528842</v>
+        <v>528836</v>
       </c>
       <c r="R11" t="n">
-        <v>6998786</v>
+        <v>6998668</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1798,11 +1808,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1829,10 +1834,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122822354</v>
+        <v>122822120</v>
       </c>
       <c r="B12" t="n">
-        <v>91116</v>
+        <v>79847</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1845,21 +1850,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1588</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1869,10 +1874,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528838</v>
+        <v>528832</v>
       </c>
       <c r="R12" t="n">
-        <v>6998736</v>
+        <v>6998742</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1931,10 +1936,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122820150</v>
+        <v>122820550</v>
       </c>
       <c r="B13" t="n">
-        <v>79022</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1943,41 +1948,46 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6459</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528898</v>
+        <v>528843</v>
       </c>
       <c r="R13" t="n">
-        <v>6998770</v>
+        <v>6998785</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2004,24 +2014,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2036,22 +2036,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122819726</v>
+        <v>122821953</v>
       </c>
       <c r="B14" t="n">
-        <v>57589</v>
+        <v>57478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2060,20 +2060,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2081,14 +2081,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2097,10 +2093,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528900</v>
+        <v>528813</v>
       </c>
       <c r="R14" t="n">
-        <v>6998697</v>
+        <v>6998760</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2133,6 +2129,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2159,10 +2160,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122819608</v>
+        <v>122819030</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2175,27 +2176,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2204,13 +2205,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528807</v>
+        <v>528811</v>
       </c>
       <c r="R15" t="n">
-        <v>6998706</v>
+        <v>6998709</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2244,7 +2245,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Relativt ymnigt på många granar. Fertila bålar finns här.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2255,31 +2256,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2296,10 +2272,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122819010</v>
+        <v>122822354</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>91116</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2312,39 +2288,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1588</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528818</v>
+        <v>528838</v>
       </c>
       <c r="R16" t="n">
-        <v>6998712</v>
+        <v>6998736</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2377,11 +2348,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2408,10 +2374,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122819677</v>
+        <v>122822373</v>
       </c>
       <c r="B17" t="n">
-        <v>79848</v>
+        <v>90944</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2424,37 +2390,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528904</v>
+        <v>528856</v>
       </c>
       <c r="R17" t="n">
-        <v>6998685</v>
+        <v>6998762</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2481,9 +2447,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2498,12 +2479,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2627,10 +2608,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122819526</v>
+        <v>122822818</v>
       </c>
       <c r="B19" t="n">
-        <v>90944</v>
+        <v>79847</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2643,34 +2624,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528875</v>
+        <v>528919</v>
       </c>
       <c r="R19" t="n">
-        <v>6998691</v>
+        <v>6998644</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2700,24 +2686,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På två gamla grovbarkade sälgar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2728,26 +2704,51 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122819041</v>
+        <v>122819597</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>82553</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2760,39 +2761,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528830</v>
+        <v>528869</v>
       </c>
       <c r="R20" t="n">
-        <v>6998687</v>
+        <v>6998649</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2822,14 +2818,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2844,22 +2850,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122820365</v>
+        <v>122819726</v>
       </c>
       <c r="B21" t="n">
-        <v>57478</v>
+        <v>57589</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2868,20 +2874,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2889,25 +2895,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528893</v>
+        <v>528900</v>
       </c>
       <c r="R21" t="n">
-        <v>6998757</v>
+        <v>6998697</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2934,24 +2944,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På gammal tall, äldre ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2966,22 +2961,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122822075</v>
+        <v>122819526</v>
       </c>
       <c r="B22" t="n">
-        <v>74675</v>
+        <v>90944</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2990,38 +2985,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6428</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528829</v>
+        <v>528875</v>
       </c>
       <c r="R22" t="n">
-        <v>6998747</v>
+        <v>6998691</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3051,9 +3046,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3068,22 +3078,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122819522</v>
+        <v>122820115</v>
       </c>
       <c r="B23" t="n">
-        <v>57478</v>
+        <v>74855</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3096,39 +3106,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528843</v>
+        <v>528898</v>
       </c>
       <c r="R23" t="n">
-        <v>6998616</v>
+        <v>6998773</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3158,14 +3163,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På ved på gammal levande sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3180,22 +3195,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122822228</v>
+        <v>122822761</v>
       </c>
       <c r="B24" t="n">
-        <v>57631</v>
+        <v>79847</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3208,43 +3223,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528846</v>
+        <v>528879</v>
       </c>
       <c r="R24" t="n">
-        <v>6998743</v>
+        <v>6998619</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3274,9 +3280,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3291,22 +3312,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122819543</v>
+        <v>122820150</v>
       </c>
       <c r="B25" t="n">
-        <v>74849</v>
+        <v>79022</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3319,21 +3340,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>306</v>
+        <v>6459</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3343,13 +3364,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528863</v>
+        <v>528898</v>
       </c>
       <c r="R25" t="n">
-        <v>6998680</v>
+        <v>6998770</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3378,7 +3399,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3388,12 +3409,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På ved på björkhögstubbe i gammal granskog</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3420,10 +3441,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122819182</v>
+        <v>122822259</v>
       </c>
       <c r="B26" t="n">
-        <v>90940</v>
+        <v>78766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3436,37 +3457,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528836</v>
+        <v>528831</v>
       </c>
       <c r="R26" t="n">
-        <v>6998668</v>
+        <v>6998741</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3493,9 +3519,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3510,22 +3551,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122819870</v>
+        <v>122820365</v>
       </c>
       <c r="B27" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3538,31 +3579,27 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3571,13 +3608,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528902</v>
+        <v>528893</v>
       </c>
       <c r="R27" t="n">
-        <v>6998729</v>
+        <v>6998757</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3606,7 +3643,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3616,12 +3653,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På björklåga</t>
+          <t>På gammal tall, äldre ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3636,22 +3673,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122819697</v>
+        <v>122820176</v>
       </c>
       <c r="B28" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3664,39 +3701,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528891</v>
+        <v>528888</v>
       </c>
       <c r="R28" t="n">
-        <v>6998754</v>
+        <v>6998720</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3726,24 +3758,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gammal levande tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3758,22 +3775,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122822290</v>
+        <v>122822680</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>78503</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3786,39 +3803,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528824</v>
+        <v>528888</v>
       </c>
       <c r="R29" t="n">
-        <v>6998724</v>
+        <v>6998655</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3848,14 +3860,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en hackspettsbearbetad död gran.</t>
+          <t>På kolad ved på tallhögstubbe</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3866,51 +3888,26 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122819825</v>
+        <v>122819543</v>
       </c>
       <c r="B30" t="n">
-        <v>74675</v>
+        <v>74849</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3923,37 +3920,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6428</v>
+        <v>306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528895</v>
+        <v>528863</v>
       </c>
       <c r="R30" t="n">
-        <v>6998697</v>
+        <v>6998680</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3980,9 +3977,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På ved på björkhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3997,22 +4009,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122822818</v>
+        <v>122819919</v>
       </c>
       <c r="B31" t="n">
-        <v>79847</v>
+        <v>74854</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4021,43 +4033,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>492</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528919</v>
+        <v>528873</v>
       </c>
       <c r="R31" t="n">
-        <v>6998644</v>
+        <v>6998728</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4087,14 +4094,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På två gamla grovbarkade sälgar.</t>
+          <t>På bark i hålighet vid basen av gammal björkhögstubbe</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4105,51 +4122,26 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122820550</v>
+        <v>122819987</v>
       </c>
       <c r="B32" t="n">
-        <v>57478</v>
+        <v>79882</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4158,43 +4150,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528843</v>
+        <v>528883</v>
       </c>
       <c r="R32" t="n">
-        <v>6998785</v>
+        <v>6998770</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4224,14 +4211,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4246,22 +4243,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122820141</v>
+        <v>122819041</v>
       </c>
       <c r="B33" t="n">
-        <v>90944</v>
+        <v>57478</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4274,34 +4271,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528888</v>
+        <v>528830</v>
       </c>
       <c r="R33" t="n">
-        <v>6998720</v>
+        <v>6998687</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4334,6 +4336,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4360,10 +4367,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122822197</v>
+        <v>122819057</v>
       </c>
       <c r="B34" t="n">
-        <v>95903</v>
+        <v>78766</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4376,37 +4383,46 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528847</v>
+        <v>528830</v>
       </c>
       <c r="R34" t="n">
-        <v>6998739</v>
+        <v>6998611</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4433,9 +4449,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Rikligt på gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4450,22 +4481,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122822373</v>
+        <v>122822075</v>
       </c>
       <c r="B35" t="n">
-        <v>90944</v>
+        <v>74675</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4474,41 +4505,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6428</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528856</v>
+        <v>528829</v>
       </c>
       <c r="R35" t="n">
-        <v>6998762</v>
+        <v>6998747</v>
       </c>
       <c r="S35" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4535,24 +4566,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4567,22 +4583,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122819701</v>
+        <v>122819825</v>
       </c>
       <c r="B36" t="n">
-        <v>78766</v>
+        <v>74675</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4591,25 +4607,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4619,13 +4635,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528843</v>
+        <v>528895</v>
       </c>
       <c r="R36" t="n">
-        <v>6998744</v>
+        <v>6998697</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4657,11 +4673,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Rikligt på många granar.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4670,31 +4681,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4711,10 +4697,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122819919</v>
+        <v>122823006</v>
       </c>
       <c r="B37" t="n">
-        <v>74854</v>
+        <v>79847</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4723,41 +4709,46 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>492</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528873</v>
+        <v>528861</v>
       </c>
       <c r="R37" t="n">
-        <v>6998728</v>
+        <v>6998604</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4784,26 +4775,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På bark i hålighet vid basen av gammal björkhögstubbe</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4812,26 +4788,51 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122822120</v>
+        <v>122821939</v>
       </c>
       <c r="B38" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4844,37 +4845,46 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528832</v>
+        <v>528796</v>
       </c>
       <c r="R38" t="n">
-        <v>6998742</v>
+        <v>6998791</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4901,9 +4911,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4918,19 +4938,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122819081</v>
+        <v>122822290</v>
       </c>
       <c r="B39" t="n">
         <v>57478</v>
@@ -4975,10 +4995,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528837</v>
+        <v>528824</v>
       </c>
       <c r="R39" t="n">
-        <v>6998667</v>
+        <v>6998724</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5015,7 +5035,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre ringhack på en hackspettsbearbetad död gran.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5026,6 +5046,31 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5042,10 +5087,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122819626</v>
+        <v>122822436</v>
       </c>
       <c r="B40" t="n">
-        <v>79847</v>
+        <v>78503</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5058,37 +5103,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528907</v>
+        <v>528840</v>
       </c>
       <c r="R40" t="n">
-        <v>6998684</v>
+        <v>6998787</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5115,14 +5160,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>På kolad ved på tallstubbe</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5137,22 +5192,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122823006</v>
+        <v>122819701</v>
       </c>
       <c r="B41" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5165,42 +5220,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528861</v>
+        <v>528843</v>
       </c>
       <c r="R41" t="n">
-        <v>6998604</v>
+        <v>6998744</v>
       </c>
       <c r="S41" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5232,6 +5282,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Rikligt på många granar.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5243,27 +5298,27 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5281,10 +5336,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122819055</v>
+        <v>122822228</v>
       </c>
       <c r="B42" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5297,39 +5352,43 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528843</v>
+        <v>528846</v>
       </c>
       <c r="R42" t="n">
-        <v>6998681</v>
+        <v>6998743</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5362,11 +5421,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5393,10 +5447,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122819030</v>
+        <v>122819626</v>
       </c>
       <c r="B43" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5409,39 +5463,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528811</v>
+        <v>528907</v>
       </c>
       <c r="R43" t="n">
-        <v>6998709</v>
+        <v>6998684</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5478,7 +5527,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5505,10 +5554,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122822436</v>
+        <v>122819055</v>
       </c>
       <c r="B44" t="n">
-        <v>78503</v>
+        <v>57478</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5521,37 +5570,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528840</v>
+        <v>528843</v>
       </c>
       <c r="R44" t="n">
-        <v>6998787</v>
+        <v>6998681</v>
       </c>
       <c r="S44" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5578,24 +5632,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På kolad ved på tallstubbe</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5610,22 +5654,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122820232</v>
+        <v>122819213</v>
       </c>
       <c r="B45" t="n">
-        <v>77709</v>
+        <v>79847</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5638,21 +5682,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>314</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5662,10 +5706,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528897</v>
+        <v>528849</v>
       </c>
       <c r="R45" t="n">
-        <v>6998766</v>
+        <v>6998626</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5697,7 +5741,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5707,12 +5751,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5727,22 +5771,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122819597</v>
+        <v>122822197</v>
       </c>
       <c r="B46" t="n">
-        <v>82553</v>
+        <v>95903</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5755,34 +5799,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1312</v>
+        <v>53</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528869</v>
+        <v>528847</v>
       </c>
       <c r="R46" t="n">
-        <v>6998649</v>
+        <v>6998739</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5812,24 +5856,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5844,22 +5873,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122819057</v>
+        <v>122820141</v>
       </c>
       <c r="B47" t="n">
-        <v>78766</v>
+        <v>90944</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5872,46 +5901,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528830</v>
+        <v>528888</v>
       </c>
       <c r="R47" t="n">
-        <v>6998611</v>
+        <v>6998720</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5938,24 +5958,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>10:51</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>10:51</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Rikligt på gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5970,22 +5975,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122819987</v>
+        <v>122822781</v>
       </c>
       <c r="B48" t="n">
-        <v>79882</v>
+        <v>79883</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5998,21 +6003,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6022,10 +6027,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528883</v>
+        <v>528877</v>
       </c>
       <c r="R48" t="n">
-        <v>6998770</v>
+        <v>6998634</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6057,7 +6062,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6067,12 +6072,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På sälglåga</t>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6087,22 +6092,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122820739</v>
+        <v>122819522</v>
       </c>
       <c r="B49" t="n">
-        <v>77699</v>
+        <v>57478</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6115,34 +6120,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528795</v>
+        <v>528843</v>
       </c>
       <c r="R49" t="n">
-        <v>6998791</v>
+        <v>6998616</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6172,24 +6182,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6204,12 +6204,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6612,10 +6612,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122820539</v>
+        <v>122820461</v>
       </c>
       <c r="B53" t="n">
-        <v>90944</v>
+        <v>57478</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6628,42 +6628,47 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>528851</v>
+        <v>528854</v>
       </c>
       <c r="R53" t="n">
-        <v>6998721</v>
+        <v>6998728</v>
       </c>
       <c r="S53" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6695,6 +6700,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Färska ringhack längs ca 3 m på en granstam i barrnaturskog med revir för tretåig hackspett i höga livsmiljövärden.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6721,12 +6731,12 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6744,10 +6754,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122820461</v>
+        <v>122820539</v>
       </c>
       <c r="B54" t="n">
-        <v>57478</v>
+        <v>90944</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6760,47 +6770,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>528854</v>
+        <v>528851</v>
       </c>
       <c r="R54" t="n">
-        <v>6998728</v>
+        <v>6998721</v>
       </c>
       <c r="S54" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6832,11 +6837,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Färska ringhack längs ca 3 m på en granstam i barrnaturskog med revir för tretåig hackspett i höga livsmiljövärden.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6863,12 +6863,12 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>

--- a/artfynd/A 55408-2024 artfynd.xlsx
+++ b/artfynd/A 55408-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122819677</v>
+        <v>122819608</v>
       </c>
       <c r="B2" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528904</v>
+        <v>528807</v>
       </c>
       <c r="R2" t="n">
-        <v>6998685</v>
+        <v>6998706</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,6 +758,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Relativt ymnigt på många granar. Fertila bålar finns här.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -761,6 +771,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -777,10 +812,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122819608</v>
+        <v>122819677</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,42 +828,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528807</v>
+        <v>528904</v>
       </c>
       <c r="R3" t="n">
-        <v>6998706</v>
+        <v>6998685</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,11 +890,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Relativt ymnigt på många granar. Fertila bålar finns här.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -873,31 +898,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -4950,10 +4950,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122822290</v>
+        <v>122822436</v>
       </c>
       <c r="B39" t="n">
-        <v>57478</v>
+        <v>78503</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4966,42 +4966,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528824</v>
+        <v>528840</v>
       </c>
       <c r="R39" t="n">
-        <v>6998724</v>
+        <v>6998787</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5028,14 +5023,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en hackspettsbearbetad död gran.</t>
+          <t>På kolad ved på tallstubbe</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5046,51 +5051,26 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122822436</v>
+        <v>122822290</v>
       </c>
       <c r="B40" t="n">
-        <v>78503</v>
+        <v>57478</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5103,37 +5083,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528840</v>
+        <v>528824</v>
       </c>
       <c r="R40" t="n">
-        <v>6998787</v>
+        <v>6998724</v>
       </c>
       <c r="S40" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5160,24 +5145,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På kolad ved på tallstubbe</t>
+          <t>Äldre ringhack på en hackspettsbearbetad död gran.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5188,16 +5163,41 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>

--- a/artfynd/A 55408-2024 artfynd.xlsx
+++ b/artfynd/A 55408-2024 artfynd.xlsx
@@ -1255,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122819870</v>
+        <v>122819697</v>
       </c>
       <c r="B7" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,31 +1271,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1304,13 +1300,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528902</v>
+        <v>528891</v>
       </c>
       <c r="R7" t="n">
-        <v>6998729</v>
+        <v>6998754</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1339,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,12 +1345,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På björklåga</t>
+          <t>Äldre ringhack på gammal levande tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1369,19 +1365,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122819697</v>
+        <v>122819081</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1422,14 +1418,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528891</v>
+        <v>528837</v>
       </c>
       <c r="R8" t="n">
-        <v>6998754</v>
+        <v>6998667</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1459,24 +1455,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gammal levande tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,22 +1477,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122819081</v>
+        <v>122819870</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1519,42 +1505,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528837</v>
+        <v>528902</v>
       </c>
       <c r="R9" t="n">
-        <v>6998667</v>
+        <v>6998729</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1581,14 +1571,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På björklåga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,12 +1603,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -4950,10 +4950,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122822436</v>
+        <v>122822290</v>
       </c>
       <c r="B39" t="n">
-        <v>78503</v>
+        <v>57478</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4966,37 +4966,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528840</v>
+        <v>528824</v>
       </c>
       <c r="R39" t="n">
-        <v>6998787</v>
+        <v>6998724</v>
       </c>
       <c r="S39" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5023,24 +5028,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På kolad ved på tallstubbe</t>
+          <t>Äldre ringhack på en hackspettsbearbetad död gran.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5051,26 +5046,51 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122822290</v>
+        <v>122822436</v>
       </c>
       <c r="B40" t="n">
-        <v>57478</v>
+        <v>78503</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5083,42 +5103,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528824</v>
+        <v>528840</v>
       </c>
       <c r="R40" t="n">
-        <v>6998724</v>
+        <v>6998787</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5145,14 +5160,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en hackspettsbearbetad död gran.</t>
+          <t>På kolad ved på tallstubbe</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5163,41 +5188,16 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5885,10 +5885,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122820141</v>
+        <v>122822781</v>
       </c>
       <c r="B47" t="n">
-        <v>90944</v>
+        <v>79883</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5897,38 +5897,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528888</v>
+        <v>528877</v>
       </c>
       <c r="R47" t="n">
-        <v>6998720</v>
+        <v>6998634</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5958,9 +5958,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5975,22 +5990,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122822781</v>
+        <v>122820141</v>
       </c>
       <c r="B48" t="n">
-        <v>79883</v>
+        <v>90944</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5999,38 +6014,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528877</v>
+        <v>528888</v>
       </c>
       <c r="R48" t="n">
-        <v>6998634</v>
+        <v>6998720</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6060,24 +6075,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6092,12 +6092,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>

--- a/artfynd/A 55408-2024 artfynd.xlsx
+++ b/artfynd/A 55408-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122819608</v>
+        <v>122822120</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528807</v>
+        <v>528832</v>
       </c>
       <c r="R2" t="n">
-        <v>6998706</v>
+        <v>6998742</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,11 +753,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Relativt ymnigt på många granar. Fertila bålar finns här.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -771,31 +761,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -812,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122819677</v>
+        <v>122819030</v>
       </c>
       <c r="B3" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528904</v>
+        <v>528811</v>
       </c>
       <c r="R3" t="n">
-        <v>6998685</v>
+        <v>6998709</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122820739</v>
+        <v>122822228</v>
       </c>
       <c r="B4" t="n">
-        <v>77699</v>
+        <v>57631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,34 +905,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228579</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528795</v>
+        <v>528846</v>
       </c>
       <c r="R4" t="n">
-        <v>6998791</v>
+        <v>6998743</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,24 +971,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,22 +988,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122819010</v>
+        <v>122822436</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>78503</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,42 +1016,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528818</v>
+        <v>528840</v>
       </c>
       <c r="R5" t="n">
-        <v>6998712</v>
+        <v>6998787</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1109,14 +1073,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På kolad ved på tallstubbe</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,22 +1105,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122820570</v>
+        <v>122820232</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>77709</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,39 +1133,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528842</v>
+        <v>528897</v>
       </c>
       <c r="R6" t="n">
-        <v>6998786</v>
+        <v>6998766</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,14 +1190,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,22 +1222,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122819697</v>
+        <v>122819677</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,39 +1250,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528891</v>
+        <v>528904</v>
       </c>
       <c r="R7" t="n">
-        <v>6998754</v>
+        <v>6998685</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,24 +1307,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gammal levande tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,22 +1324,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122819081</v>
+        <v>122819870</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,42 +1352,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528837</v>
+        <v>528902</v>
       </c>
       <c r="R8" t="n">
-        <v>6998667</v>
+        <v>6998729</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1455,14 +1418,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På björklåga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,22 +1450,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122819870</v>
+        <v>122819608</v>
       </c>
       <c r="B9" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1505,43 +1478,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528902</v>
+        <v>528807</v>
       </c>
       <c r="R9" t="n">
-        <v>6998729</v>
+        <v>6998706</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1571,24 +1540,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:29</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:29</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På björklåga</t>
+          <t>Relativt ymnigt på många granar. Fertila bålar finns här.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1599,26 +1558,51 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122820232</v>
+        <v>122819522</v>
       </c>
       <c r="B10" t="n">
-        <v>77709</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1631,34 +1615,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>314</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528897</v>
+        <v>528843</v>
       </c>
       <c r="R10" t="n">
-        <v>6998766</v>
+        <v>6998616</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1688,24 +1677,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1720,22 +1699,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122819182</v>
+        <v>122819057</v>
       </c>
       <c r="B11" t="n">
-        <v>90940</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1748,37 +1727,46 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528836</v>
+        <v>528830</v>
       </c>
       <c r="R11" t="n">
-        <v>6998668</v>
+        <v>6998611</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1805,9 +1793,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt på gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1822,22 +1825,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122822120</v>
+        <v>122819526</v>
       </c>
       <c r="B12" t="n">
-        <v>79847</v>
+        <v>90952</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1850,34 +1853,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528832</v>
+        <v>528875</v>
       </c>
       <c r="R12" t="n">
-        <v>6998742</v>
+        <v>6998691</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,9 +1910,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1924,12 +1942,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2160,10 +2178,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122819030</v>
+        <v>122822197</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>95911</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2176,39 +2194,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528811</v>
+        <v>528847</v>
       </c>
       <c r="R15" t="n">
-        <v>6998709</v>
+        <v>6998739</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2241,11 +2254,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2272,10 +2280,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122822354</v>
+        <v>122819597</v>
       </c>
       <c r="B16" t="n">
-        <v>91116</v>
+        <v>82553</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2288,34 +2296,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1588</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528838</v>
+        <v>528869</v>
       </c>
       <c r="R16" t="n">
-        <v>6998736</v>
+        <v>6998649</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2345,9 +2353,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2362,22 +2385,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122822373</v>
+        <v>122822259</v>
       </c>
       <c r="B17" t="n">
-        <v>90944</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2390,37 +2413,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528856</v>
+        <v>528831</v>
       </c>
       <c r="R17" t="n">
-        <v>6998762</v>
+        <v>6998741</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2449,7 +2477,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2459,12 +2487,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2479,22 +2507,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122820558</v>
+        <v>122822761</v>
       </c>
       <c r="B18" t="n">
-        <v>74863</v>
+        <v>79847</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2507,21 +2535,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2531,13 +2559,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528878</v>
+        <v>528879</v>
       </c>
       <c r="R18" t="n">
-        <v>6998770</v>
+        <v>6998619</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2566,7 +2594,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2576,12 +2604,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2608,10 +2636,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122822818</v>
+        <v>122820141</v>
       </c>
       <c r="B19" t="n">
-        <v>79847</v>
+        <v>90952</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2624,39 +2652,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528919</v>
+        <v>528888</v>
       </c>
       <c r="R19" t="n">
-        <v>6998644</v>
+        <v>6998720</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2691,11 +2714,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På två gamla grovbarkade sälgar.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2704,31 +2722,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2745,10 +2738,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122819597</v>
+        <v>122820150</v>
       </c>
       <c r="B20" t="n">
-        <v>82553</v>
+        <v>79022</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2757,25 +2750,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>6459</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2785,13 +2778,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528869</v>
+        <v>528898</v>
       </c>
       <c r="R20" t="n">
-        <v>6998649</v>
+        <v>6998770</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2820,7 +2813,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2830,12 +2823,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2862,10 +2855,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122819726</v>
+        <v>122821939</v>
       </c>
       <c r="B21" t="n">
-        <v>57589</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2874,50 +2867,50 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528900</v>
+        <v>528796</v>
       </c>
       <c r="R21" t="n">
-        <v>6998697</v>
+        <v>6998791</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2944,9 +2937,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2961,22 +2964,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122819526</v>
+        <v>122822075</v>
       </c>
       <c r="B22" t="n">
-        <v>90944</v>
+        <v>74675</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2985,38 +2988,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6428</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528875</v>
+        <v>528829</v>
       </c>
       <c r="R22" t="n">
-        <v>6998691</v>
+        <v>6998747</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3046,24 +3049,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3078,22 +3066,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122820115</v>
+        <v>122819825</v>
       </c>
       <c r="B23" t="n">
-        <v>74855</v>
+        <v>74675</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3102,38 +3090,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>308</v>
+        <v>6428</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528898</v>
+        <v>528895</v>
       </c>
       <c r="R23" t="n">
-        <v>6998773</v>
+        <v>6998697</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3163,24 +3151,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På ved på gammal levande sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3195,22 +3168,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122822761</v>
+        <v>122819726</v>
       </c>
       <c r="B24" t="n">
-        <v>79847</v>
+        <v>57589</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3219,38 +3192,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>103031</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528879</v>
+        <v>528900</v>
       </c>
       <c r="R24" t="n">
-        <v>6998619</v>
+        <v>6998697</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3280,24 +3262,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3312,22 +3279,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122820150</v>
+        <v>122819055</v>
       </c>
       <c r="B25" t="n">
-        <v>79022</v>
+        <v>57478</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3336,41 +3303,46 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6459</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528898</v>
+        <v>528843</v>
       </c>
       <c r="R25" t="n">
-        <v>6998770</v>
+        <v>6998681</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3397,24 +3369,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3429,22 +3391,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122822259</v>
+        <v>122822818</v>
       </c>
       <c r="B26" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3457,42 +3419,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528831</v>
+        <v>528919</v>
       </c>
       <c r="R26" t="n">
-        <v>6998741</v>
+        <v>6998644</v>
       </c>
       <c r="S26" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3519,24 +3481,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På två gamla grovbarkade sälgar.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3547,26 +3499,51 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122820365</v>
+        <v>122819543</v>
       </c>
       <c r="B27" t="n">
-        <v>57478</v>
+        <v>74849</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3575,43 +3552,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528893</v>
+        <v>528863</v>
       </c>
       <c r="R27" t="n">
-        <v>6998757</v>
+        <v>6998680</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3643,7 +3615,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3653,12 +3625,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På gammal tall, äldre ringhack</t>
+          <t>På ved på björkhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3685,10 +3657,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122820176</v>
+        <v>122819041</v>
       </c>
       <c r="B28" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3701,34 +3673,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528888</v>
+        <v>528830</v>
       </c>
       <c r="R28" t="n">
-        <v>6998720</v>
+        <v>6998687</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3761,6 +3738,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3787,10 +3769,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122822680</v>
+        <v>122820570</v>
       </c>
       <c r="B29" t="n">
-        <v>78503</v>
+        <v>57478</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3803,34 +3785,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528888</v>
+        <v>528842</v>
       </c>
       <c r="R29" t="n">
-        <v>6998655</v>
+        <v>6998786</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3860,24 +3847,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På kolad ved på tallhögstubbe</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3892,22 +3869,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122819543</v>
+        <v>122820176</v>
       </c>
       <c r="B30" t="n">
-        <v>74849</v>
+        <v>57631</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3916,41 +3893,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>306</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528863</v>
+        <v>528888</v>
       </c>
       <c r="R30" t="n">
-        <v>6998680</v>
+        <v>6998720</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3977,24 +3954,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På ved på björkhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4009,22 +3971,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122819919</v>
+        <v>122819701</v>
       </c>
       <c r="B31" t="n">
-        <v>74854</v>
+        <v>78766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4033,41 +3995,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>492</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528873</v>
+        <v>528843</v>
       </c>
       <c r="R31" t="n">
-        <v>6998728</v>
+        <v>6998744</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4094,24 +4056,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På bark i hålighet vid basen av gammal björkhögstubbe</t>
+          <t>Rikligt på många granar.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4122,26 +4074,51 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122819987</v>
+        <v>122822680</v>
       </c>
       <c r="B32" t="n">
-        <v>79882</v>
+        <v>78503</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4150,25 +4127,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6463</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4178,10 +4155,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528883</v>
+        <v>528888</v>
       </c>
       <c r="R32" t="n">
-        <v>6998770</v>
+        <v>6998655</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4213,7 +4190,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4223,12 +4200,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På sälglåga</t>
+          <t>På kolad ved på tallhögstubbe</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4243,22 +4220,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122819041</v>
+        <v>122822354</v>
       </c>
       <c r="B33" t="n">
-        <v>57478</v>
+        <v>91124</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4271,39 +4248,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>1588</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528830</v>
+        <v>528838</v>
       </c>
       <c r="R33" t="n">
-        <v>6998687</v>
+        <v>6998736</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4336,11 +4308,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4367,10 +4334,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122819057</v>
+        <v>122820558</v>
       </c>
       <c r="B34" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4383,46 +4350,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528830</v>
+        <v>528878</v>
       </c>
       <c r="R34" t="n">
-        <v>6998611</v>
+        <v>6998770</v>
       </c>
       <c r="S34" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4451,7 +4409,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4461,12 +4419,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Rikligt på gamla granar i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4481,22 +4439,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122822075</v>
+        <v>122819213</v>
       </c>
       <c r="B35" t="n">
-        <v>74675</v>
+        <v>79847</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4505,38 +4463,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6428</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528829</v>
+        <v>528849</v>
       </c>
       <c r="R35" t="n">
-        <v>6998747</v>
+        <v>6998626</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4566,9 +4524,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4583,22 +4556,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122819825</v>
+        <v>122819010</v>
       </c>
       <c r="B36" t="n">
-        <v>74675</v>
+        <v>57478</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4607,38 +4580,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6428</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528895</v>
+        <v>528818</v>
       </c>
       <c r="R36" t="n">
-        <v>6998697</v>
+        <v>6998712</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4671,6 +4649,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4697,10 +4680,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122823006</v>
+        <v>122820739</v>
       </c>
       <c r="B37" t="n">
-        <v>79847</v>
+        <v>77699</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4713,42 +4696,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528861</v>
+        <v>528795</v>
       </c>
       <c r="R37" t="n">
-        <v>6998604</v>
+        <v>6998791</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4775,11 +4753,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4788,51 +4781,26 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122821939</v>
+        <v>122819626</v>
       </c>
       <c r="B38" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4845,46 +4813,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528796</v>
+        <v>528907</v>
       </c>
       <c r="R38" t="n">
-        <v>6998791</v>
+        <v>6998684</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4911,19 +4870,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>12:42</t>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4938,22 +4892,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122822290</v>
+        <v>122819182</v>
       </c>
       <c r="B39" t="n">
-        <v>57478</v>
+        <v>90948</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4966,39 +4920,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528824</v>
+        <v>528836</v>
       </c>
       <c r="R39" t="n">
-        <v>6998724</v>
+        <v>6998668</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5033,11 +4982,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på en hackspettsbearbetad död gran.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5046,31 +4990,6 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5087,10 +5006,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122822436</v>
+        <v>122819081</v>
       </c>
       <c r="B40" t="n">
-        <v>78503</v>
+        <v>57478</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5103,37 +5022,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528840</v>
+        <v>528837</v>
       </c>
       <c r="R40" t="n">
-        <v>6998787</v>
+        <v>6998667</v>
       </c>
       <c r="S40" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5160,24 +5084,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På kolad ved på tallstubbe</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5192,22 +5106,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122819701</v>
+        <v>122820115</v>
       </c>
       <c r="B41" t="n">
-        <v>78766</v>
+        <v>74855</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5220,37 +5134,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528843</v>
+        <v>528898</v>
       </c>
       <c r="R41" t="n">
-        <v>6998744</v>
+        <v>6998773</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5277,14 +5191,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Rikligt på många granar.</t>
+          <t>På ved på gammal levande sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5295,51 +5219,26 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122822228</v>
+        <v>122822781</v>
       </c>
       <c r="B42" t="n">
-        <v>57631</v>
+        <v>79883</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5348,47 +5247,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528846</v>
+        <v>528877</v>
       </c>
       <c r="R42" t="n">
-        <v>6998743</v>
+        <v>6998634</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5418,9 +5308,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5435,19 +5340,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122819626</v>
+        <v>122823006</v>
       </c>
       <c r="B43" t="n">
         <v>79847</v>
@@ -5481,19 +5386,24 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528907</v>
+        <v>528861</v>
       </c>
       <c r="R43" t="n">
-        <v>6998684</v>
+        <v>6998604</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5525,11 +5435,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På björk</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5538,6 +5443,31 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5554,10 +5484,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122819055</v>
+        <v>122819987</v>
       </c>
       <c r="B44" t="n">
-        <v>57478</v>
+        <v>79882</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5566,43 +5496,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528843</v>
+        <v>528883</v>
       </c>
       <c r="R44" t="n">
-        <v>6998681</v>
+        <v>6998770</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5632,14 +5557,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5654,22 +5589,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122819213</v>
+        <v>122822373</v>
       </c>
       <c r="B45" t="n">
-        <v>79847</v>
+        <v>90952</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5682,21 +5617,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5706,13 +5641,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528849</v>
+        <v>528856</v>
       </c>
       <c r="R45" t="n">
-        <v>6998626</v>
+        <v>6998762</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5741,7 +5676,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5751,12 +5686,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5771,22 +5706,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122822197</v>
+        <v>122822290</v>
       </c>
       <c r="B46" t="n">
-        <v>95903</v>
+        <v>57478</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5799,34 +5734,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528847</v>
+        <v>528824</v>
       </c>
       <c r="R46" t="n">
-        <v>6998739</v>
+        <v>6998724</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5861,6 +5801,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på en hackspettsbearbetad död gran.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5869,6 +5814,31 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5885,10 +5855,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122822781</v>
+        <v>122820365</v>
       </c>
       <c r="B47" t="n">
-        <v>79883</v>
+        <v>57478</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5897,41 +5867,46 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528877</v>
+        <v>528893</v>
       </c>
       <c r="R47" t="n">
-        <v>6998634</v>
+        <v>6998757</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5960,7 +5935,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5970,12 +5945,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+          <t>På gammal tall, äldre ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6002,10 +5977,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122820141</v>
+        <v>122819919</v>
       </c>
       <c r="B48" t="n">
-        <v>90944</v>
+        <v>74854</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6014,38 +5989,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>492</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528888</v>
+        <v>528873</v>
       </c>
       <c r="R48" t="n">
-        <v>6998720</v>
+        <v>6998728</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6075,9 +6050,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På bark i hålighet vid basen av gammal björkhögstubbe</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6092,19 +6082,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122819522</v>
+        <v>122819697</v>
       </c>
       <c r="B49" t="n">
         <v>57478</v>
@@ -6145,14 +6135,14 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528843</v>
+        <v>528891</v>
       </c>
       <c r="R49" t="n">
-        <v>6998616</v>
+        <v>6998754</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6182,14 +6172,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre ringhack på gammal levande tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6204,22 +6204,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122819960</v>
+        <v>122822850</v>
       </c>
       <c r="B50" t="n">
-        <v>57478</v>
+        <v>5489</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6232,58 +6232,43 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>101410</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>528893</v>
+        <v>528902</v>
       </c>
       <c r="R50" t="n">
-        <v>6998687</v>
+        <v>6998601</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6318,17 +6303,13 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Rätt så skygg hane av tretåig hackspett i barrnaturskog med mycket höga livsmiljövärden för tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6339,7 +6320,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Kontinuitetsskog med höga naturvärden.</t>
+          <t>Gammal flerskiktad naturskogsartad kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6357,10 +6338,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122822850</v>
+        <v>122819960</v>
       </c>
       <c r="B51" t="n">
-        <v>5489</v>
+        <v>57478</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6373,43 +6354,58 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>101410</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>528902</v>
+        <v>528893</v>
       </c>
       <c r="R51" t="n">
-        <v>6998601</v>
+        <v>6998687</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6444,13 +6440,17 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Rätt så skygg hane av tretåig hackspett i barrnaturskog med mycket höga livsmiljövärden för tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6461,7 +6461,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Gammal flerskiktad naturskogsartad kontinuitetsskog.</t>
+          <t>Kontinuitetsskog med höga naturvärden.</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6612,10 +6612,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122820461</v>
+        <v>122820539</v>
       </c>
       <c r="B53" t="n">
-        <v>57478</v>
+        <v>90952</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6628,47 +6628,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>528854</v>
+        <v>528851</v>
       </c>
       <c r="R53" t="n">
-        <v>6998728</v>
+        <v>6998721</v>
       </c>
       <c r="S53" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6700,11 +6695,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Färska ringhack längs ca 3 m på en granstam i barrnaturskog med revir för tretåig hackspett i höga livsmiljövärden.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6731,12 +6721,12 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6754,10 +6744,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122820539</v>
+        <v>122820461</v>
       </c>
       <c r="B54" t="n">
-        <v>90944</v>
+        <v>57478</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6770,42 +6760,47 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>528851</v>
+        <v>528854</v>
       </c>
       <c r="R54" t="n">
-        <v>6998721</v>
+        <v>6998728</v>
       </c>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6837,6 +6832,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Färska ringhack längs ca 3 m på en granstam i barrnaturskog med revir för tretåig hackspett i höga livsmiljövärden.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6863,12 +6863,12 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>

--- a/artfynd/A 55408-2024 artfynd.xlsx
+++ b/artfynd/A 55408-2024 artfynd.xlsx
@@ -2519,10 +2519,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122822761</v>
+        <v>122820141</v>
       </c>
       <c r="B18" t="n">
-        <v>79847</v>
+        <v>90952</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2535,34 +2535,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528879</v>
+        <v>528888</v>
       </c>
       <c r="R18" t="n">
-        <v>6998619</v>
+        <v>6998720</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2592,24 +2592,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2624,22 +2609,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122820141</v>
+        <v>122822761</v>
       </c>
       <c r="B19" t="n">
-        <v>90952</v>
+        <v>79847</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2652,34 +2637,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528888</v>
+        <v>528879</v>
       </c>
       <c r="R19" t="n">
-        <v>6998720</v>
+        <v>6998619</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2709,9 +2694,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2726,12 +2726,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 55408-2024 artfynd.xlsx
+++ b/artfynd/A 55408-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122822120</v>
+        <v>122820115</v>
       </c>
       <c r="B2" t="n">
-        <v>79847</v>
+        <v>74855</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528832</v>
+        <v>528898</v>
       </c>
       <c r="R2" t="n">
-        <v>6998742</v>
+        <v>6998773</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,9 +748,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På ved på gammal levande sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,19 +780,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122819030</v>
+        <v>122821953</v>
       </c>
       <c r="B3" t="n">
         <v>57478</v>
@@ -818,14 +833,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528811</v>
+        <v>528813</v>
       </c>
       <c r="R3" t="n">
-        <v>6998709</v>
+        <v>6998760</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +877,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122822228</v>
+        <v>122822373</v>
       </c>
       <c r="B4" t="n">
-        <v>57631</v>
+        <v>90952</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,46 +920,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528846</v>
+        <v>528856</v>
       </c>
       <c r="R4" t="n">
-        <v>6998743</v>
+        <v>6998762</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,9 +977,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -988,22 +1009,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122822436</v>
+        <v>122819213</v>
       </c>
       <c r="B5" t="n">
-        <v>78503</v>
+        <v>79847</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1016,21 +1037,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1040,13 +1061,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528840</v>
+        <v>528849</v>
       </c>
       <c r="R5" t="n">
-        <v>6998787</v>
+        <v>6998626</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1075,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1085,12 +1106,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På kolad ved på tallstubbe</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122820232</v>
+        <v>122822197</v>
       </c>
       <c r="B6" t="n">
-        <v>77709</v>
+        <v>95911</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,34 +1154,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>314</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528897</v>
+        <v>528847</v>
       </c>
       <c r="R6" t="n">
-        <v>6998766</v>
+        <v>6998739</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,24 +1211,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,22 +1228,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122819677</v>
+        <v>122819543</v>
       </c>
       <c r="B7" t="n">
-        <v>79848</v>
+        <v>74849</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,41 +1252,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528904</v>
+        <v>528863</v>
       </c>
       <c r="R7" t="n">
-        <v>6998685</v>
+        <v>6998680</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1307,9 +1313,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På ved på björkhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1324,22 +1345,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122819870</v>
+        <v>122822228</v>
       </c>
       <c r="B8" t="n">
-        <v>79847</v>
+        <v>57631</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1352,46 +1373,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528902</v>
+        <v>528846</v>
       </c>
       <c r="R8" t="n">
-        <v>6998729</v>
+        <v>6998743</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1418,24 +1439,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:29</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:29</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På björklåga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1450,22 +1456,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122819608</v>
+        <v>122819919</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>74854</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1474,46 +1480,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528807</v>
+        <v>528873</v>
       </c>
       <c r="R9" t="n">
-        <v>6998706</v>
+        <v>6998728</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1540,14 +1541,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Relativt ymnigt på många granar. Fertila bålar finns här.</t>
+          <t>På bark i hålighet vid basen av gammal björkhögstubbe</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1558,51 +1569,26 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122819522</v>
+        <v>122822761</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1615,39 +1601,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528843</v>
+        <v>528879</v>
       </c>
       <c r="R10" t="n">
-        <v>6998616</v>
+        <v>6998619</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,14 +1658,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1699,22 +1690,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122819057</v>
+        <v>122819030</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1727,46 +1718,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528830</v>
+        <v>528811</v>
       </c>
       <c r="R11" t="n">
-        <v>6998611</v>
+        <v>6998709</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1793,24 +1780,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>10:51</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>10:51</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt på gamla granar i gammal granskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,22 +1802,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122819526</v>
+        <v>122820232</v>
       </c>
       <c r="B12" t="n">
-        <v>90952</v>
+        <v>77709</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1853,21 +1830,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1877,10 +1854,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528875</v>
+        <v>528897</v>
       </c>
       <c r="R12" t="n">
-        <v>6998691</v>
+        <v>6998766</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1912,7 +1889,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1922,12 +1899,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1942,22 +1919,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122820550</v>
+        <v>122822436</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>78503</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1970,42 +1947,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528843</v>
+        <v>528840</v>
       </c>
       <c r="R13" t="n">
-        <v>6998785</v>
+        <v>6998787</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2032,14 +2004,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På kolad ved på tallstubbe</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2054,22 +2036,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122821953</v>
+        <v>122819608</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2082,42 +2064,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528813</v>
+        <v>528807</v>
       </c>
       <c r="R14" t="n">
-        <v>6998760</v>
+        <v>6998706</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2151,7 +2133,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>Relativt ymnigt på många granar. Fertila bålar finns här.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2162,6 +2144,31 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2178,10 +2185,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122822197</v>
+        <v>122819081</v>
       </c>
       <c r="B15" t="n">
-        <v>95911</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2194,34 +2201,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528847</v>
+        <v>528837</v>
       </c>
       <c r="R15" t="n">
-        <v>6998739</v>
+        <v>6998667</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2254,6 +2266,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2280,10 +2297,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122819597</v>
+        <v>122820739</v>
       </c>
       <c r="B16" t="n">
-        <v>82553</v>
+        <v>77699</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2296,21 +2313,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>228579</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2320,10 +2337,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528869</v>
+        <v>528795</v>
       </c>
       <c r="R16" t="n">
-        <v>6998649</v>
+        <v>6998791</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2355,7 +2372,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2365,7 +2382,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2397,10 +2414,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122822259</v>
+        <v>122823006</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2413,42 +2430,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528831</v>
+        <v>528861</v>
       </c>
       <c r="R17" t="n">
-        <v>6998741</v>
+        <v>6998604</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2475,26 +2492,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2503,26 +2505,51 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122820141</v>
+        <v>122819870</v>
       </c>
       <c r="B18" t="n">
-        <v>90952</v>
+        <v>79847</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2535,37 +2562,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528888</v>
+        <v>528902</v>
       </c>
       <c r="R18" t="n">
-        <v>6998720</v>
+        <v>6998729</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2592,9 +2628,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På björklåga</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2609,22 +2660,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122822761</v>
+        <v>122819526</v>
       </c>
       <c r="B19" t="n">
-        <v>79847</v>
+        <v>90952</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2637,21 +2688,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2661,10 +2712,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528879</v>
+        <v>528875</v>
       </c>
       <c r="R19" t="n">
-        <v>6998619</v>
+        <v>6998691</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2696,7 +2747,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2706,12 +2757,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På sälglåga</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2738,10 +2789,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122820150</v>
+        <v>122820558</v>
       </c>
       <c r="B20" t="n">
-        <v>79022</v>
+        <v>74863</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2750,25 +2801,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6459</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2778,13 +2829,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528898</v>
+        <v>528878</v>
       </c>
       <c r="R20" t="n">
         <v>6998770</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2813,7 +2864,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2823,12 +2874,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2843,22 +2894,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122821939</v>
+        <v>122819825</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>74675</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2867,50 +2918,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528796</v>
+        <v>528895</v>
       </c>
       <c r="R21" t="n">
-        <v>6998791</v>
+        <v>6998697</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2937,19 +2979,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>12:42</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2964,22 +2996,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122822075</v>
+        <v>122821939</v>
       </c>
       <c r="B22" t="n">
-        <v>74675</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2988,41 +3020,50 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528829</v>
+        <v>528796</v>
       </c>
       <c r="R22" t="n">
-        <v>6998747</v>
+        <v>6998791</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3049,9 +3090,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3066,22 +3117,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122819825</v>
+        <v>122820570</v>
       </c>
       <c r="B23" t="n">
-        <v>74675</v>
+        <v>57478</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3090,38 +3141,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6428</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528895</v>
+        <v>528842</v>
       </c>
       <c r="R23" t="n">
-        <v>6998697</v>
+        <v>6998786</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3154,6 +3210,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3180,10 +3241,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122819726</v>
+        <v>122819597</v>
       </c>
       <c r="B24" t="n">
-        <v>57589</v>
+        <v>82553</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3192,47 +3253,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103031</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528900</v>
+        <v>528869</v>
       </c>
       <c r="R24" t="n">
-        <v>6998697</v>
+        <v>6998649</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3262,9 +3314,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3279,19 +3346,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122819055</v>
+        <v>122820550</v>
       </c>
       <c r="B25" t="n">
         <v>57478</v>
@@ -3327,19 +3394,19 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
         <v>528843</v>
       </c>
       <c r="R25" t="n">
-        <v>6998681</v>
+        <v>6998785</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3403,10 +3470,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122822818</v>
+        <v>122819697</v>
       </c>
       <c r="B26" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3419,39 +3486,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528919</v>
+        <v>528891</v>
       </c>
       <c r="R26" t="n">
-        <v>6998644</v>
+        <v>6998754</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3481,14 +3548,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På två gamla grovbarkade sälgar.</t>
+          <t>Äldre ringhack på gammal levande tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3499,51 +3576,26 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122819543</v>
+        <v>122822075</v>
       </c>
       <c r="B27" t="n">
-        <v>74849</v>
+        <v>74675</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3556,37 +3608,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>306</v>
+        <v>6428</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528863</v>
+        <v>528829</v>
       </c>
       <c r="R27" t="n">
-        <v>6998680</v>
+        <v>6998747</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3613,24 +3665,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På ved på björkhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3645,22 +3682,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122819041</v>
+        <v>122819701</v>
       </c>
       <c r="B28" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3673,42 +3710,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528830</v>
+        <v>528843</v>
       </c>
       <c r="R28" t="n">
-        <v>6998687</v>
+        <v>6998744</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3742,7 +3774,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt på många granar.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3753,6 +3785,31 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3769,10 +3826,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122820570</v>
+        <v>122820141</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>90952</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3785,39 +3842,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528842</v>
+        <v>528888</v>
       </c>
       <c r="R29" t="n">
-        <v>6998786</v>
+        <v>6998720</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3850,11 +3902,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3881,10 +3928,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122820176</v>
+        <v>122820150</v>
       </c>
       <c r="B30" t="n">
-        <v>57631</v>
+        <v>79022</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3893,41 +3940,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>6459</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528888</v>
+        <v>528898</v>
       </c>
       <c r="R30" t="n">
-        <v>6998720</v>
+        <v>6998770</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3954,9 +4001,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3971,22 +4033,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122819701</v>
+        <v>122820365</v>
       </c>
       <c r="B31" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3999,37 +4061,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528843</v>
+        <v>528893</v>
       </c>
       <c r="R31" t="n">
-        <v>6998744</v>
+        <v>6998757</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4056,14 +4123,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Rikligt på många granar.</t>
+          <t>På gammal tall, äldre ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4074,51 +4151,26 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122822680</v>
+        <v>122820176</v>
       </c>
       <c r="B32" t="n">
-        <v>78503</v>
+        <v>57631</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4131,34 +4183,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
         <v>528888</v>
       </c>
       <c r="R32" t="n">
-        <v>6998655</v>
+        <v>6998720</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4188,24 +4240,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På kolad ved på tallhögstubbe</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4220,22 +4257,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122822354</v>
+        <v>122819057</v>
       </c>
       <c r="B33" t="n">
-        <v>91124</v>
+        <v>78766</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4248,37 +4285,46 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1588</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528838</v>
+        <v>528830</v>
       </c>
       <c r="R33" t="n">
-        <v>6998736</v>
+        <v>6998611</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4305,9 +4351,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rikligt på gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4322,22 +4383,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122820558</v>
+        <v>122819987</v>
       </c>
       <c r="B34" t="n">
-        <v>74863</v>
+        <v>79882</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4346,25 +4407,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>6463</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4374,13 +4435,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528878</v>
+        <v>528883</v>
       </c>
       <c r="R34" t="n">
         <v>6998770</v>
       </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4409,7 +4470,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4419,12 +4480,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4444,17 +4505,17 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122819213</v>
+        <v>122819726</v>
       </c>
       <c r="B35" t="n">
-        <v>79847</v>
+        <v>57589</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4463,38 +4524,47 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>103031</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528849</v>
+        <v>528900</v>
       </c>
       <c r="R35" t="n">
-        <v>6998626</v>
+        <v>6998697</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4524,24 +4594,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>10:57</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>10:57</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4556,22 +4611,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122819010</v>
+        <v>122819182</v>
       </c>
       <c r="B36" t="n">
-        <v>57478</v>
+        <v>90948</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4584,39 +4639,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528818</v>
+        <v>528836</v>
       </c>
       <c r="R36" t="n">
-        <v>6998712</v>
+        <v>6998668</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4649,11 +4699,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4680,10 +4725,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122820739</v>
+        <v>122819626</v>
       </c>
       <c r="B37" t="n">
-        <v>77699</v>
+        <v>79847</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4696,34 +4741,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528795</v>
+        <v>528907</v>
       </c>
       <c r="R37" t="n">
-        <v>6998791</v>
+        <v>6998684</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4753,24 +4798,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4785,22 +4820,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122819626</v>
+        <v>122819677</v>
       </c>
       <c r="B38" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4813,21 +4848,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4837,10 +4872,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528907</v>
+        <v>528904</v>
       </c>
       <c r="R38" t="n">
-        <v>6998684</v>
+        <v>6998685</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4873,11 +4908,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4904,10 +4934,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122819182</v>
+        <v>122822818</v>
       </c>
       <c r="B39" t="n">
-        <v>90948</v>
+        <v>79847</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4920,34 +4950,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528836</v>
+        <v>528919</v>
       </c>
       <c r="R39" t="n">
-        <v>6998668</v>
+        <v>6998644</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4982,6 +5017,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På två gamla grovbarkade sälgar.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4990,6 +5030,31 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5006,10 +5071,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122819081</v>
+        <v>122822354</v>
       </c>
       <c r="B40" t="n">
-        <v>57478</v>
+        <v>91124</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5022,39 +5087,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>1588</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528837</v>
+        <v>528838</v>
       </c>
       <c r="R40" t="n">
-        <v>6998667</v>
+        <v>6998736</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5087,11 +5147,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5118,10 +5173,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122820115</v>
+        <v>122822120</v>
       </c>
       <c r="B41" t="n">
-        <v>74855</v>
+        <v>79847</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5134,34 +5189,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528898</v>
+        <v>528832</v>
       </c>
       <c r="R41" t="n">
-        <v>6998773</v>
+        <v>6998742</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5191,24 +5246,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På ved på gammal levande sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5223,22 +5263,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122822781</v>
+        <v>122822680</v>
       </c>
       <c r="B42" t="n">
-        <v>79883</v>
+        <v>78503</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5247,25 +5287,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6464</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5275,10 +5315,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528877</v>
+        <v>528888</v>
       </c>
       <c r="R42" t="n">
-        <v>6998634</v>
+        <v>6998655</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5310,7 +5350,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5320,12 +5360,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+          <t>På kolad ved på tallhögstubbe</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5345,17 +5385,17 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122823006</v>
+        <v>122822259</v>
       </c>
       <c r="B43" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5368,42 +5408,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528861</v>
+        <v>528831</v>
       </c>
       <c r="R43" t="n">
-        <v>6998604</v>
+        <v>6998741</v>
       </c>
       <c r="S43" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5430,11 +5470,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5443,51 +5498,26 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122819987</v>
+        <v>122819522</v>
       </c>
       <c r="B44" t="n">
-        <v>79882</v>
+        <v>57478</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5496,38 +5526,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528883</v>
+        <v>528843</v>
       </c>
       <c r="R44" t="n">
-        <v>6998770</v>
+        <v>6998616</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5557,24 +5592,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På sälglåga</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5589,22 +5614,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122822373</v>
+        <v>122822781</v>
       </c>
       <c r="B45" t="n">
-        <v>90952</v>
+        <v>79883</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5613,25 +5638,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5641,13 +5666,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528856</v>
+        <v>528877</v>
       </c>
       <c r="R45" t="n">
-        <v>6998762</v>
+        <v>6998634</v>
       </c>
       <c r="S45" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5676,7 +5701,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5686,12 +5711,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5711,14 +5736,14 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122822290</v>
+        <v>122819041</v>
       </c>
       <c r="B46" t="n">
         <v>57478</v>
@@ -5763,10 +5788,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528824</v>
+        <v>528830</v>
       </c>
       <c r="R46" t="n">
-        <v>6998724</v>
+        <v>6998687</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5803,7 +5828,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en hackspettsbearbetad död gran.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5814,31 +5839,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5855,7 +5855,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122820365</v>
+        <v>122819010</v>
       </c>
       <c r="B47" t="n">
         <v>57478</v>
@@ -5896,17 +5896,17 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528893</v>
+        <v>528818</v>
       </c>
       <c r="R47" t="n">
-        <v>6998757</v>
+        <v>6998712</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5933,24 +5933,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På gammal tall, äldre ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5965,22 +5955,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122819919</v>
+        <v>122822290</v>
       </c>
       <c r="B48" t="n">
-        <v>74854</v>
+        <v>57478</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5989,38 +5979,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528873</v>
+        <v>528824</v>
       </c>
       <c r="R48" t="n">
-        <v>6998728</v>
+        <v>6998724</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6050,24 +6045,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På bark i hålighet vid basen av gammal björkhögstubbe</t>
+          <t>Äldre ringhack på en hackspettsbearbetad död gran.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6078,23 +6063,48 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122819697</v>
+        <v>122819055</v>
       </c>
       <c r="B49" t="n">
         <v>57478</v>
@@ -6135,14 +6145,14 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528891</v>
+        <v>528843</v>
       </c>
       <c r="R49" t="n">
-        <v>6998754</v>
+        <v>6998681</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6172,24 +6182,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gammal levande tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6204,22 +6204,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122822850</v>
+        <v>122820024</v>
       </c>
       <c r="B50" t="n">
-        <v>5489</v>
+        <v>57589</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6228,47 +6228,54 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>101410</v>
+        <v>103031</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>528902</v>
+        <v>528891</v>
       </c>
       <c r="R50" t="n">
-        <v>6998601</v>
+        <v>6998690</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6303,13 +6310,17 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Tre lavskrikor i naturskog med höga naturvärden.</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6320,7 +6331,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Gammal flerskiktad naturskogsartad kontinuitetsskog.</t>
+          <t>Flerskiktad hänglavsrik barrnaturskog med höga naturvärden.</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6338,7 +6349,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122819960</v>
+        <v>122819915</v>
       </c>
       <c r="B51" t="n">
         <v>57478</v>
@@ -6373,22 +6384,18 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -6442,7 +6449,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Rätt så skygg hane av tretåig hackspett i barrnaturskog med mycket höga livsmiljövärden för tretåig hackspett.</t>
+          <t>Födosökande hona och hane av tretåig hackspett i skog med höga till mycket höga livsmiljövärden.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6461,7 +6468,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Kontinuitetsskog med höga naturvärden.</t>
+          <t>Flerskiktad barrnaturskog med höga naturvärden.</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6479,10 +6486,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122820024</v>
+        <v>122822850</v>
       </c>
       <c r="B52" t="n">
-        <v>57589</v>
+        <v>5489</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6491,54 +6498,47 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103031</v>
+        <v>101410</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>528891</v>
+        <v>528902</v>
       </c>
       <c r="R52" t="n">
-        <v>6998690</v>
+        <v>6998601</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6573,17 +6573,13 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Tre lavskrikor i naturskog med höga naturvärden.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6594,7 +6590,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Flerskiktad hänglavsrik barrnaturskog med höga naturvärden.</t>
+          <t>Gammal flerskiktad naturskogsartad kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>

--- a/artfynd/A 55408-2024 artfynd.xlsx
+++ b/artfynd/A 55408-2024 artfynd.xlsx
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122822373</v>
+        <v>122819213</v>
       </c>
       <c r="B4" t="n">
-        <v>90952</v>
+        <v>79847</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,21 +920,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,13 +944,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528856</v>
+        <v>528849</v>
       </c>
       <c r="R4" t="n">
-        <v>6998762</v>
+        <v>6998626</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,22 +1009,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122819213</v>
+        <v>122822373</v>
       </c>
       <c r="B5" t="n">
-        <v>79847</v>
+        <v>90952</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,21 +1037,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528849</v>
+        <v>528856</v>
       </c>
       <c r="R5" t="n">
-        <v>6998626</v>
+        <v>6998762</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,12 +1126,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -4395,10 +4395,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122819987</v>
+        <v>122819726</v>
       </c>
       <c r="B34" t="n">
-        <v>79882</v>
+        <v>57589</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4411,34 +4411,43 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6463</v>
+        <v>103031</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528883</v>
+        <v>528900</v>
       </c>
       <c r="R34" t="n">
-        <v>6998770</v>
+        <v>6998697</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4468,24 +4477,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4500,22 +4494,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122819726</v>
+        <v>122819987</v>
       </c>
       <c r="B35" t="n">
-        <v>57589</v>
+        <v>79882</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4528,43 +4522,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103031</v>
+        <v>6463</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528900</v>
+        <v>528883</v>
       </c>
       <c r="R35" t="n">
-        <v>6998697</v>
+        <v>6998770</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4594,9 +4579,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4611,12 +4611,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -5071,10 +5071,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122822354</v>
+        <v>122822120</v>
       </c>
       <c r="B40" t="n">
-        <v>91124</v>
+        <v>79847</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5087,21 +5087,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1588</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5111,10 +5111,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528838</v>
+        <v>528832</v>
       </c>
       <c r="R40" t="n">
-        <v>6998736</v>
+        <v>6998742</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5173,10 +5173,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122822120</v>
+        <v>122822354</v>
       </c>
       <c r="B41" t="n">
-        <v>79847</v>
+        <v>91124</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5189,21 +5189,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>1588</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5213,10 +5213,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528832</v>
+        <v>528838</v>
       </c>
       <c r="R41" t="n">
-        <v>6998742</v>
+        <v>6998736</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 55408-2024 artfynd.xlsx
+++ b/artfynd/A 55408-2024 artfynd.xlsx
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122819213</v>
+        <v>122822373</v>
       </c>
       <c r="B4" t="n">
-        <v>79847</v>
+        <v>90952</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,21 +920,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,13 +944,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528849</v>
+        <v>528856</v>
       </c>
       <c r="R4" t="n">
-        <v>6998626</v>
+        <v>6998762</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,22 +1009,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122822373</v>
+        <v>122819213</v>
       </c>
       <c r="B5" t="n">
-        <v>90952</v>
+        <v>79847</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,21 +1037,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528856</v>
+        <v>528849</v>
       </c>
       <c r="R5" t="n">
-        <v>6998762</v>
+        <v>6998626</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,12 +1126,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -2185,10 +2185,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122819081</v>
+        <v>122823006</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2201,27 +2201,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2230,13 +2230,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528837</v>
+        <v>528861</v>
       </c>
       <c r="R15" t="n">
-        <v>6998667</v>
+        <v>6998604</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2268,11 +2268,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2281,6 +2276,31 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2297,10 +2317,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122820739</v>
+        <v>122819870</v>
       </c>
       <c r="B16" t="n">
-        <v>77699</v>
+        <v>79847</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2313,37 +2333,46 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528795</v>
+        <v>528902</v>
       </c>
       <c r="R16" t="n">
-        <v>6998791</v>
+        <v>6998729</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2372,7 +2401,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2382,12 +2411,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På björklåga</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2402,22 +2431,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122823006</v>
+        <v>122819081</v>
       </c>
       <c r="B17" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2430,27 +2459,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2459,13 +2488,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528861</v>
+        <v>528837</v>
       </c>
       <c r="R17" t="n">
-        <v>6998604</v>
+        <v>6998667</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2497,6 +2526,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2505,31 +2539,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2546,10 +2555,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122819870</v>
+        <v>122820739</v>
       </c>
       <c r="B18" t="n">
-        <v>79847</v>
+        <v>77699</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2562,46 +2571,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528902</v>
+        <v>528795</v>
       </c>
       <c r="R18" t="n">
-        <v>6998729</v>
+        <v>6998791</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2640,12 +2640,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På björklåga</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2660,12 +2660,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -3694,10 +3694,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122819701</v>
+        <v>122820141</v>
       </c>
       <c r="B28" t="n">
-        <v>78766</v>
+        <v>90952</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3710,21 +3710,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3734,13 +3734,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528843</v>
+        <v>528888</v>
       </c>
       <c r="R28" t="n">
-        <v>6998744</v>
+        <v>6998720</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3772,11 +3772,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt på många granar.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3785,31 +3780,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3826,10 +3796,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122820141</v>
+        <v>122820150</v>
       </c>
       <c r="B29" t="n">
-        <v>90952</v>
+        <v>79022</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3838,41 +3808,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6459</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528888</v>
+        <v>528898</v>
       </c>
       <c r="R29" t="n">
-        <v>6998720</v>
+        <v>6998770</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3899,9 +3869,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3916,22 +3901,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122820150</v>
+        <v>122820365</v>
       </c>
       <c r="B30" t="n">
-        <v>79022</v>
+        <v>57478</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3940,41 +3925,46 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6459</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528898</v>
+        <v>528893</v>
       </c>
       <c r="R30" t="n">
-        <v>6998770</v>
+        <v>6998757</v>
       </c>
       <c r="S30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4003,7 +3993,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4013,12 +4003,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>På gammal tall, äldre ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4045,10 +4035,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122820365</v>
+        <v>122820176</v>
       </c>
       <c r="B31" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4061,42 +4051,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528893</v>
+        <v>528888</v>
       </c>
       <c r="R31" t="n">
-        <v>6998757</v>
+        <v>6998720</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4123,24 +4108,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På gammal tall, äldre ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4155,22 +4125,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122820176</v>
+        <v>122819701</v>
       </c>
       <c r="B32" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4183,37 +4153,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528888</v>
+        <v>528843</v>
       </c>
       <c r="R32" t="n">
-        <v>6998720</v>
+        <v>6998744</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4245,6 +4215,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Rikligt på många granar.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4253,6 +4228,31 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4623,10 +4623,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122819182</v>
+        <v>122819626</v>
       </c>
       <c r="B36" t="n">
-        <v>90948</v>
+        <v>79847</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4639,21 +4639,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4663,10 +4663,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528836</v>
+        <v>528907</v>
       </c>
       <c r="R36" t="n">
-        <v>6998668</v>
+        <v>6998684</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4699,6 +4699,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4725,10 +4730,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122819626</v>
+        <v>122819677</v>
       </c>
       <c r="B37" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4741,21 +4746,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4765,10 +4770,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528907</v>
+        <v>528904</v>
       </c>
       <c r="R37" t="n">
-        <v>6998684</v>
+        <v>6998685</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4801,11 +4806,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4832,10 +4832,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122819677</v>
+        <v>122819182</v>
       </c>
       <c r="B38" t="n">
-        <v>79848</v>
+        <v>90948</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4848,21 +4848,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4872,10 +4872,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528904</v>
+        <v>528836</v>
       </c>
       <c r="R38" t="n">
-        <v>6998685</v>
+        <v>6998668</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5071,10 +5071,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122822120</v>
+        <v>122822354</v>
       </c>
       <c r="B40" t="n">
-        <v>79847</v>
+        <v>91124</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5087,21 +5087,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>1588</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5111,10 +5111,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528832</v>
+        <v>528838</v>
       </c>
       <c r="R40" t="n">
-        <v>6998742</v>
+        <v>6998736</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5173,10 +5173,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122822354</v>
+        <v>122822120</v>
       </c>
       <c r="B41" t="n">
-        <v>91124</v>
+        <v>79847</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5189,21 +5189,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1588</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5213,10 +5213,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528838</v>
+        <v>528832</v>
       </c>
       <c r="R41" t="n">
-        <v>6998736</v>
+        <v>6998742</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 55408-2024 artfynd.xlsx
+++ b/artfynd/A 55408-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122820115</v>
+        <v>122820365</v>
       </c>
       <c r="B2" t="n">
-        <v>74855</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528898</v>
+        <v>528893</v>
       </c>
       <c r="R2" t="n">
-        <v>6998773</v>
+        <v>6998757</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På ved på gammal levande sälg i gammal granskog</t>
+          <t>På gammal tall, äldre ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -904,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122822373</v>
+        <v>122819825</v>
       </c>
       <c r="B4" t="n">
-        <v>90952</v>
+        <v>74675</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,41 +921,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6428</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528856</v>
+        <v>528895</v>
       </c>
       <c r="R4" t="n">
-        <v>6998762</v>
+        <v>6998697</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,24 +982,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,22 +999,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122819213</v>
+        <v>122819182</v>
       </c>
       <c r="B5" t="n">
-        <v>79847</v>
+        <v>90948</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,34 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528849</v>
+        <v>528836</v>
       </c>
       <c r="R5" t="n">
-        <v>6998626</v>
+        <v>6998668</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,24 +1084,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:57</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:57</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,22 +1101,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122822197</v>
+        <v>122820115</v>
       </c>
       <c r="B6" t="n">
-        <v>95911</v>
+        <v>74855</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,34 +1129,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528847</v>
+        <v>528898</v>
       </c>
       <c r="R6" t="n">
-        <v>6998739</v>
+        <v>6998773</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,9 +1186,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På ved på gammal levande sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,22 +1218,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122819543</v>
+        <v>122821939</v>
       </c>
       <c r="B7" t="n">
-        <v>74849</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1252,41 +1242,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>306</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528863</v>
+        <v>528796</v>
       </c>
       <c r="R7" t="n">
-        <v>6998680</v>
+        <v>6998791</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1315,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,12 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På ved på björkhögstubbe i gammal granskog</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,22 +1339,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122822228</v>
+        <v>122819608</v>
       </c>
       <c r="B8" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,46 +1367,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528846</v>
+        <v>528807</v>
       </c>
       <c r="R8" t="n">
-        <v>6998743</v>
+        <v>6998706</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1444,6 +1434,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Relativt ymnigt på många granar. Fertila bålar finns här.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1452,6 +1447,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1468,10 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122819919</v>
+        <v>122822259</v>
       </c>
       <c r="B9" t="n">
-        <v>74854</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,41 +1500,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>492</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528873</v>
+        <v>528831</v>
       </c>
       <c r="R9" t="n">
-        <v>6998728</v>
+        <v>6998741</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1543,7 +1568,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1553,12 +1578,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På bark i hålighet vid basen av gammal björkhögstubbe</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1573,22 +1598,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122822761</v>
+        <v>122820141</v>
       </c>
       <c r="B10" t="n">
-        <v>79847</v>
+        <v>90952</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1601,34 +1626,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528879</v>
+        <v>528888</v>
       </c>
       <c r="R10" t="n">
-        <v>6998619</v>
+        <v>6998720</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1658,24 +1683,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1690,22 +1700,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122819030</v>
+        <v>122820150</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>79022</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,46 +1724,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6459</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528811</v>
+        <v>528898</v>
       </c>
       <c r="R11" t="n">
-        <v>6998709</v>
+        <v>6998770</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1780,14 +1785,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1802,22 +1817,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122820232</v>
+        <v>122822354</v>
       </c>
       <c r="B12" t="n">
-        <v>77709</v>
+        <v>91124</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1830,34 +1845,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>314</v>
+        <v>1588</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528897</v>
+        <v>528838</v>
       </c>
       <c r="R12" t="n">
-        <v>6998766</v>
+        <v>6998736</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1887,24 +1902,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1919,12 +1919,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2048,10 +2048,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122819608</v>
+        <v>122819526</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>90952</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2064,42 +2064,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528807</v>
+        <v>528875</v>
       </c>
       <c r="R14" t="n">
-        <v>6998706</v>
+        <v>6998691</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2126,14 +2121,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Relativt ymnigt på många granar. Fertila bålar finns här.</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2144,51 +2149,26 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122823006</v>
+        <v>122819726</v>
       </c>
       <c r="B15" t="n">
-        <v>79847</v>
+        <v>57589</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2197,46 +2177,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>103031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med soral</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528861</v>
+        <v>528900</v>
       </c>
       <c r="R15" t="n">
-        <v>6998604</v>
+        <v>6998697</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2276,31 +2260,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2317,7 +2276,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122819870</v>
+        <v>122819213</v>
       </c>
       <c r="B16" t="n">
         <v>79847</v>
@@ -2350,29 +2309,20 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528902</v>
+        <v>528849</v>
       </c>
       <c r="R16" t="n">
-        <v>6998729</v>
+        <v>6998626</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2401,7 +2351,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2411,12 +2361,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På björklåga</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2443,7 +2393,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122819081</v>
+        <v>122819697</v>
       </c>
       <c r="B17" t="n">
         <v>57478</v>
@@ -2484,14 +2434,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528837</v>
+        <v>528891</v>
       </c>
       <c r="R17" t="n">
-        <v>6998667</v>
+        <v>6998754</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2521,14 +2471,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre ringhack på gammal levande tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2543,22 +2503,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122820739</v>
+        <v>122822781</v>
       </c>
       <c r="B18" t="n">
-        <v>77699</v>
+        <v>79883</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2567,25 +2527,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228579</v>
+        <v>6464</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2595,10 +2555,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528795</v>
+        <v>528877</v>
       </c>
       <c r="R18" t="n">
-        <v>6998791</v>
+        <v>6998634</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2630,7 +2590,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2640,12 +2600,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2672,10 +2632,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122819526</v>
+        <v>122822075</v>
       </c>
       <c r="B19" t="n">
-        <v>90952</v>
+        <v>74675</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2684,38 +2644,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6428</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528875</v>
+        <v>528829</v>
       </c>
       <c r="R19" t="n">
-        <v>6998691</v>
+        <v>6998747</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2745,24 +2705,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2777,22 +2722,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122820558</v>
+        <v>122819597</v>
       </c>
       <c r="B20" t="n">
-        <v>74863</v>
+        <v>82553</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2805,21 +2750,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2829,13 +2774,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528878</v>
+        <v>528869</v>
       </c>
       <c r="R20" t="n">
-        <v>6998770</v>
+        <v>6998649</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2864,7 +2809,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2874,12 +2819,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2894,22 +2839,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122819825</v>
+        <v>122820558</v>
       </c>
       <c r="B21" t="n">
-        <v>74675</v>
+        <v>74863</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2918,41 +2863,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6428</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528895</v>
+        <v>528878</v>
       </c>
       <c r="R21" t="n">
-        <v>6998697</v>
+        <v>6998770</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2979,9 +2924,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2996,22 +2956,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122821939</v>
+        <v>122819626</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3024,46 +2984,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528796</v>
+        <v>528907</v>
       </c>
       <c r="R22" t="n">
-        <v>6998791</v>
+        <v>6998684</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3090,19 +3041,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>12:42</t>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3117,22 +3063,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122820570</v>
+        <v>122819870</v>
       </c>
       <c r="B23" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3145,42 +3091,46 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528842</v>
+        <v>528902</v>
       </c>
       <c r="R23" t="n">
-        <v>6998786</v>
+        <v>6998729</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3207,14 +3157,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På björklåga</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3229,22 +3189,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122819597</v>
+        <v>122820176</v>
       </c>
       <c r="B24" t="n">
-        <v>82553</v>
+        <v>57631</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3257,34 +3217,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528869</v>
+        <v>528888</v>
       </c>
       <c r="R24" t="n">
-        <v>6998649</v>
+        <v>6998720</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3314,24 +3274,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3346,22 +3291,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122820550</v>
+        <v>122820739</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
+        <v>77699</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3374,39 +3319,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528843</v>
+        <v>528795</v>
       </c>
       <c r="R25" t="n">
-        <v>6998785</v>
+        <v>6998791</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3436,14 +3376,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3458,19 +3408,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122819697</v>
+        <v>122819041</v>
       </c>
       <c r="B26" t="n">
         <v>57478</v>
@@ -3511,14 +3461,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528891</v>
+        <v>528830</v>
       </c>
       <c r="R26" t="n">
-        <v>6998754</v>
+        <v>6998687</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3548,24 +3498,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gammal levande tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3580,22 +3520,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122822075</v>
+        <v>122823006</v>
       </c>
       <c r="B27" t="n">
-        <v>74675</v>
+        <v>79847</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3604,41 +3544,46 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6428</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528829</v>
+        <v>528861</v>
       </c>
       <c r="R27" t="n">
-        <v>6998747</v>
+        <v>6998604</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3678,6 +3623,31 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3694,10 +3664,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122820141</v>
+        <v>122820550</v>
       </c>
       <c r="B28" t="n">
-        <v>90952</v>
+        <v>57478</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3710,34 +3680,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528888</v>
+        <v>528843</v>
       </c>
       <c r="R28" t="n">
-        <v>6998720</v>
+        <v>6998785</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3770,6 +3745,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3796,10 +3776,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122820150</v>
+        <v>122819030</v>
       </c>
       <c r="B29" t="n">
-        <v>79022</v>
+        <v>57478</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3808,41 +3788,46 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6459</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528898</v>
+        <v>528811</v>
       </c>
       <c r="R29" t="n">
-        <v>6998770</v>
+        <v>6998709</v>
       </c>
       <c r="S29" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3869,24 +3854,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3901,22 +3876,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122820365</v>
+        <v>122822120</v>
       </c>
       <c r="B30" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3929,42 +3904,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528893</v>
+        <v>528832</v>
       </c>
       <c r="R30" t="n">
-        <v>6998757</v>
+        <v>6998742</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3991,24 +3961,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På gammal tall, äldre ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4023,22 +3978,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122820176</v>
+        <v>122819010</v>
       </c>
       <c r="B31" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4051,34 +4006,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528888</v>
+        <v>528818</v>
       </c>
       <c r="R31" t="n">
-        <v>6998720</v>
+        <v>6998712</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4111,6 +4071,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4137,10 +4102,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122819701</v>
+        <v>122819055</v>
       </c>
       <c r="B32" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4153,24 +4118,29 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
@@ -4180,10 +4150,10 @@
         <v>528843</v>
       </c>
       <c r="R32" t="n">
-        <v>6998744</v>
+        <v>6998681</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4217,7 +4187,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Rikligt på många granar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4228,31 +4198,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4269,10 +4214,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122819057</v>
+        <v>122822373</v>
       </c>
       <c r="B33" t="n">
-        <v>78766</v>
+        <v>90952</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4285,43 +4230,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528830</v>
+        <v>528856</v>
       </c>
       <c r="R33" t="n">
-        <v>6998611</v>
+        <v>6998762</v>
       </c>
       <c r="S33" t="n">
         <v>8</v>
@@ -4353,7 +4289,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4363,12 +4299,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Rikligt på gamla granar i gammal granskog</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4395,10 +4331,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122819726</v>
+        <v>122822680</v>
       </c>
       <c r="B34" t="n">
-        <v>57589</v>
+        <v>78503</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4407,47 +4343,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103031</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528900</v>
+        <v>528888</v>
       </c>
       <c r="R34" t="n">
-        <v>6998697</v>
+        <v>6998655</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4477,9 +4404,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På kolad ved på tallhögstubbe</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4494,22 +4436,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122819987</v>
+        <v>122819543</v>
       </c>
       <c r="B35" t="n">
-        <v>79882</v>
+        <v>74849</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4522,21 +4464,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6463</v>
+        <v>306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4546,13 +4488,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528883</v>
+        <v>528863</v>
       </c>
       <c r="R35" t="n">
-        <v>6998770</v>
+        <v>6998680</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4581,7 +4523,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4591,12 +4533,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På sälglåga</t>
+          <t>På ved på björkhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4611,7 +4553,7 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
@@ -4623,10 +4565,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122819626</v>
+        <v>122819522</v>
       </c>
       <c r="B36" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4639,34 +4581,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528907</v>
+        <v>528843</v>
       </c>
       <c r="R36" t="n">
-        <v>6998684</v>
+        <v>6998616</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4703,7 +4650,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4730,10 +4677,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122819677</v>
+        <v>122820232</v>
       </c>
       <c r="B37" t="n">
-        <v>79848</v>
+        <v>77709</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4746,34 +4693,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528904</v>
+        <v>528897</v>
       </c>
       <c r="R37" t="n">
-        <v>6998685</v>
+        <v>6998766</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4803,9 +4750,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4820,22 +4782,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122819182</v>
+        <v>122822761</v>
       </c>
       <c r="B38" t="n">
-        <v>90948</v>
+        <v>79847</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4848,34 +4810,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528836</v>
+        <v>528879</v>
       </c>
       <c r="R38" t="n">
-        <v>6998668</v>
+        <v>6998619</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4905,9 +4867,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4922,22 +4899,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122822818</v>
+        <v>122819987</v>
       </c>
       <c r="B39" t="n">
-        <v>79847</v>
+        <v>79882</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4946,43 +4923,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528919</v>
+        <v>528883</v>
       </c>
       <c r="R39" t="n">
-        <v>6998644</v>
+        <v>6998770</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5012,14 +4984,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På två gamla grovbarkade sälgar.</t>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5030,51 +5012,26 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122822354</v>
+        <v>122819057</v>
       </c>
       <c r="B40" t="n">
-        <v>91124</v>
+        <v>78766</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5087,37 +5044,46 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1588</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528838</v>
+        <v>528830</v>
       </c>
       <c r="R40" t="n">
-        <v>6998736</v>
+        <v>6998611</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5144,9 +5110,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Rikligt på gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5161,22 +5142,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122822120</v>
+        <v>122819919</v>
       </c>
       <c r="B41" t="n">
-        <v>79847</v>
+        <v>74854</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5185,38 +5166,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>492</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528832</v>
+        <v>528873</v>
       </c>
       <c r="R41" t="n">
-        <v>6998742</v>
+        <v>6998728</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5246,9 +5227,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På bark i hålighet vid basen av gammal björkhögstubbe</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5263,22 +5259,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122822680</v>
+        <v>122822228</v>
       </c>
       <c r="B42" t="n">
-        <v>78503</v>
+        <v>57631</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5291,34 +5287,43 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528888</v>
+        <v>528846</v>
       </c>
       <c r="R42" t="n">
-        <v>6998655</v>
+        <v>6998743</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5348,24 +5353,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På kolad ved på tallhögstubbe</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5380,22 +5370,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122822259</v>
+        <v>122822197</v>
       </c>
       <c r="B43" t="n">
-        <v>78766</v>
+        <v>95911</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5408,42 +5398,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528831</v>
+        <v>528847</v>
       </c>
       <c r="R43" t="n">
-        <v>6998741</v>
+        <v>6998739</v>
       </c>
       <c r="S43" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5470,24 +5455,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5502,19 +5472,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122819522</v>
+        <v>122820570</v>
       </c>
       <c r="B44" t="n">
         <v>57478</v>
@@ -5550,19 +5520,19 @@
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528843</v>
+        <v>528842</v>
       </c>
       <c r="R44" t="n">
-        <v>6998616</v>
+        <v>6998786</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5626,10 +5596,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122822781</v>
+        <v>122822290</v>
       </c>
       <c r="B45" t="n">
-        <v>79883</v>
+        <v>57478</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5638,38 +5608,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528877</v>
+        <v>528824</v>
       </c>
       <c r="R45" t="n">
-        <v>6998634</v>
+        <v>6998724</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5699,24 +5674,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+          <t>Äldre ringhack på en hackspettsbearbetad död gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5727,26 +5692,51 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122819041</v>
+        <v>122822818</v>
       </c>
       <c r="B46" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5759,27 +5749,27 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5788,10 +5778,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528830</v>
+        <v>528919</v>
       </c>
       <c r="R46" t="n">
-        <v>6998687</v>
+        <v>6998644</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5828,7 +5818,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På två gamla grovbarkade sälgar.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5839,6 +5829,31 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5855,7 +5870,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122819010</v>
+        <v>122819081</v>
       </c>
       <c r="B47" t="n">
         <v>57478</v>
@@ -5900,10 +5915,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528818</v>
+        <v>528837</v>
       </c>
       <c r="R47" t="n">
-        <v>6998712</v>
+        <v>6998667</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5967,10 +5982,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122822290</v>
+        <v>122819701</v>
       </c>
       <c r="B48" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5983,42 +5998,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528824</v>
+        <v>528843</v>
       </c>
       <c r="R48" t="n">
-        <v>6998724</v>
+        <v>6998744</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6052,7 +6062,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en hackspettsbearbetad död gran.</t>
+          <t>Rikligt på många granar.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6066,7 +6076,7 @@
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -6081,12 +6091,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6104,10 +6114,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122819055</v>
+        <v>122819677</v>
       </c>
       <c r="B49" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6120,39 +6130,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528843</v>
+        <v>528904</v>
       </c>
       <c r="R49" t="n">
-        <v>6998681</v>
+        <v>6998685</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6185,11 +6190,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6216,10 +6216,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122820024</v>
+        <v>122819960</v>
       </c>
       <c r="B50" t="n">
-        <v>57589</v>
+        <v>57478</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6228,20 +6228,20 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -6251,11 +6251,19 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M50" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -6272,10 +6280,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>528891</v>
+        <v>528893</v>
       </c>
       <c r="R50" t="n">
-        <v>6998690</v>
+        <v>6998687</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6312,7 +6320,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Tre lavskrikor i naturskog med höga naturvärden.</t>
+          <t>Rätt så skygg hane av tretåig hackspett i barrnaturskog med mycket höga livsmiljövärden för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6331,7 +6339,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Flerskiktad hänglavsrik barrnaturskog med höga naturvärden.</t>
+          <t>Kontinuitetsskog med höga naturvärden.</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6349,10 +6357,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122819915</v>
+        <v>122820024</v>
       </c>
       <c r="B51" t="n">
-        <v>57478</v>
+        <v>57589</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6361,20 +6369,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -6384,18 +6392,14 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -6409,10 +6413,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>528893</v>
+        <v>528891</v>
       </c>
       <c r="R51" t="n">
-        <v>6998687</v>
+        <v>6998690</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6449,7 +6453,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Födosökande hona och hane av tretåig hackspett i skog med höga till mycket höga livsmiljövärden.</t>
+          <t>Tre lavskrikor i naturskog med höga naturvärden.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6468,7 +6472,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Flerskiktad barrnaturskog med höga naturvärden.</t>
+          <t>Flerskiktad hänglavsrik barrnaturskog med höga naturvärden.</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6608,10 +6612,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122820539</v>
+        <v>122820461</v>
       </c>
       <c r="B53" t="n">
-        <v>90952</v>
+        <v>57478</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6624,42 +6628,47 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>528851</v>
+        <v>528854</v>
       </c>
       <c r="R53" t="n">
-        <v>6998721</v>
+        <v>6998728</v>
       </c>
       <c r="S53" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6691,6 +6700,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Färska ringhack längs ca 3 m på en granstam i barrnaturskog med revir för tretåig hackspett i höga livsmiljövärden.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6717,12 +6731,12 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6740,10 +6754,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122820461</v>
+        <v>122820539</v>
       </c>
       <c r="B54" t="n">
-        <v>57478</v>
+        <v>90952</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6756,47 +6770,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>528854</v>
+        <v>528851</v>
       </c>
       <c r="R54" t="n">
-        <v>6998728</v>
+        <v>6998721</v>
       </c>
       <c r="S54" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6828,11 +6837,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Färska ringhack längs ca 3 m på en granstam i barrnaturskog med revir för tretåig hackspett i höga livsmiljövärden.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6859,12 +6863,12 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>

--- a/artfynd/A 55408-2024 artfynd.xlsx
+++ b/artfynd/A 55408-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122820365</v>
+        <v>122822373</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>90952</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528893</v>
+        <v>528856</v>
       </c>
       <c r="R2" t="n">
-        <v>6998757</v>
+        <v>6998762</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gammal tall, äldre ringhack</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122821953</v>
+        <v>122820150</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>79022</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,46 +804,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6459</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528813</v>
+        <v>528898</v>
       </c>
       <c r="R3" t="n">
-        <v>6998760</v>
+        <v>6998770</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,14 +865,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,22 +897,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122819825</v>
+        <v>122819608</v>
       </c>
       <c r="B4" t="n">
-        <v>74675</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,41 +921,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528895</v>
+        <v>528807</v>
       </c>
       <c r="R4" t="n">
-        <v>6998697</v>
+        <v>6998706</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,6 +992,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Relativt ymnigt på många granar. Fertila bålar finns här.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -995,6 +1005,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1011,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122819182</v>
+        <v>122822259</v>
       </c>
       <c r="B5" t="n">
-        <v>90948</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,37 +1062,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528836</v>
+        <v>528831</v>
       </c>
       <c r="R5" t="n">
-        <v>6998668</v>
+        <v>6998741</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,9 +1124,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,22 +1156,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122820115</v>
+        <v>122822761</v>
       </c>
       <c r="B6" t="n">
-        <v>74855</v>
+        <v>79847</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,21 +1184,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,10 +1208,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528898</v>
+        <v>528879</v>
       </c>
       <c r="R6" t="n">
-        <v>6998773</v>
+        <v>6998619</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,7 +1243,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1198,12 +1253,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På ved på gammal levande sälg i gammal granskog</t>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,19 +1273,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122821939</v>
+        <v>122819057</v>
       </c>
       <c r="B7" t="n">
         <v>78766</v>
@@ -1265,7 +1320,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1279,10 +1334,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528796</v>
+        <v>528830</v>
       </c>
       <c r="R7" t="n">
-        <v>6998791</v>
+        <v>6998611</v>
       </c>
       <c r="S7" t="n">
         <v>8</v>
@@ -1314,7 +1369,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1379,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt på gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1339,22 +1399,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122819608</v>
+        <v>122819041</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,27 +1427,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1396,13 +1456,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528807</v>
+        <v>528830</v>
       </c>
       <c r="R8" t="n">
-        <v>6998706</v>
+        <v>6998687</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1436,7 +1496,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Relativt ymnigt på många granar. Fertila bålar finns här.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,31 +1507,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1488,10 +1523,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122822259</v>
+        <v>122820570</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1504,42 +1539,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528831</v>
+        <v>528842</v>
       </c>
       <c r="R9" t="n">
-        <v>6998741</v>
+        <v>6998786</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1566,24 +1601,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1598,22 +1623,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122820141</v>
+        <v>122822290</v>
       </c>
       <c r="B10" t="n">
-        <v>90952</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1626,34 +1651,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528888</v>
+        <v>528824</v>
       </c>
       <c r="R10" t="n">
-        <v>6998720</v>
+        <v>6998724</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1688,6 +1718,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på en hackspettsbearbetad död gran.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1696,6 +1731,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1712,10 +1772,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122820150</v>
+        <v>122819522</v>
       </c>
       <c r="B11" t="n">
-        <v>79022</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1724,41 +1784,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6459</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528898</v>
+        <v>528843</v>
       </c>
       <c r="R11" t="n">
-        <v>6998770</v>
+        <v>6998616</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1785,24 +1850,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1817,22 +1872,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122822354</v>
+        <v>122819726</v>
       </c>
       <c r="B12" t="n">
-        <v>91124</v>
+        <v>57589</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1841,38 +1896,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1588</v>
+        <v>103031</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528838</v>
+        <v>528900</v>
       </c>
       <c r="R12" t="n">
-        <v>6998736</v>
+        <v>6998697</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1931,10 +1995,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122822436</v>
+        <v>122822818</v>
       </c>
       <c r="B13" t="n">
-        <v>78503</v>
+        <v>79847</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1947,37 +2011,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528840</v>
+        <v>528919</v>
       </c>
       <c r="R13" t="n">
-        <v>6998787</v>
+        <v>6998644</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2004,24 +2073,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På kolad ved på tallstubbe</t>
+          <t>På två gamla grovbarkade sälgar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2032,26 +2091,51 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122819526</v>
+        <v>122820365</v>
       </c>
       <c r="B14" t="n">
-        <v>90952</v>
+        <v>57478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2064,37 +2148,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528875</v>
+        <v>528893</v>
       </c>
       <c r="R14" t="n">
-        <v>6998691</v>
+        <v>6998757</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2123,7 +2212,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2133,12 +2222,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På gammal tall, äldre ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2153,22 +2242,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122819726</v>
+        <v>122822228</v>
       </c>
       <c r="B15" t="n">
-        <v>57589</v>
+        <v>57631</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2177,25 +2266,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2214,10 +2303,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528900</v>
+        <v>528846</v>
       </c>
       <c r="R15" t="n">
-        <v>6998697</v>
+        <v>6998743</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2276,10 +2365,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122819213</v>
+        <v>122819526</v>
       </c>
       <c r="B16" t="n">
-        <v>79847</v>
+        <v>90952</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2292,21 +2381,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2316,10 +2405,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528849</v>
+        <v>528875</v>
       </c>
       <c r="R16" t="n">
-        <v>6998626</v>
+        <v>6998691</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2351,7 +2440,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2361,12 +2450,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2393,10 +2482,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122819697</v>
+        <v>122820739</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>77699</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2409,39 +2498,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528891</v>
+        <v>528795</v>
       </c>
       <c r="R17" t="n">
-        <v>6998754</v>
+        <v>6998791</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2473,7 +2557,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2483,12 +2567,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gammal levande tall</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2515,10 +2599,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122822781</v>
+        <v>122823006</v>
       </c>
       <c r="B18" t="n">
-        <v>79883</v>
+        <v>79847</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2527,41 +2611,46 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528877</v>
+        <v>528861</v>
       </c>
       <c r="R18" t="n">
-        <v>6998634</v>
+        <v>6998604</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2588,26 +2677,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2616,26 +2690,51 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122822075</v>
+        <v>122819055</v>
       </c>
       <c r="B19" t="n">
-        <v>74675</v>
+        <v>57478</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2644,38 +2743,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6428</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528829</v>
+        <v>528843</v>
       </c>
       <c r="R19" t="n">
-        <v>6998747</v>
+        <v>6998681</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2708,6 +2812,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2734,10 +2843,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122819597</v>
+        <v>122820232</v>
       </c>
       <c r="B20" t="n">
-        <v>82553</v>
+        <v>77709</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2750,21 +2859,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2774,10 +2883,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528869</v>
+        <v>528897</v>
       </c>
       <c r="R20" t="n">
-        <v>6998649</v>
+        <v>6998766</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2809,7 +2918,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2819,7 +2928,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2851,10 +2960,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122820558</v>
+        <v>122820141</v>
       </c>
       <c r="B21" t="n">
-        <v>74863</v>
+        <v>90952</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2867,37 +2976,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528878</v>
+        <v>528888</v>
       </c>
       <c r="R21" t="n">
-        <v>6998770</v>
+        <v>6998720</v>
       </c>
       <c r="S21" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2924,24 +3033,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2956,22 +3050,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122819626</v>
+        <v>122820558</v>
       </c>
       <c r="B22" t="n">
-        <v>79847</v>
+        <v>74863</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2984,37 +3078,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528907</v>
+        <v>528878</v>
       </c>
       <c r="R22" t="n">
-        <v>6998684</v>
+        <v>6998770</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3041,14 +3135,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3063,22 +3167,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122819870</v>
+        <v>122819597</v>
       </c>
       <c r="B23" t="n">
-        <v>79847</v>
+        <v>82553</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3091,46 +3195,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528902</v>
+        <v>528869</v>
       </c>
       <c r="R23" t="n">
-        <v>6998729</v>
+        <v>6998649</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3159,7 +3254,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3169,12 +3264,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På björklåga</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3189,22 +3284,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122820176</v>
+        <v>122819213</v>
       </c>
       <c r="B24" t="n">
-        <v>57631</v>
+        <v>79847</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3217,34 +3312,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528888</v>
+        <v>528849</v>
       </c>
       <c r="R24" t="n">
-        <v>6998720</v>
+        <v>6998626</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3274,9 +3369,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3291,22 +3401,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122820739</v>
+        <v>122819870</v>
       </c>
       <c r="B25" t="n">
-        <v>77699</v>
+        <v>79847</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3319,37 +3429,46 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528795</v>
+        <v>528902</v>
       </c>
       <c r="R25" t="n">
-        <v>6998791</v>
+        <v>6998729</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3378,7 +3497,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3388,12 +3507,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På björklåga</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3408,22 +3527,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122819041</v>
+        <v>122819919</v>
       </c>
       <c r="B26" t="n">
-        <v>57478</v>
+        <v>74854</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3432,43 +3551,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>492</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528830</v>
+        <v>528873</v>
       </c>
       <c r="R26" t="n">
-        <v>6998687</v>
+        <v>6998728</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3498,14 +3612,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På bark i hålighet vid basen av gammal björkhögstubbe</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3520,22 +3644,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122823006</v>
+        <v>122819677</v>
       </c>
       <c r="B27" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3548,42 +3672,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528861</v>
+        <v>528904</v>
       </c>
       <c r="R27" t="n">
-        <v>6998604</v>
+        <v>6998685</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3623,31 +3742,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3664,7 +3758,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122820550</v>
+        <v>122819030</v>
       </c>
       <c r="B28" t="n">
         <v>57478</v>
@@ -3700,19 +3794,19 @@
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528843</v>
+        <v>528811</v>
       </c>
       <c r="R28" t="n">
-        <v>6998785</v>
+        <v>6998709</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3776,10 +3870,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122819030</v>
+        <v>122820176</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3792,39 +3886,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528811</v>
+        <v>528888</v>
       </c>
       <c r="R29" t="n">
-        <v>6998709</v>
+        <v>6998720</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3857,11 +3946,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3888,10 +3972,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122822120</v>
+        <v>122822436</v>
       </c>
       <c r="B30" t="n">
-        <v>79847</v>
+        <v>78503</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3904,37 +3988,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528832</v>
+        <v>528840</v>
       </c>
       <c r="R30" t="n">
-        <v>6998742</v>
+        <v>6998787</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3961,9 +4045,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På kolad ved på tallstubbe</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3978,22 +4077,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122819010</v>
+        <v>122822197</v>
       </c>
       <c r="B31" t="n">
-        <v>57478</v>
+        <v>95911</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4006,39 +4105,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528818</v>
+        <v>528847</v>
       </c>
       <c r="R31" t="n">
-        <v>6998712</v>
+        <v>6998739</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4071,11 +4165,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4102,10 +4191,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122819055</v>
+        <v>122822354</v>
       </c>
       <c r="B32" t="n">
-        <v>57478</v>
+        <v>91124</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4118,39 +4207,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>1588</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528843</v>
+        <v>528838</v>
       </c>
       <c r="R32" t="n">
-        <v>6998681</v>
+        <v>6998736</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4183,11 +4267,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4214,10 +4293,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122822373</v>
+        <v>122820550</v>
       </c>
       <c r="B33" t="n">
-        <v>90952</v>
+        <v>57478</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4230,37 +4309,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528856</v>
+        <v>528843</v>
       </c>
       <c r="R33" t="n">
-        <v>6998762</v>
+        <v>6998785</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4287,24 +4371,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4319,22 +4393,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122822680</v>
+        <v>122822120</v>
       </c>
       <c r="B34" t="n">
-        <v>78503</v>
+        <v>79847</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4347,34 +4421,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528888</v>
+        <v>528832</v>
       </c>
       <c r="R34" t="n">
-        <v>6998655</v>
+        <v>6998742</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4404,24 +4478,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På kolad ved på tallhögstubbe</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4436,22 +4495,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122819543</v>
+        <v>122821939</v>
       </c>
       <c r="B35" t="n">
-        <v>74849</v>
+        <v>78766</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4460,41 +4519,50 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>306</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528863</v>
+        <v>528796</v>
       </c>
       <c r="R35" t="n">
-        <v>6998680</v>
+        <v>6998791</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4523,7 +4591,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4533,12 +4601,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På ved på björkhögstubbe i gammal granskog</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4553,22 +4616,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122819522</v>
+        <v>122822781</v>
       </c>
       <c r="B36" t="n">
-        <v>57478</v>
+        <v>79883</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4577,43 +4640,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528843</v>
+        <v>528877</v>
       </c>
       <c r="R36" t="n">
-        <v>6998616</v>
+        <v>6998634</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4643,14 +4701,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4665,22 +4733,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122820232</v>
+        <v>122819701</v>
       </c>
       <c r="B37" t="n">
-        <v>77709</v>
+        <v>78766</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4693,37 +4761,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528897</v>
+        <v>528843</v>
       </c>
       <c r="R37" t="n">
-        <v>6998766</v>
+        <v>6998744</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4750,24 +4818,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>11:42</t>
-        </is>
-      </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>Rikligt på många granar.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4778,26 +4836,51 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122822761</v>
+        <v>122819010</v>
       </c>
       <c r="B38" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4810,34 +4893,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528879</v>
+        <v>528818</v>
       </c>
       <c r="R38" t="n">
-        <v>6998619</v>
+        <v>6998712</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4867,24 +4955,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På sälglåga</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4899,22 +4977,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122819987</v>
+        <v>122820115</v>
       </c>
       <c r="B39" t="n">
-        <v>79882</v>
+        <v>74855</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4923,25 +5001,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6463</v>
+        <v>308</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4951,10 +5029,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528883</v>
+        <v>528898</v>
       </c>
       <c r="R39" t="n">
-        <v>6998770</v>
+        <v>6998773</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4986,7 +5064,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4996,12 +5074,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På sälglåga</t>
+          <t>På ved på gammal levande sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5016,22 +5094,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122819057</v>
+        <v>122819543</v>
       </c>
       <c r="B40" t="n">
-        <v>78766</v>
+        <v>74849</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5040,50 +5118,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528830</v>
+        <v>528863</v>
       </c>
       <c r="R40" t="n">
-        <v>6998611</v>
+        <v>6998680</v>
       </c>
       <c r="S40" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5112,7 +5181,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5122,12 +5191,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Rikligt på gamla granar i gammal granskog</t>
+          <t>På ved på björkhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5154,10 +5223,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122819919</v>
+        <v>122821953</v>
       </c>
       <c r="B41" t="n">
-        <v>74854</v>
+        <v>57478</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5166,38 +5235,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528873</v>
+        <v>528813</v>
       </c>
       <c r="R41" t="n">
-        <v>6998728</v>
+        <v>6998760</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5227,24 +5301,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På bark i hålighet vid basen av gammal björkhögstubbe</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5259,22 +5323,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122822228</v>
+        <v>122822075</v>
       </c>
       <c r="B42" t="n">
-        <v>57631</v>
+        <v>74675</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5283,47 +5347,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>6428</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528846</v>
+        <v>528829</v>
       </c>
       <c r="R42" t="n">
-        <v>6998743</v>
+        <v>6998747</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5382,10 +5437,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122822197</v>
+        <v>122819626</v>
       </c>
       <c r="B43" t="n">
-        <v>95911</v>
+        <v>79847</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5398,21 +5453,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5422,10 +5477,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528847</v>
+        <v>528907</v>
       </c>
       <c r="R43" t="n">
-        <v>6998739</v>
+        <v>6998684</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5458,6 +5513,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5484,7 +5544,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122820570</v>
+        <v>122819697</v>
       </c>
       <c r="B44" t="n">
         <v>57478</v>
@@ -5520,19 +5580,19 @@
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528842</v>
+        <v>528891</v>
       </c>
       <c r="R44" t="n">
-        <v>6998786</v>
+        <v>6998754</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5562,14 +5622,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre ringhack på gammal levande tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5584,22 +5654,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122822290</v>
+        <v>122819182</v>
       </c>
       <c r="B45" t="n">
-        <v>57478</v>
+        <v>90948</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5612,39 +5682,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528824</v>
+        <v>528836</v>
       </c>
       <c r="R45" t="n">
-        <v>6998724</v>
+        <v>6998668</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5679,11 +5744,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på en hackspettsbearbetad död gran.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5692,31 +5752,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5733,10 +5768,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122822818</v>
+        <v>122819825</v>
       </c>
       <c r="B46" t="n">
-        <v>79847</v>
+        <v>74675</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5745,43 +5780,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6428</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528919</v>
+        <v>528895</v>
       </c>
       <c r="R46" t="n">
-        <v>6998644</v>
+        <v>6998697</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5816,11 +5846,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På två gamla grovbarkade sälgar.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5829,31 +5854,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5982,10 +5982,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122819701</v>
+        <v>122819987</v>
       </c>
       <c r="B48" t="n">
-        <v>78766</v>
+        <v>79882</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5994,20 +5994,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -6018,17 +6018,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528843</v>
+        <v>528883</v>
       </c>
       <c r="R48" t="n">
-        <v>6998744</v>
+        <v>6998770</v>
       </c>
       <c r="S48" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6055,14 +6055,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Rikligt på många granar.</t>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6073,51 +6083,26 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122819677</v>
+        <v>122822680</v>
       </c>
       <c r="B49" t="n">
-        <v>79848</v>
+        <v>78503</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6130,34 +6115,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528904</v>
+        <v>528888</v>
       </c>
       <c r="R49" t="n">
-        <v>6998685</v>
+        <v>6998655</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6187,9 +6172,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På kolad ved på tallhögstubbe</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6204,22 +6204,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122819960</v>
+        <v>122820024</v>
       </c>
       <c r="B50" t="n">
-        <v>57478</v>
+        <v>57589</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6228,20 +6228,20 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -6251,19 +6251,11 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -6280,10 +6272,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>528893</v>
+        <v>528891</v>
       </c>
       <c r="R50" t="n">
-        <v>6998687</v>
+        <v>6998690</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6320,7 +6312,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Rätt så skygg hane av tretåig hackspett i barrnaturskog med mycket höga livsmiljövärden för tretåig hackspett.</t>
+          <t>Tre lavskrikor i naturskog med höga naturvärden.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6339,7 +6331,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Kontinuitetsskog med höga naturvärden.</t>
+          <t>Flerskiktad hänglavsrik barrnaturskog med höga naturvärden.</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6357,10 +6349,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122820024</v>
+        <v>122819960</v>
       </c>
       <c r="B51" t="n">
-        <v>57589</v>
+        <v>57478</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6369,20 +6361,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -6392,11 +6384,19 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -6413,10 +6413,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>528891</v>
+        <v>528893</v>
       </c>
       <c r="R51" t="n">
-        <v>6998690</v>
+        <v>6998687</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6453,7 +6453,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Tre lavskrikor i naturskog med höga naturvärden.</t>
+          <t>Rätt så skygg hane av tretåig hackspett i barrnaturskog med mycket höga livsmiljövärden för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Flerskiktad hänglavsrik barrnaturskog med höga naturvärden.</t>
+          <t>Kontinuitetsskog med höga naturvärden.</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6612,10 +6612,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122820461</v>
+        <v>122820539</v>
       </c>
       <c r="B53" t="n">
-        <v>57478</v>
+        <v>90952</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6628,47 +6628,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>528854</v>
+        <v>528851</v>
       </c>
       <c r="R53" t="n">
-        <v>6998728</v>
+        <v>6998721</v>
       </c>
       <c r="S53" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6700,11 +6695,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Färska ringhack längs ca 3 m på en granstam i barrnaturskog med revir för tretåig hackspett i höga livsmiljövärden.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6731,12 +6721,12 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6754,10 +6744,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122820539</v>
+        <v>122820461</v>
       </c>
       <c r="B54" t="n">
-        <v>90952</v>
+        <v>57478</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6770,42 +6760,47 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>528851</v>
+        <v>528854</v>
       </c>
       <c r="R54" t="n">
-        <v>6998721</v>
+        <v>6998728</v>
       </c>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6837,6 +6832,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Färska ringhack längs ca 3 m på en granstam i barrnaturskog med revir för tretåig hackspett i höga livsmiljövärden.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6863,12 +6863,12 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>

--- a/artfynd/A 55408-2024 artfynd.xlsx
+++ b/artfynd/A 55408-2024 artfynd.xlsx
@@ -2132,10 +2132,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122820365</v>
+        <v>122822228</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2148,42 +2148,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528893</v>
+        <v>528846</v>
       </c>
       <c r="R14" t="n">
-        <v>6998757</v>
+        <v>6998743</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2210,24 +2214,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På gammal tall, äldre ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2242,22 +2231,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122822228</v>
+        <v>122820365</v>
       </c>
       <c r="B15" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2270,46 +2259,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528846</v>
+        <v>528893</v>
       </c>
       <c r="R15" t="n">
-        <v>6998743</v>
+        <v>6998757</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2336,9 +2321,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På gammal tall, äldre ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2353,12 +2353,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -3539,10 +3539,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122819919</v>
+        <v>122820176</v>
       </c>
       <c r="B26" t="n">
-        <v>74854</v>
+        <v>57631</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3551,38 +3551,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>492</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528873</v>
+        <v>528888</v>
       </c>
       <c r="R26" t="n">
-        <v>6998728</v>
+        <v>6998720</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3612,24 +3612,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På bark i hålighet vid basen av gammal björkhögstubbe</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3644,22 +3629,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122819677</v>
+        <v>122819919</v>
       </c>
       <c r="B27" t="n">
-        <v>79848</v>
+        <v>74854</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3668,38 +3653,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>492</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528904</v>
+        <v>528873</v>
       </c>
       <c r="R27" t="n">
-        <v>6998685</v>
+        <v>6998728</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3729,9 +3714,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På bark i hålighet vid basen av gammal björkhögstubbe</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3746,22 +3746,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122819030</v>
+        <v>122819677</v>
       </c>
       <c r="B28" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3774,39 +3774,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528811</v>
+        <v>528904</v>
       </c>
       <c r="R28" t="n">
-        <v>6998709</v>
+        <v>6998685</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3839,11 +3834,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3870,10 +3860,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122820176</v>
+        <v>122819030</v>
       </c>
       <c r="B29" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3886,34 +3876,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528888</v>
+        <v>528811</v>
       </c>
       <c r="R29" t="n">
-        <v>6998720</v>
+        <v>6998709</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3946,6 +3941,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4989,10 +4989,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122820115</v>
+        <v>122822075</v>
       </c>
       <c r="B39" t="n">
-        <v>74855</v>
+        <v>74675</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5001,38 +5001,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>308</v>
+        <v>6428</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528898</v>
+        <v>528829</v>
       </c>
       <c r="R39" t="n">
-        <v>6998773</v>
+        <v>6998747</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5062,24 +5062,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På ved på gammal levande sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5094,22 +5079,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122819543</v>
+        <v>122820115</v>
       </c>
       <c r="B40" t="n">
-        <v>74849</v>
+        <v>74855</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5118,25 +5103,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5146,13 +5131,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528863</v>
+        <v>528898</v>
       </c>
       <c r="R40" t="n">
-        <v>6998680</v>
+        <v>6998773</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5181,7 +5166,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5191,12 +5176,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På ved på björkhögstubbe i gammal granskog</t>
+          <t>På ved på gammal levande sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5223,10 +5208,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122821953</v>
+        <v>122819543</v>
       </c>
       <c r="B41" t="n">
-        <v>57478</v>
+        <v>74849</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5235,46 +5220,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528813</v>
+        <v>528863</v>
       </c>
       <c r="R41" t="n">
-        <v>6998760</v>
+        <v>6998680</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5301,14 +5281,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>På ved på björkhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5323,22 +5313,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122822075</v>
+        <v>122821953</v>
       </c>
       <c r="B42" t="n">
-        <v>74675</v>
+        <v>57478</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5347,38 +5337,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6428</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528829</v>
+        <v>528813</v>
       </c>
       <c r="R42" t="n">
-        <v>6998747</v>
+        <v>6998760</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5411,6 +5406,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 55408-2024 artfynd.xlsx
+++ b/artfynd/A 55408-2024 artfynd.xlsx
@@ -2132,10 +2132,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122822228</v>
+        <v>122820365</v>
       </c>
       <c r="B14" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2148,46 +2148,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528846</v>
+        <v>528893</v>
       </c>
       <c r="R14" t="n">
-        <v>6998743</v>
+        <v>6998757</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2214,9 +2210,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På gammal tall, äldre ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2231,22 +2242,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122820365</v>
+        <v>122822228</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2259,42 +2270,46 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528893</v>
+        <v>528846</v>
       </c>
       <c r="R15" t="n">
-        <v>6998757</v>
+        <v>6998743</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2321,24 +2336,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På gammal tall, äldre ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2353,12 +2353,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -3539,10 +3539,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122820176</v>
+        <v>122819919</v>
       </c>
       <c r="B26" t="n">
-        <v>57631</v>
+        <v>74854</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3551,38 +3551,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>492</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528888</v>
+        <v>528873</v>
       </c>
       <c r="R26" t="n">
-        <v>6998720</v>
+        <v>6998728</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3612,9 +3612,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På bark i hålighet vid basen av gammal björkhögstubbe</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3629,22 +3644,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122819919</v>
+        <v>122819677</v>
       </c>
       <c r="B27" t="n">
-        <v>74854</v>
+        <v>79848</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3653,38 +3668,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>492</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528873</v>
+        <v>528904</v>
       </c>
       <c r="R27" t="n">
-        <v>6998728</v>
+        <v>6998685</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3714,24 +3729,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På bark i hålighet vid basen av gammal björkhögstubbe</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3746,22 +3746,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122819677</v>
+        <v>122819030</v>
       </c>
       <c r="B28" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3774,34 +3774,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528904</v>
+        <v>528811</v>
       </c>
       <c r="R28" t="n">
-        <v>6998685</v>
+        <v>6998709</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3834,6 +3839,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3860,10 +3870,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122819030</v>
+        <v>122820176</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3876,39 +3886,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528811</v>
+        <v>528888</v>
       </c>
       <c r="R29" t="n">
-        <v>6998709</v>
+        <v>6998720</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3941,11 +3946,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 55408-2024 artfynd.xlsx
+++ b/artfynd/A 55408-2024 artfynd.xlsx
@@ -3539,10 +3539,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122819919</v>
+        <v>122820176</v>
       </c>
       <c r="B26" t="n">
-        <v>74854</v>
+        <v>57631</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3551,38 +3551,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>492</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528873</v>
+        <v>528888</v>
       </c>
       <c r="R26" t="n">
-        <v>6998728</v>
+        <v>6998720</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3612,24 +3612,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På bark i hålighet vid basen av gammal björkhögstubbe</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3644,22 +3629,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122819677</v>
+        <v>122819919</v>
       </c>
       <c r="B27" t="n">
-        <v>79848</v>
+        <v>74854</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3668,38 +3653,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>492</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528904</v>
+        <v>528873</v>
       </c>
       <c r="R27" t="n">
-        <v>6998685</v>
+        <v>6998728</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3729,9 +3714,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På bark i hålighet vid basen av gammal björkhögstubbe</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3746,22 +3746,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122819030</v>
+        <v>122819677</v>
       </c>
       <c r="B28" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3774,39 +3774,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528811</v>
+        <v>528904</v>
       </c>
       <c r="R28" t="n">
-        <v>6998709</v>
+        <v>6998685</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3839,11 +3834,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3870,10 +3860,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122820176</v>
+        <v>122819030</v>
       </c>
       <c r="B29" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3886,34 +3876,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528888</v>
+        <v>528811</v>
       </c>
       <c r="R29" t="n">
-        <v>6998720</v>
+        <v>6998709</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3946,6 +3941,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 55408-2024 artfynd.xlsx
+++ b/artfynd/A 55408-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122822373</v>
+        <v>122819526</v>
       </c>
       <c r="B2" t="n">
-        <v>90952</v>
+        <v>90955</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528856</v>
+        <v>528875</v>
       </c>
       <c r="R2" t="n">
-        <v>6998762</v>
+        <v>6998691</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122820150</v>
+        <v>122819701</v>
       </c>
       <c r="B3" t="n">
-        <v>79022</v>
+        <v>78769</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,41 +804,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6459</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528898</v>
+        <v>528843</v>
       </c>
       <c r="R3" t="n">
-        <v>6998770</v>
+        <v>6998744</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,24 +865,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>Rikligt på många granar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,26 +883,51 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122819608</v>
+        <v>122822680</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>78506</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,42 +940,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528807</v>
+        <v>528888</v>
       </c>
       <c r="R4" t="n">
-        <v>6998706</v>
+        <v>6998655</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,14 +997,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Relativt ymnigt på många granar. Fertila bålar finns här.</t>
+          <t>På kolad ved på tallhögstubbe</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,51 +1025,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122822259</v>
+        <v>122820232</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>77712</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1062,42 +1057,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528831</v>
+        <v>528897</v>
       </c>
       <c r="R5" t="n">
-        <v>6998741</v>
+        <v>6998766</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1126,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1136,12 +1126,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,7 +1146,7 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1168,10 +1158,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122822761</v>
+        <v>122819543</v>
       </c>
       <c r="B6" t="n">
-        <v>79847</v>
+        <v>74852</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1180,25 +1170,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1208,13 +1198,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528879</v>
+        <v>528863</v>
       </c>
       <c r="R6" t="n">
-        <v>6998619</v>
+        <v>6998680</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1243,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1253,12 +1243,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På sälglåga</t>
+          <t>På ved på björkhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1273,22 +1263,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122819057</v>
+        <v>122822761</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>79850</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1301,46 +1291,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528830</v>
+        <v>528879</v>
       </c>
       <c r="R7" t="n">
-        <v>6998611</v>
+        <v>6998619</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1369,7 +1350,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1379,12 +1360,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt på gamla granar i gammal granskog</t>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1399,22 +1380,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122819041</v>
+        <v>122822120</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>79850</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1427,39 +1408,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528830</v>
+        <v>528832</v>
       </c>
       <c r="R8" t="n">
-        <v>6998687</v>
+        <v>6998742</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1492,11 +1468,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1523,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122820570</v>
+        <v>122822818</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>79850</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1539,39 +1510,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528842</v>
+        <v>528919</v>
       </c>
       <c r="R9" t="n">
-        <v>6998786</v>
+        <v>6998644</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1608,7 +1579,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På två gamla grovbarkade sälgar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1619,6 +1590,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1635,10 +1631,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122822290</v>
+        <v>122820739</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>77702</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1651,39 +1647,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528824</v>
+        <v>528795</v>
       </c>
       <c r="R10" t="n">
-        <v>6998724</v>
+        <v>6998791</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1713,14 +1704,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en hackspettsbearbetad död gran.</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1731,51 +1732,26 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122819522</v>
+        <v>122819626</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>79850</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1788,39 +1764,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528843</v>
+        <v>528907</v>
       </c>
       <c r="R11" t="n">
-        <v>6998616</v>
+        <v>6998684</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1857,7 +1828,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1884,10 +1855,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122819726</v>
+        <v>122820141</v>
       </c>
       <c r="B12" t="n">
-        <v>57589</v>
+        <v>90955</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1896,47 +1867,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103031</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528900</v>
+        <v>528888</v>
       </c>
       <c r="R12" t="n">
-        <v>6998697</v>
+        <v>6998720</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1995,10 +1957,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122822818</v>
+        <v>122819597</v>
       </c>
       <c r="B13" t="n">
-        <v>79847</v>
+        <v>82556</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2011,39 +1973,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528919</v>
+        <v>528869</v>
       </c>
       <c r="R13" t="n">
-        <v>6998644</v>
+        <v>6998649</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2073,14 +2030,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På två gamla grovbarkade sälgar.</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2091,51 +2058,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122820365</v>
+        <v>122822259</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>78769</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2148,27 +2090,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2177,13 +2119,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528893</v>
+        <v>528831</v>
       </c>
       <c r="R14" t="n">
-        <v>6998757</v>
+        <v>6998741</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2212,7 +2154,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2222,12 +2164,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gammal tall, äldre ringhack</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2242,22 +2184,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122822228</v>
+        <v>122819697</v>
       </c>
       <c r="B15" t="n">
-        <v>57631</v>
+        <v>57481</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2270,43 +2212,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528846</v>
+        <v>528891</v>
       </c>
       <c r="R15" t="n">
-        <v>6998743</v>
+        <v>6998754</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2336,9 +2274,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gammal levande tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2353,22 +2306,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122819526</v>
+        <v>122819010</v>
       </c>
       <c r="B16" t="n">
-        <v>90952</v>
+        <v>57481</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2381,34 +2334,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528875</v>
+        <v>528818</v>
       </c>
       <c r="R16" t="n">
-        <v>6998691</v>
+        <v>6998712</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2438,24 +2396,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2470,22 +2418,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122820739</v>
+        <v>122822228</v>
       </c>
       <c r="B17" t="n">
-        <v>77699</v>
+        <v>57634</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2498,34 +2446,43 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228579</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528795</v>
+        <v>528846</v>
       </c>
       <c r="R17" t="n">
-        <v>6998791</v>
+        <v>6998743</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2555,24 +2512,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2587,22 +2529,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122823006</v>
+        <v>122820558</v>
       </c>
       <c r="B18" t="n">
-        <v>79847</v>
+        <v>74866</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2615,42 +2557,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528861</v>
+        <v>528878</v>
       </c>
       <c r="R18" t="n">
-        <v>6998604</v>
+        <v>6998770</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2677,11 +2614,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2690,51 +2642,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122819055</v>
+        <v>122820150</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
+        <v>79025</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2743,46 +2670,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6459</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528843</v>
+        <v>528898</v>
       </c>
       <c r="R19" t="n">
-        <v>6998681</v>
+        <v>6998770</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2809,14 +2731,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2831,22 +2763,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122820232</v>
+        <v>122820115</v>
       </c>
       <c r="B20" t="n">
-        <v>77709</v>
+        <v>74858</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2859,21 +2791,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2883,10 +2815,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528897</v>
+        <v>528898</v>
       </c>
       <c r="R20" t="n">
-        <v>6998766</v>
+        <v>6998773</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2918,7 +2850,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2928,12 +2860,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På ved på gammal levande sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2960,10 +2892,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122820141</v>
+        <v>122822373</v>
       </c>
       <c r="B21" t="n">
-        <v>90952</v>
+        <v>90955</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2996,17 +2928,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528888</v>
+        <v>528856</v>
       </c>
       <c r="R21" t="n">
-        <v>6998720</v>
+        <v>6998762</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3033,9 +2965,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3050,22 +2997,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122820558</v>
+        <v>122820365</v>
       </c>
       <c r="B22" t="n">
-        <v>74863</v>
+        <v>57481</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3078,37 +3025,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528878</v>
+        <v>528893</v>
       </c>
       <c r="R22" t="n">
-        <v>6998770</v>
+        <v>6998757</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3137,7 +3089,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3147,12 +3099,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gammal tall, äldre ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3167,22 +3119,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122819597</v>
+        <v>122822354</v>
       </c>
       <c r="B23" t="n">
-        <v>82553</v>
+        <v>91127</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3195,34 +3147,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>1588</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528869</v>
+        <v>528838</v>
       </c>
       <c r="R23" t="n">
-        <v>6998649</v>
+        <v>6998736</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3252,24 +3204,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3284,22 +3221,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122819213</v>
+        <v>122823006</v>
       </c>
       <c r="B24" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3330,19 +3267,24 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528849</v>
+        <v>528861</v>
       </c>
       <c r="R24" t="n">
-        <v>6998626</v>
+        <v>6998604</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3369,26 +3311,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>10:57</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>10:57</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3397,26 +3324,51 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122819870</v>
+        <v>122819081</v>
       </c>
       <c r="B25" t="n">
-        <v>79847</v>
+        <v>57481</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3429,46 +3381,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528902</v>
+        <v>528837</v>
       </c>
       <c r="R25" t="n">
-        <v>6998729</v>
+        <v>6998667</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3495,24 +3443,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:29</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:29</t>
-        </is>
-      </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På björklåga</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3527,12 +3465,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3542,7 +3480,7 @@
         <v>122820176</v>
       </c>
       <c r="B26" t="n">
-        <v>57631</v>
+        <v>57634</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3641,10 +3579,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122819919</v>
+        <v>122819182</v>
       </c>
       <c r="B27" t="n">
-        <v>74854</v>
+        <v>90951</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3653,38 +3591,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>492</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528873</v>
+        <v>528836</v>
       </c>
       <c r="R27" t="n">
-        <v>6998728</v>
+        <v>6998668</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3714,24 +3652,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På bark i hålighet vid basen av gammal björkhögstubbe</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3746,22 +3669,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122819677</v>
+        <v>122819825</v>
       </c>
       <c r="B28" t="n">
-        <v>79848</v>
+        <v>74678</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3770,25 +3693,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>6428</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3798,10 +3721,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528904</v>
+        <v>528895</v>
       </c>
       <c r="R28" t="n">
-        <v>6998685</v>
+        <v>6998697</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3860,10 +3783,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122819030</v>
+        <v>122819987</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>79885</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3872,43 +3795,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528811</v>
+        <v>528883</v>
       </c>
       <c r="R29" t="n">
-        <v>6998709</v>
+        <v>6998770</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3938,14 +3856,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3960,22 +3888,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122822436</v>
+        <v>122819030</v>
       </c>
       <c r="B30" t="n">
-        <v>78503</v>
+        <v>57481</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3988,37 +3916,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528840</v>
+        <v>528811</v>
       </c>
       <c r="R30" t="n">
-        <v>6998787</v>
+        <v>6998709</v>
       </c>
       <c r="S30" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4045,24 +3978,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På kolad ved på tallstubbe</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4077,22 +4000,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122822197</v>
+        <v>122819870</v>
       </c>
       <c r="B31" t="n">
-        <v>95911</v>
+        <v>79850</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4105,37 +4028,46 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528847</v>
+        <v>528902</v>
       </c>
       <c r="R31" t="n">
-        <v>6998739</v>
+        <v>6998729</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4162,9 +4094,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På björklåga</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4179,22 +4126,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122822354</v>
+        <v>122820550</v>
       </c>
       <c r="B32" t="n">
-        <v>91124</v>
+        <v>57481</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4207,34 +4154,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1588</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528838</v>
+        <v>528843</v>
       </c>
       <c r="R32" t="n">
-        <v>6998736</v>
+        <v>6998785</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4267,6 +4219,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4293,10 +4250,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122820550</v>
+        <v>122822197</v>
       </c>
       <c r="B33" t="n">
-        <v>57478</v>
+        <v>95914</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4309,39 +4266,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528843</v>
+        <v>528847</v>
       </c>
       <c r="R33" t="n">
-        <v>6998785</v>
+        <v>6998739</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4374,11 +4326,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4405,10 +4352,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122822120</v>
+        <v>122819213</v>
       </c>
       <c r="B34" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4441,14 +4388,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528832</v>
+        <v>528849</v>
       </c>
       <c r="R34" t="n">
-        <v>6998742</v>
+        <v>6998626</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4478,9 +4425,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4495,22 +4457,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122821939</v>
+        <v>122822075</v>
       </c>
       <c r="B35" t="n">
-        <v>78766</v>
+        <v>74678</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4519,50 +4481,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528796</v>
+        <v>528829</v>
       </c>
       <c r="R35" t="n">
-        <v>6998791</v>
+        <v>6998747</v>
       </c>
       <c r="S35" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4589,19 +4542,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>12:42</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4616,22 +4559,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122822781</v>
+        <v>122822290</v>
       </c>
       <c r="B36" t="n">
-        <v>79883</v>
+        <v>57481</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4640,38 +4583,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528877</v>
+        <v>528824</v>
       </c>
       <c r="R36" t="n">
-        <v>6998634</v>
+        <v>6998724</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4701,24 +4649,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+          <t>Äldre ringhack på en hackspettsbearbetad död gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4729,26 +4667,51 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122819701</v>
+        <v>122822781</v>
       </c>
       <c r="B37" t="n">
-        <v>78766</v>
+        <v>79886</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4757,41 +4720,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528843</v>
+        <v>528877</v>
       </c>
       <c r="R37" t="n">
-        <v>6998744</v>
+        <v>6998634</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4818,14 +4781,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Rikligt på många granar.</t>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4836,51 +4809,26 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122819010</v>
+        <v>122819057</v>
       </c>
       <c r="B38" t="n">
-        <v>57478</v>
+        <v>78769</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4893,42 +4841,46 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528818</v>
+        <v>528830</v>
       </c>
       <c r="R38" t="n">
-        <v>6998712</v>
+        <v>6998611</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4955,14 +4907,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt på gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4977,22 +4939,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122822075</v>
+        <v>122819041</v>
       </c>
       <c r="B39" t="n">
-        <v>74675</v>
+        <v>57481</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5001,38 +4963,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6428</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528829</v>
+        <v>528830</v>
       </c>
       <c r="R39" t="n">
-        <v>6998747</v>
+        <v>6998687</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5065,6 +5032,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5091,10 +5063,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122820115</v>
+        <v>122819522</v>
       </c>
       <c r="B40" t="n">
-        <v>74855</v>
+        <v>57481</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5107,34 +5079,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528898</v>
+        <v>528843</v>
       </c>
       <c r="R40" t="n">
-        <v>6998773</v>
+        <v>6998616</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5164,24 +5141,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På ved på gammal levande sälg i gammal granskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5196,22 +5163,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122819543</v>
+        <v>122821939</v>
       </c>
       <c r="B41" t="n">
-        <v>74849</v>
+        <v>78769</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5220,41 +5187,50 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>306</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528863</v>
+        <v>528796</v>
       </c>
       <c r="R41" t="n">
-        <v>6998680</v>
+        <v>6998791</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5283,7 +5259,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5293,12 +5269,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På ved på björkhögstubbe i gammal granskog</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5313,22 +5284,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122821953</v>
+        <v>122819608</v>
       </c>
       <c r="B42" t="n">
-        <v>57478</v>
+        <v>78769</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5341,42 +5312,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528813</v>
+        <v>528807</v>
       </c>
       <c r="R42" t="n">
-        <v>6998760</v>
+        <v>6998706</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5410,7 +5381,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>Relativt ymnigt på många granar. Fertila bålar finns här.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5421,6 +5392,31 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5437,10 +5433,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122819626</v>
+        <v>122820570</v>
       </c>
       <c r="B43" t="n">
-        <v>79847</v>
+        <v>57481</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5453,34 +5449,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528907</v>
+        <v>528842</v>
       </c>
       <c r="R43" t="n">
-        <v>6998684</v>
+        <v>6998786</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5517,7 +5518,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5544,10 +5545,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122819697</v>
+        <v>122821953</v>
       </c>
       <c r="B44" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5585,14 +5586,14 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528891</v>
+        <v>528813</v>
       </c>
       <c r="R44" t="n">
-        <v>6998754</v>
+        <v>6998760</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5622,24 +5623,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gammal levande tall</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5654,22 +5645,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122819182</v>
+        <v>122819677</v>
       </c>
       <c r="B45" t="n">
-        <v>90948</v>
+        <v>79851</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5682,21 +5673,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5706,10 +5697,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528836</v>
+        <v>528904</v>
       </c>
       <c r="R45" t="n">
-        <v>6998668</v>
+        <v>6998685</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5768,10 +5759,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122819825</v>
+        <v>122819919</v>
       </c>
       <c r="B46" t="n">
-        <v>74675</v>
+        <v>74857</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5780,38 +5771,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6428</v>
+        <v>492</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528895</v>
+        <v>528873</v>
       </c>
       <c r="R46" t="n">
-        <v>6998697</v>
+        <v>6998728</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5841,9 +5832,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På bark i hålighet vid basen av gammal björkhögstubbe</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5858,22 +5864,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122819081</v>
+        <v>122819055</v>
       </c>
       <c r="B47" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5915,10 +5921,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528837</v>
+        <v>528843</v>
       </c>
       <c r="R47" t="n">
-        <v>6998667</v>
+        <v>6998681</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5982,10 +5988,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122819987</v>
+        <v>122819726</v>
       </c>
       <c r="B48" t="n">
-        <v>79882</v>
+        <v>57592</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5998,34 +6004,43 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6463</v>
+        <v>103031</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528883</v>
+        <v>528900</v>
       </c>
       <c r="R48" t="n">
-        <v>6998770</v>
+        <v>6998697</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6055,24 +6070,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6087,22 +6087,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122822680</v>
+        <v>122822436</v>
       </c>
       <c r="B49" t="n">
-        <v>78503</v>
+        <v>78506</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6139,13 +6139,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528888</v>
+        <v>528840</v>
       </c>
       <c r="R49" t="n">
-        <v>6998655</v>
+        <v>6998787</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På kolad ved på tallhögstubbe</t>
+          <t>På kolad ved på tallstubbe</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6204,22 +6204,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122820024</v>
+        <v>122819915</v>
       </c>
       <c r="B50" t="n">
-        <v>57589</v>
+        <v>57481</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6228,20 +6228,20 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -6251,14 +6251,18 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -6272,10 +6276,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>528891</v>
+        <v>528893</v>
       </c>
       <c r="R50" t="n">
-        <v>6998690</v>
+        <v>6998687</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6312,7 +6316,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Tre lavskrikor i naturskog med höga naturvärden.</t>
+          <t>Födosökande hona och hane av tretåig hackspett i skog med höga till mycket höga livsmiljövärden.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6331,7 +6335,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Flerskiktad hänglavsrik barrnaturskog med höga naturvärden.</t>
+          <t>Flerskiktad barrnaturskog med höga naturvärden.</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6349,10 +6353,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122819960</v>
+        <v>122820024</v>
       </c>
       <c r="B51" t="n">
-        <v>57478</v>
+        <v>57592</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6361,20 +6365,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -6384,19 +6388,11 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -6413,10 +6409,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>528893</v>
+        <v>528891</v>
       </c>
       <c r="R51" t="n">
-        <v>6998687</v>
+        <v>6998690</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6453,7 +6449,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Rätt så skygg hane av tretåig hackspett i barrnaturskog med mycket höga livsmiljövärden för tretåig hackspett.</t>
+          <t>Tre lavskrikor i naturskog med höga naturvärden.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6472,7 +6468,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Kontinuitetsskog med höga naturvärden.</t>
+          <t>Flerskiktad hänglavsrik barrnaturskog med höga naturvärden.</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6615,7 +6611,7 @@
         <v>122820539</v>
       </c>
       <c r="B53" t="n">
-        <v>90952</v>
+        <v>90955</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6747,7 +6743,7 @@
         <v>122820461</v>
       </c>
       <c r="B54" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6889,7 +6885,7 @@
         <v>122819853</v>
       </c>
       <c r="B55" t="n">
-        <v>79044</v>
+        <v>79047</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>

--- a/artfynd/A 55408-2024 artfynd.xlsx
+++ b/artfynd/A 55408-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122819526</v>
+        <v>122822354</v>
       </c>
       <c r="B2" t="n">
-        <v>90955</v>
+        <v>91129</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>1588</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528875</v>
+        <v>528838</v>
       </c>
       <c r="R2" t="n">
-        <v>6998691</v>
+        <v>6998736</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,24 +748,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122819701</v>
+        <v>122819522</v>
       </c>
       <c r="B3" t="n">
-        <v>78769</v>
+        <v>57481</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,24 +793,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
@@ -835,10 +825,10 @@
         <v>528843</v>
       </c>
       <c r="R3" t="n">
-        <v>6998744</v>
+        <v>6998616</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt på många granar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,31 +873,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -924,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122822680</v>
+        <v>122822781</v>
       </c>
       <c r="B4" t="n">
-        <v>78506</v>
+        <v>79888</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6464</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -964,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528888</v>
+        <v>528877</v>
       </c>
       <c r="R4" t="n">
-        <v>6998655</v>
+        <v>6998634</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,12 +974,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På kolad ved på tallhögstubbe</t>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122820232</v>
+        <v>122822436</v>
       </c>
       <c r="B5" t="n">
-        <v>77712</v>
+        <v>78508</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,21 +1022,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>314</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1081,13 +1046,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528897</v>
+        <v>528840</v>
       </c>
       <c r="R5" t="n">
-        <v>6998766</v>
+        <v>6998787</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1116,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,12 +1091,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På kolad ved på tallstubbe</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,7 +1111,7 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1158,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122819543</v>
+        <v>122819677</v>
       </c>
       <c r="B6" t="n">
-        <v>74852</v>
+        <v>79853</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1170,41 +1135,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>306</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528863</v>
+        <v>528904</v>
       </c>
       <c r="R6" t="n">
-        <v>6998680</v>
+        <v>6998685</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1231,24 +1196,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På ved på björkhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,22 +1213,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122822761</v>
+        <v>122820558</v>
       </c>
       <c r="B7" t="n">
-        <v>79850</v>
+        <v>74866</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1291,21 +1241,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1315,13 +1265,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528879</v>
+        <v>528878</v>
       </c>
       <c r="R7" t="n">
-        <v>6998619</v>
+        <v>6998770</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1350,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1360,12 +1310,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På sälglåga</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1392,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122822120</v>
+        <v>122819213</v>
       </c>
       <c r="B8" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1428,14 +1378,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528832</v>
+        <v>528849</v>
       </c>
       <c r="R8" t="n">
-        <v>6998742</v>
+        <v>6998626</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1465,9 +1415,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,12 +1447,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1497,7 +1462,7 @@
         <v>122822818</v>
       </c>
       <c r="B9" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1631,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122820739</v>
+        <v>122820550</v>
       </c>
       <c r="B10" t="n">
-        <v>77702</v>
+        <v>57481</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1647,34 +1612,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528795</v>
+        <v>528843</v>
       </c>
       <c r="R10" t="n">
-        <v>6998791</v>
+        <v>6998785</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1704,24 +1674,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1736,22 +1696,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122819626</v>
+        <v>122820141</v>
       </c>
       <c r="B11" t="n">
-        <v>79850</v>
+        <v>90957</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1764,21 +1724,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1788,10 +1748,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528907</v>
+        <v>528888</v>
       </c>
       <c r="R11" t="n">
-        <v>6998684</v>
+        <v>6998720</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1824,11 +1784,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1855,10 +1810,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122820141</v>
+        <v>122819055</v>
       </c>
       <c r="B12" t="n">
-        <v>90955</v>
+        <v>57481</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1871,34 +1826,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528888</v>
+        <v>528843</v>
       </c>
       <c r="R12" t="n">
-        <v>6998720</v>
+        <v>6998681</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1931,6 +1891,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1957,10 +1922,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122819597</v>
+        <v>122823006</v>
       </c>
       <c r="B13" t="n">
-        <v>82556</v>
+        <v>79852</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1973,37 +1938,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528869</v>
+        <v>528861</v>
       </c>
       <c r="R13" t="n">
-        <v>6998649</v>
+        <v>6998604</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2030,26 +2000,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2058,26 +2013,51 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122822259</v>
+        <v>122819057</v>
       </c>
       <c r="B14" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2107,10 +2087,14 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2119,13 +2103,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528831</v>
+        <v>528830</v>
       </c>
       <c r="R14" t="n">
-        <v>6998741</v>
+        <v>6998611</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2154,7 +2138,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2164,12 +2148,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Rikligt på gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2184,22 +2168,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122819697</v>
+        <v>122822373</v>
       </c>
       <c r="B15" t="n">
-        <v>57481</v>
+        <v>90957</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2212,42 +2196,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528891</v>
+        <v>528856</v>
       </c>
       <c r="R15" t="n">
-        <v>6998754</v>
+        <v>6998762</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2276,7 +2255,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2286,12 +2265,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gammal levande tall</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2318,10 +2297,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122819010</v>
+        <v>122819870</v>
       </c>
       <c r="B16" t="n">
-        <v>57481</v>
+        <v>79852</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2334,42 +2313,46 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528818</v>
+        <v>528902</v>
       </c>
       <c r="R16" t="n">
-        <v>6998712</v>
+        <v>6998729</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2396,14 +2379,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På björklåga</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2418,22 +2411,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122822228</v>
+        <v>122822259</v>
       </c>
       <c r="B17" t="n">
-        <v>57634</v>
+        <v>78771</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2446,46 +2439,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528846</v>
+        <v>528831</v>
       </c>
       <c r="R17" t="n">
-        <v>6998743</v>
+        <v>6998741</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2512,9 +2501,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2529,22 +2533,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122820558</v>
+        <v>122819919</v>
       </c>
       <c r="B18" t="n">
-        <v>74866</v>
+        <v>74857</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2553,25 +2557,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>492</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2581,13 +2585,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528878</v>
+        <v>528873</v>
       </c>
       <c r="R18" t="n">
-        <v>6998770</v>
+        <v>6998728</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2616,7 +2620,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2626,12 +2630,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark i hålighet vid basen av gammal björkhögstubbe</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2646,22 +2650,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122820150</v>
+        <v>122822761</v>
       </c>
       <c r="B19" t="n">
-        <v>79025</v>
+        <v>79852</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2670,25 +2674,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6459</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2698,13 +2702,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528898</v>
+        <v>528879</v>
       </c>
       <c r="R19" t="n">
-        <v>6998770</v>
+        <v>6998619</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2733,7 +2737,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2743,12 +2747,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gammal sälg i gammal granskog</t>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2763,22 +2767,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122820115</v>
+        <v>122819597</v>
       </c>
       <c r="B20" t="n">
-        <v>74858</v>
+        <v>82558</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2791,21 +2795,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>308</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2815,10 +2819,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528898</v>
+        <v>528869</v>
       </c>
       <c r="R20" t="n">
-        <v>6998773</v>
+        <v>6998649</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2850,7 +2854,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2860,12 +2864,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På ved på gammal levande sälg i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2892,10 +2896,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122822373</v>
+        <v>122819626</v>
       </c>
       <c r="B21" t="n">
-        <v>90955</v>
+        <v>79852</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2908,37 +2912,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528856</v>
+        <v>528907</v>
       </c>
       <c r="R21" t="n">
-        <v>6998762</v>
+        <v>6998684</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2965,24 +2969,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På gammal granlåga i gammal granskog</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2997,22 +2991,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122820365</v>
+        <v>122822120</v>
       </c>
       <c r="B22" t="n">
-        <v>57481</v>
+        <v>79852</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3025,42 +3019,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528893</v>
+        <v>528832</v>
       </c>
       <c r="R22" t="n">
-        <v>6998757</v>
+        <v>6998742</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3087,24 +3076,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På gammal tall, äldre ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3119,22 +3093,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122822354</v>
+        <v>122819030</v>
       </c>
       <c r="B23" t="n">
-        <v>91127</v>
+        <v>57481</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3147,34 +3121,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1588</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528838</v>
+        <v>528811</v>
       </c>
       <c r="R23" t="n">
-        <v>6998736</v>
+        <v>6998709</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3207,6 +3186,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3233,10 +3217,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122823006</v>
+        <v>122819825</v>
       </c>
       <c r="B24" t="n">
-        <v>79850</v>
+        <v>74678</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3245,46 +3229,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6428</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528861</v>
+        <v>528895</v>
       </c>
       <c r="R24" t="n">
-        <v>6998604</v>
+        <v>6998697</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3324,31 +3303,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3365,10 +3319,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122819081</v>
+        <v>122820739</v>
       </c>
       <c r="B25" t="n">
-        <v>57481</v>
+        <v>77704</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3381,39 +3335,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528837</v>
+        <v>528795</v>
       </c>
       <c r="R25" t="n">
-        <v>6998667</v>
+        <v>6998791</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3443,14 +3392,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3465,22 +3424,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122820176</v>
+        <v>122819543</v>
       </c>
       <c r="B26" t="n">
-        <v>57634</v>
+        <v>74852</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3489,41 +3448,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528888</v>
+        <v>528863</v>
       </c>
       <c r="R26" t="n">
-        <v>6998720</v>
+        <v>6998680</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3550,9 +3509,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På ved på björkhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3567,22 +3541,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122819182</v>
+        <v>122822075</v>
       </c>
       <c r="B27" t="n">
-        <v>90951</v>
+        <v>74678</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3591,25 +3565,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>6428</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3619,10 +3593,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528836</v>
+        <v>528829</v>
       </c>
       <c r="R27" t="n">
-        <v>6998668</v>
+        <v>6998747</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3681,10 +3655,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122819825</v>
+        <v>122821939</v>
       </c>
       <c r="B28" t="n">
-        <v>74678</v>
+        <v>78771</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3693,41 +3667,50 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528895</v>
+        <v>528796</v>
       </c>
       <c r="R28" t="n">
-        <v>6998697</v>
+        <v>6998791</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3754,9 +3737,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3771,22 +3764,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122819987</v>
+        <v>122819726</v>
       </c>
       <c r="B29" t="n">
-        <v>79885</v>
+        <v>57592</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3799,34 +3792,43 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6463</v>
+        <v>103031</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528883</v>
+        <v>528900</v>
       </c>
       <c r="R29" t="n">
-        <v>6998770</v>
+        <v>6998697</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3856,24 +3858,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3888,22 +3875,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122819030</v>
+        <v>122822197</v>
       </c>
       <c r="B30" t="n">
-        <v>57481</v>
+        <v>95916</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3916,39 +3903,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528811</v>
+        <v>528847</v>
       </c>
       <c r="R30" t="n">
-        <v>6998709</v>
+        <v>6998739</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3981,11 +3963,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4012,10 +3989,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122819870</v>
+        <v>122819526</v>
       </c>
       <c r="B31" t="n">
-        <v>79850</v>
+        <v>90957</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4028,46 +4005,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528902</v>
+        <v>528875</v>
       </c>
       <c r="R31" t="n">
-        <v>6998729</v>
+        <v>6998691</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4096,7 +4064,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4106,12 +4074,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På björklåga</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4138,10 +4106,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122820550</v>
+        <v>122820232</v>
       </c>
       <c r="B32" t="n">
-        <v>57481</v>
+        <v>77714</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4154,39 +4122,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528843</v>
+        <v>528897</v>
       </c>
       <c r="R32" t="n">
-        <v>6998785</v>
+        <v>6998766</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4216,14 +4179,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4238,22 +4211,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122822197</v>
+        <v>122820150</v>
       </c>
       <c r="B33" t="n">
-        <v>95914</v>
+        <v>79027</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4262,41 +4235,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>6459</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528847</v>
+        <v>528898</v>
       </c>
       <c r="R33" t="n">
-        <v>6998739</v>
+        <v>6998770</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4323,9 +4296,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4340,22 +4328,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122819213</v>
+        <v>122819987</v>
       </c>
       <c r="B34" t="n">
-        <v>79850</v>
+        <v>79887</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4364,25 +4352,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4392,10 +4380,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528849</v>
+        <v>528883</v>
       </c>
       <c r="R34" t="n">
-        <v>6998626</v>
+        <v>6998770</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4427,7 +4415,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4437,12 +4425,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4469,10 +4457,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122822075</v>
+        <v>122822680</v>
       </c>
       <c r="B35" t="n">
-        <v>74678</v>
+        <v>78508</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4481,38 +4469,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6428</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528829</v>
+        <v>528888</v>
       </c>
       <c r="R35" t="n">
-        <v>6998747</v>
+        <v>6998655</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4542,9 +4530,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På kolad ved på tallhögstubbe</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4559,19 +4562,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122822290</v>
+        <v>122820365</v>
       </c>
       <c r="B36" t="n">
         <v>57481</v>
@@ -4612,17 +4615,17 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528824</v>
+        <v>528893</v>
       </c>
       <c r="R36" t="n">
-        <v>6998724</v>
+        <v>6998757</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4649,14 +4652,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en hackspettsbearbetad död gran.</t>
+          <t>På gammal tall, äldre ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4667,51 +4680,26 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122822781</v>
+        <v>122820570</v>
       </c>
       <c r="B37" t="n">
-        <v>79886</v>
+        <v>57481</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4720,38 +4708,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528877</v>
+        <v>528842</v>
       </c>
       <c r="R37" t="n">
-        <v>6998634</v>
+        <v>6998786</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4781,24 +4774,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4813,22 +4796,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122819057</v>
+        <v>122819010</v>
       </c>
       <c r="B38" t="n">
-        <v>78769</v>
+        <v>57481</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4841,46 +4824,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528830</v>
+        <v>528818</v>
       </c>
       <c r="R38" t="n">
-        <v>6998611</v>
+        <v>6998712</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4907,24 +4886,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>10:51</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>10:51</t>
-        </is>
-      </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Rikligt på gamla granar i gammal granskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4939,22 +4908,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122819041</v>
+        <v>122819182</v>
       </c>
       <c r="B39" t="n">
-        <v>57481</v>
+        <v>90953</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4967,39 +4936,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528830</v>
+        <v>528836</v>
       </c>
       <c r="R39" t="n">
-        <v>6998687</v>
+        <v>6998668</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5032,11 +4996,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5063,10 +5022,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122819522</v>
+        <v>122820115</v>
       </c>
       <c r="B40" t="n">
-        <v>57481</v>
+        <v>74858</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5079,39 +5038,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528843</v>
+        <v>528898</v>
       </c>
       <c r="R40" t="n">
-        <v>6998616</v>
+        <v>6998773</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5141,14 +5095,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På ved på gammal levande sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5163,22 +5127,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122821939</v>
+        <v>122819701</v>
       </c>
       <c r="B41" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5208,29 +5172,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528796</v>
+        <v>528843</v>
       </c>
       <c r="R41" t="n">
-        <v>6998791</v>
+        <v>6998744</v>
       </c>
       <c r="S41" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5257,19 +5212,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>12:42</t>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Rikligt på många granar.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5280,26 +5230,51 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122819608</v>
+        <v>122820176</v>
       </c>
       <c r="B42" t="n">
-        <v>78769</v>
+        <v>57634</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5312,42 +5287,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528807</v>
+        <v>528888</v>
       </c>
       <c r="R42" t="n">
-        <v>6998706</v>
+        <v>6998720</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5379,11 +5349,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Relativt ymnigt på många granar. Fertila bålar finns här.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5392,31 +5357,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5433,7 +5373,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122820570</v>
+        <v>122819697</v>
       </c>
       <c r="B43" t="n">
         <v>57481</v>
@@ -5469,19 +5409,19 @@
       <c r="I43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528842</v>
+        <v>528891</v>
       </c>
       <c r="R43" t="n">
-        <v>6998786</v>
+        <v>6998754</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5511,14 +5451,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre ringhack på gammal levande tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5533,19 +5483,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122821953</v>
+        <v>122822290</v>
       </c>
       <c r="B44" t="n">
         <v>57481</v>
@@ -5586,14 +5536,14 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528813</v>
+        <v>528824</v>
       </c>
       <c r="R44" t="n">
-        <v>6998760</v>
+        <v>6998724</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5630,7 +5580,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>Äldre ringhack på en hackspettsbearbetad död gran.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5641,6 +5591,31 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5657,10 +5632,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122819677</v>
+        <v>122819081</v>
       </c>
       <c r="B45" t="n">
-        <v>79851</v>
+        <v>57481</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5673,34 +5648,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528904</v>
+        <v>528837</v>
       </c>
       <c r="R45" t="n">
-        <v>6998685</v>
+        <v>6998667</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5733,6 +5713,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5759,10 +5744,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122819919</v>
+        <v>122819041</v>
       </c>
       <c r="B46" t="n">
-        <v>74857</v>
+        <v>57481</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5771,38 +5756,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528873</v>
+        <v>528830</v>
       </c>
       <c r="R46" t="n">
-        <v>6998728</v>
+        <v>6998687</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5832,24 +5822,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På bark i hålighet vid basen av gammal björkhögstubbe</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5864,19 +5844,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122819055</v>
+        <v>122821953</v>
       </c>
       <c r="B47" t="n">
         <v>57481</v>
@@ -5917,14 +5897,14 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528843</v>
+        <v>528813</v>
       </c>
       <c r="R47" t="n">
-        <v>6998681</v>
+        <v>6998760</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5961,7 +5941,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5988,10 +5968,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122819726</v>
+        <v>122822228</v>
       </c>
       <c r="B48" t="n">
-        <v>57592</v>
+        <v>57634</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6000,25 +5980,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -6037,10 +6017,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528900</v>
+        <v>528846</v>
       </c>
       <c r="R48" t="n">
-        <v>6998697</v>
+        <v>6998743</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6099,10 +6079,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122822436</v>
+        <v>122819608</v>
       </c>
       <c r="B49" t="n">
-        <v>78506</v>
+        <v>78771</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6115,37 +6095,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528840</v>
+        <v>528807</v>
       </c>
       <c r="R49" t="n">
-        <v>6998787</v>
+        <v>6998706</v>
       </c>
       <c r="S49" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6172,24 +6157,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På kolad ved på tallstubbe</t>
+          <t>Relativt ymnigt på många granar. Fertila bålar finns här.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6200,26 +6175,51 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122819915</v>
+        <v>122822850</v>
       </c>
       <c r="B50" t="n">
-        <v>57481</v>
+        <v>5489</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6232,54 +6232,43 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>101410</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>528893</v>
+        <v>528902</v>
       </c>
       <c r="R50" t="n">
-        <v>6998687</v>
+        <v>6998601</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6314,17 +6303,13 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Födosökande hona och hane av tretåig hackspett i skog med höga till mycket höga livsmiljövärden.</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6335,7 +6320,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Flerskiktad barrnaturskog med höga naturvärden.</t>
+          <t>Gammal flerskiktad naturskogsartad kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6353,10 +6338,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122820024</v>
+        <v>122819960</v>
       </c>
       <c r="B51" t="n">
-        <v>57592</v>
+        <v>57481</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6365,20 +6350,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -6388,11 +6373,19 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -6409,10 +6402,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>528891</v>
+        <v>528893</v>
       </c>
       <c r="R51" t="n">
-        <v>6998690</v>
+        <v>6998687</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6449,7 +6442,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Tre lavskrikor i naturskog med höga naturvärden.</t>
+          <t>Rätt så skygg hane av tretåig hackspett i barrnaturskog med mycket höga livsmiljövärden för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6468,7 +6461,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Flerskiktad hänglavsrik barrnaturskog med höga naturvärden.</t>
+          <t>Kontinuitetsskog med höga naturvärden.</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6486,10 +6479,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122822850</v>
+        <v>122820024</v>
       </c>
       <c r="B52" t="n">
-        <v>5489</v>
+        <v>57592</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6498,47 +6491,54 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>101410</v>
+        <v>103031</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>528902</v>
+        <v>528891</v>
       </c>
       <c r="R52" t="n">
-        <v>6998601</v>
+        <v>6998690</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6573,13 +6573,17 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Tre lavskrikor i naturskog med höga naturvärden.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6590,7 +6594,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Gammal flerskiktad naturskogsartad kontinuitetsskog.</t>
+          <t>Flerskiktad hänglavsrik barrnaturskog med höga naturvärden.</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6608,10 +6612,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122820539</v>
+        <v>122820461</v>
       </c>
       <c r="B53" t="n">
-        <v>90955</v>
+        <v>57481</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6624,42 +6628,47 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>528851</v>
+        <v>528854</v>
       </c>
       <c r="R53" t="n">
-        <v>6998721</v>
+        <v>6998728</v>
       </c>
       <c r="S53" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6691,6 +6700,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Färska ringhack längs ca 3 m på en granstam i barrnaturskog med revir för tretåig hackspett i höga livsmiljövärden.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6717,12 +6731,12 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6740,10 +6754,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122820461</v>
+        <v>122820539</v>
       </c>
       <c r="B54" t="n">
-        <v>57481</v>
+        <v>90957</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6756,47 +6770,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>528854</v>
+        <v>528851</v>
       </c>
       <c r="R54" t="n">
-        <v>6998728</v>
+        <v>6998721</v>
       </c>
       <c r="S54" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6828,11 +6837,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Färska ringhack längs ca 3 m på en granstam i barrnaturskog med revir för tretåig hackspett i höga livsmiljövärden.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6859,12 +6863,12 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6885,7 +6889,7 @@
         <v>122819853</v>
       </c>
       <c r="B55" t="n">
-        <v>79047</v>
+        <v>79049</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>

--- a/artfynd/A 55408-2024 artfynd.xlsx
+++ b/artfynd/A 55408-2024 artfynd.xlsx
@@ -5139,10 +5139,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122819701</v>
+        <v>122820176</v>
       </c>
       <c r="B41" t="n">
-        <v>78771</v>
+        <v>57634</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5155,37 +5155,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528843</v>
+        <v>528888</v>
       </c>
       <c r="R41" t="n">
-        <v>6998744</v>
+        <v>6998720</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5217,11 +5217,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Rikligt på många granar.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5230,31 +5225,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5271,10 +5241,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122820176</v>
+        <v>122819697</v>
       </c>
       <c r="B42" t="n">
-        <v>57634</v>
+        <v>57481</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5287,34 +5257,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528888</v>
+        <v>528891</v>
       </c>
       <c r="R42" t="n">
-        <v>6998720</v>
+        <v>6998754</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5344,9 +5319,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gammal levande tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5361,19 +5351,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122819697</v>
+        <v>122822290</v>
       </c>
       <c r="B43" t="n">
         <v>57481</v>
@@ -5414,14 +5404,14 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528891</v>
+        <v>528824</v>
       </c>
       <c r="R43" t="n">
-        <v>6998754</v>
+        <v>6998724</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5451,24 +5441,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gammal levande tall</t>
+          <t>Äldre ringhack på en hackspettsbearbetad död gran.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5479,23 +5459,48 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122822290</v>
+        <v>122819081</v>
       </c>
       <c r="B44" t="n">
         <v>57481</v>
@@ -5540,10 +5545,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528824</v>
+        <v>528837</v>
       </c>
       <c r="R44" t="n">
-        <v>6998724</v>
+        <v>6998667</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5580,7 +5585,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en hackspettsbearbetad död gran.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5591,31 +5596,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5632,10 +5612,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122819081</v>
+        <v>122819701</v>
       </c>
       <c r="B45" t="n">
-        <v>57481</v>
+        <v>78771</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5648,42 +5628,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528837</v>
+        <v>528843</v>
       </c>
       <c r="R45" t="n">
-        <v>6998667</v>
+        <v>6998744</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5717,7 +5692,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt på många granar.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5728,6 +5703,31 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">

--- a/artfynd/A 55408-2024 artfynd.xlsx
+++ b/artfynd/A 55408-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122822354</v>
+        <v>122820176</v>
       </c>
       <c r="B2" t="n">
-        <v>91129</v>
+        <v>57634</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1588</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528838</v>
+        <v>528888</v>
       </c>
       <c r="R2" t="n">
-        <v>6998736</v>
+        <v>6998720</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122819522</v>
+        <v>122822120</v>
       </c>
       <c r="B3" t="n">
-        <v>57481</v>
+        <v>79853</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528843</v>
+        <v>528832</v>
       </c>
       <c r="R3" t="n">
-        <v>6998616</v>
+        <v>6998742</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122822781</v>
+        <v>122819825</v>
       </c>
       <c r="B4" t="n">
-        <v>79888</v>
+        <v>74678</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,34 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6464</v>
+        <v>6428</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528877</v>
+        <v>528895</v>
       </c>
       <c r="R4" t="n">
-        <v>6998634</v>
+        <v>6998697</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,24 +952,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,22 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122822436</v>
+        <v>122819697</v>
       </c>
       <c r="B5" t="n">
-        <v>78508</v>
+        <v>57481</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,37 +997,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528840</v>
+        <v>528891</v>
       </c>
       <c r="R5" t="n">
-        <v>6998787</v>
+        <v>6998754</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,7 +1061,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,12 +1071,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På kolad ved på tallstubbe</t>
+          <t>Äldre ringhack på gammal levande tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,22 +1091,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122819677</v>
+        <v>122820232</v>
       </c>
       <c r="B6" t="n">
-        <v>79853</v>
+        <v>77715</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,34 +1119,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528904</v>
+        <v>528897</v>
       </c>
       <c r="R6" t="n">
-        <v>6998685</v>
+        <v>6998766</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,9 +1176,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1213,22 +1208,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122820558</v>
+        <v>122822228</v>
       </c>
       <c r="B7" t="n">
-        <v>74866</v>
+        <v>57634</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,37 +1236,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528878</v>
+        <v>528846</v>
       </c>
       <c r="R7" t="n">
-        <v>6998770</v>
+        <v>6998743</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1298,24 +1302,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1330,22 +1319,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122819213</v>
+        <v>122822373</v>
       </c>
       <c r="B8" t="n">
-        <v>79852</v>
+        <v>90963</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1358,21 +1347,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,13 +1371,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528849</v>
+        <v>528856</v>
       </c>
       <c r="R8" t="n">
-        <v>6998626</v>
+        <v>6998762</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1417,7 +1406,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1427,12 +1416,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,22 +1436,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122822818</v>
+        <v>122819081</v>
       </c>
       <c r="B9" t="n">
-        <v>79852</v>
+        <v>57481</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,27 +1464,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1504,10 +1493,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528919</v>
+        <v>528837</v>
       </c>
       <c r="R9" t="n">
-        <v>6998644</v>
+        <v>6998667</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1544,7 +1533,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På två gamla grovbarkade sälgar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1555,31 +1544,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1596,10 +1560,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122820550</v>
+        <v>122822259</v>
       </c>
       <c r="B10" t="n">
-        <v>57481</v>
+        <v>78772</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1612,42 +1576,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528843</v>
+        <v>528831</v>
       </c>
       <c r="R10" t="n">
-        <v>6998785</v>
+        <v>6998741</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1674,14 +1638,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,22 +1670,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122820141</v>
+        <v>122819677</v>
       </c>
       <c r="B11" t="n">
-        <v>90957</v>
+        <v>79854</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1724,21 +1698,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1748,10 +1722,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528888</v>
+        <v>528904</v>
       </c>
       <c r="R11" t="n">
-        <v>6998720</v>
+        <v>6998685</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1810,7 +1784,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122819055</v>
+        <v>122820365</v>
       </c>
       <c r="B12" t="n">
         <v>57481</v>
@@ -1851,17 +1825,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528843</v>
+        <v>528893</v>
       </c>
       <c r="R12" t="n">
-        <v>6998681</v>
+        <v>6998757</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1888,14 +1862,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gammal tall, äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1910,22 +1894,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122823006</v>
+        <v>122819030</v>
       </c>
       <c r="B13" t="n">
-        <v>79852</v>
+        <v>57481</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1938,27 +1922,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1967,13 +1951,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528861</v>
+        <v>528811</v>
       </c>
       <c r="R13" t="n">
-        <v>6998604</v>
+        <v>6998709</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2005,6 +1989,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2013,31 +2002,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2054,10 +2018,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122819057</v>
+        <v>122819626</v>
       </c>
       <c r="B14" t="n">
-        <v>78771</v>
+        <v>79853</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2070,46 +2034,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528830</v>
+        <v>528907</v>
       </c>
       <c r="R14" t="n">
-        <v>6998611</v>
+        <v>6998684</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2136,24 +2091,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:51</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:51</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rikligt på gamla granar i gammal granskog</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2168,22 +2113,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122822373</v>
+        <v>122822075</v>
       </c>
       <c r="B15" t="n">
-        <v>90957</v>
+        <v>74678</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2192,41 +2137,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6428</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528856</v>
+        <v>528829</v>
       </c>
       <c r="R15" t="n">
-        <v>6998762</v>
+        <v>6998747</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2253,24 +2198,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På gammal granlåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2285,22 +2215,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122819870</v>
+        <v>122822818</v>
       </c>
       <c r="B16" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2330,29 +2260,25 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528902</v>
+        <v>528919</v>
       </c>
       <c r="R16" t="n">
-        <v>6998729</v>
+        <v>6998644</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2379,24 +2305,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:29</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:29</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På björklåga</t>
+          <t>På två gamla grovbarkade sälgar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2407,26 +2323,51 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122822259</v>
+        <v>122820570</v>
       </c>
       <c r="B17" t="n">
-        <v>78771</v>
+        <v>57481</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2439,42 +2380,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528831</v>
+        <v>528842</v>
       </c>
       <c r="R17" t="n">
-        <v>6998741</v>
+        <v>6998786</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2501,24 +2442,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2533,22 +2464,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122819919</v>
+        <v>122820141</v>
       </c>
       <c r="B18" t="n">
-        <v>74857</v>
+        <v>90963</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2557,38 +2488,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>492</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528873</v>
+        <v>528888</v>
       </c>
       <c r="R18" t="n">
-        <v>6998728</v>
+        <v>6998720</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2618,24 +2549,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På bark i hålighet vid basen av gammal björkhögstubbe</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2650,22 +2566,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122822761</v>
+        <v>122822436</v>
       </c>
       <c r="B19" t="n">
-        <v>79852</v>
+        <v>78509</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2678,21 +2594,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2702,13 +2618,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528879</v>
+        <v>528840</v>
       </c>
       <c r="R19" t="n">
-        <v>6998619</v>
+        <v>6998787</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2737,7 +2653,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2747,12 +2663,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På sälglåga</t>
+          <t>På kolad ved på tallstubbe</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2779,10 +2695,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122819597</v>
+        <v>122819701</v>
       </c>
       <c r="B20" t="n">
-        <v>82558</v>
+        <v>78772</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2795,37 +2711,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528869</v>
+        <v>528843</v>
       </c>
       <c r="R20" t="n">
-        <v>6998649</v>
+        <v>6998744</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2852,24 +2768,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>Rikligt på många granar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2880,26 +2786,51 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122819626</v>
+        <v>122820558</v>
       </c>
       <c r="B21" t="n">
-        <v>79852</v>
+        <v>74866</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2912,37 +2843,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528907</v>
+        <v>528878</v>
       </c>
       <c r="R21" t="n">
-        <v>6998684</v>
+        <v>6998770</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2969,14 +2900,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2991,22 +2932,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122822120</v>
+        <v>122822781</v>
       </c>
       <c r="B22" t="n">
-        <v>79852</v>
+        <v>79889</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3015,38 +2956,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528832</v>
+        <v>528877</v>
       </c>
       <c r="R22" t="n">
-        <v>6998742</v>
+        <v>6998634</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3076,9 +3017,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3093,19 +3049,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122819030</v>
+        <v>122819522</v>
       </c>
       <c r="B23" t="n">
         <v>57481</v>
@@ -3150,10 +3106,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528811</v>
+        <v>528843</v>
       </c>
       <c r="R23" t="n">
-        <v>6998709</v>
+        <v>6998616</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3217,10 +3173,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122819825</v>
+        <v>122819057</v>
       </c>
       <c r="B24" t="n">
-        <v>74678</v>
+        <v>78772</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3229,41 +3185,50 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528895</v>
+        <v>528830</v>
       </c>
       <c r="R24" t="n">
-        <v>6998697</v>
+        <v>6998611</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3290,9 +3255,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt på gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3307,22 +3287,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122820739</v>
+        <v>122819182</v>
       </c>
       <c r="B25" t="n">
-        <v>77704</v>
+        <v>90959</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3335,34 +3315,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228579</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528795</v>
+        <v>528836</v>
       </c>
       <c r="R25" t="n">
-        <v>6998791</v>
+        <v>6998668</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3392,24 +3372,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3424,22 +3389,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122819543</v>
+        <v>122819919</v>
       </c>
       <c r="B26" t="n">
-        <v>74852</v>
+        <v>74857</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3448,25 +3413,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>306</v>
+        <v>492</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3476,13 +3441,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528863</v>
+        <v>528873</v>
       </c>
       <c r="R26" t="n">
-        <v>6998680</v>
+        <v>6998728</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3511,7 +3476,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3521,12 +3486,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På ved på björkhögstubbe i gammal granskog</t>
+          <t>På bark i hålighet vid basen av gammal björkhögstubbe</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3553,10 +3518,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122822075</v>
+        <v>122819041</v>
       </c>
       <c r="B27" t="n">
-        <v>74678</v>
+        <v>57481</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3565,38 +3530,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6428</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528829</v>
+        <v>528830</v>
       </c>
       <c r="R27" t="n">
-        <v>6998747</v>
+        <v>6998687</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3629,6 +3599,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3655,10 +3630,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122821939</v>
+        <v>122819010</v>
       </c>
       <c r="B28" t="n">
-        <v>78771</v>
+        <v>57481</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3671,46 +3646,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528796</v>
+        <v>528818</v>
       </c>
       <c r="R28" t="n">
-        <v>6998791</v>
+        <v>6998712</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3737,19 +3708,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>12:42</t>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3764,22 +3730,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122819726</v>
+        <v>122821939</v>
       </c>
       <c r="B29" t="n">
-        <v>57592</v>
+        <v>78772</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3788,50 +3754,50 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528900</v>
+        <v>528796</v>
       </c>
       <c r="R29" t="n">
-        <v>6998697</v>
+        <v>6998791</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3858,9 +3824,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3875,22 +3851,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122822197</v>
+        <v>122822680</v>
       </c>
       <c r="B30" t="n">
-        <v>95916</v>
+        <v>78509</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3903,34 +3879,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528847</v>
+        <v>528888</v>
       </c>
       <c r="R30" t="n">
-        <v>6998739</v>
+        <v>6998655</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3960,9 +3936,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På kolad ved på tallhögstubbe</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3977,22 +3968,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122819526</v>
+        <v>122823006</v>
       </c>
       <c r="B31" t="n">
-        <v>90957</v>
+        <v>79853</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4005,37 +3996,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528875</v>
+        <v>528861</v>
       </c>
       <c r="R31" t="n">
-        <v>6998691</v>
+        <v>6998604</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4062,26 +4058,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4090,26 +4071,51 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122820232</v>
+        <v>122819526</v>
       </c>
       <c r="B32" t="n">
-        <v>77714</v>
+        <v>90963</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4122,21 +4128,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>314</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4146,10 +4152,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528897</v>
+        <v>528875</v>
       </c>
       <c r="R32" t="n">
-        <v>6998766</v>
+        <v>6998691</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4181,7 +4187,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4191,12 +4197,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4211,22 +4217,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122820150</v>
+        <v>122819726</v>
       </c>
       <c r="B33" t="n">
-        <v>79027</v>
+        <v>57592</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4239,37 +4245,46 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6459</v>
+        <v>103031</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528898</v>
+        <v>528900</v>
       </c>
       <c r="R33" t="n">
-        <v>6998770</v>
+        <v>6998697</v>
       </c>
       <c r="S33" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4296,24 +4311,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4328,22 +4328,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122819987</v>
+        <v>122822197</v>
       </c>
       <c r="B34" t="n">
-        <v>79887</v>
+        <v>95922</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4352,38 +4352,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6463</v>
+        <v>53</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528883</v>
+        <v>528847</v>
       </c>
       <c r="R34" t="n">
-        <v>6998770</v>
+        <v>6998739</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4413,24 +4413,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4445,22 +4430,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122822680</v>
+        <v>122819543</v>
       </c>
       <c r="B35" t="n">
-        <v>78508</v>
+        <v>74852</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4469,25 +4454,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4497,13 +4482,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528888</v>
+        <v>528863</v>
       </c>
       <c r="R35" t="n">
-        <v>6998655</v>
+        <v>6998680</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4532,7 +4517,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4542,12 +4527,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På kolad ved på tallhögstubbe</t>
+          <t>På ved på björkhögstubbe i gammal granskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4574,10 +4559,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122820365</v>
+        <v>122820115</v>
       </c>
       <c r="B36" t="n">
-        <v>57481</v>
+        <v>74858</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4590,42 +4575,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528893</v>
+        <v>528898</v>
       </c>
       <c r="R36" t="n">
-        <v>6998757</v>
+        <v>6998773</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4654,7 +4634,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4664,12 +4644,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På gammal tall, äldre ringhack</t>
+          <t>På ved på gammal levande sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4696,7 +4676,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122820570</v>
+        <v>122820550</v>
       </c>
       <c r="B37" t="n">
         <v>57481</v>
@@ -4741,10 +4721,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528842</v>
+        <v>528843</v>
       </c>
       <c r="R37" t="n">
-        <v>6998786</v>
+        <v>6998785</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4808,7 +4788,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122819010</v>
+        <v>122822290</v>
       </c>
       <c r="B38" t="n">
         <v>57481</v>
@@ -4853,10 +4833,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528818</v>
+        <v>528824</v>
       </c>
       <c r="R38" t="n">
-        <v>6998712</v>
+        <v>6998724</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4893,7 +4873,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre ringhack på en hackspettsbearbetad död gran.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4904,6 +4884,31 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4920,10 +4925,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122819182</v>
+        <v>122819870</v>
       </c>
       <c r="B39" t="n">
-        <v>90953</v>
+        <v>79853</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4936,37 +4941,46 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528836</v>
+        <v>528902</v>
       </c>
       <c r="R39" t="n">
-        <v>6998668</v>
+        <v>6998729</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4993,9 +5007,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På björklåga</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5010,22 +5039,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122820115</v>
+        <v>122819608</v>
       </c>
       <c r="B40" t="n">
-        <v>74858</v>
+        <v>78772</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5038,37 +5067,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528898</v>
+        <v>528807</v>
       </c>
       <c r="R40" t="n">
-        <v>6998773</v>
+        <v>6998706</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5095,24 +5129,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På ved på gammal levande sälg i gammal granskog</t>
+          <t>Relativt ymnigt på många granar. Fertila bålar finns här.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5123,26 +5147,51 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122820176</v>
+        <v>122819987</v>
       </c>
       <c r="B41" t="n">
-        <v>57634</v>
+        <v>79888</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5151,38 +5200,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>6463</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528888</v>
+        <v>528883</v>
       </c>
       <c r="R41" t="n">
-        <v>6998720</v>
+        <v>6998770</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5212,9 +5261,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5229,22 +5293,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122819697</v>
+        <v>122820150</v>
       </c>
       <c r="B42" t="n">
-        <v>57481</v>
+        <v>79028</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5253,46 +5317,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6459</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528891</v>
+        <v>528898</v>
       </c>
       <c r="R42" t="n">
-        <v>6998754</v>
+        <v>6998770</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5321,7 +5380,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5331,12 +5390,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gammal levande tall</t>
+          <t>På gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5363,10 +5422,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122822290</v>
+        <v>122819597</v>
       </c>
       <c r="B43" t="n">
-        <v>57481</v>
+        <v>82559</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5379,39 +5438,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528824</v>
+        <v>528869</v>
       </c>
       <c r="R43" t="n">
-        <v>6998724</v>
+        <v>6998649</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5441,14 +5495,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en hackspettsbearbetad död gran.</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5459,51 +5523,26 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122819081</v>
+        <v>122822761</v>
       </c>
       <c r="B44" t="n">
-        <v>57481</v>
+        <v>79853</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5516,39 +5555,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528837</v>
+        <v>528879</v>
       </c>
       <c r="R44" t="n">
-        <v>6998667</v>
+        <v>6998619</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5578,14 +5612,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På sälglåga</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5600,22 +5644,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122819701</v>
+        <v>122819213</v>
       </c>
       <c r="B45" t="n">
-        <v>78771</v>
+        <v>79853</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5628,37 +5672,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528843</v>
+        <v>528849</v>
       </c>
       <c r="R45" t="n">
-        <v>6998744</v>
+        <v>6998626</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5685,14 +5729,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Rikligt på många granar.</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5703,51 +5757,26 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122819041</v>
+        <v>122820739</v>
       </c>
       <c r="B46" t="n">
-        <v>57481</v>
+        <v>77705</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5760,39 +5789,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528830</v>
+        <v>528795</v>
       </c>
       <c r="R46" t="n">
-        <v>6998687</v>
+        <v>6998791</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5822,14 +5846,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5844,22 +5878,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122821953</v>
+        <v>122822354</v>
       </c>
       <c r="B47" t="n">
-        <v>57481</v>
+        <v>91135</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5872,39 +5906,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>1588</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528813</v>
+        <v>528838</v>
       </c>
       <c r="R47" t="n">
-        <v>6998760</v>
+        <v>6998736</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5937,11 +5966,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5968,10 +5992,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122822228</v>
+        <v>122819055</v>
       </c>
       <c r="B48" t="n">
-        <v>57634</v>
+        <v>57481</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5984,43 +6008,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528846</v>
+        <v>528843</v>
       </c>
       <c r="R48" t="n">
-        <v>6998743</v>
+        <v>6998681</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6053,6 +6073,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6079,10 +6104,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122819608</v>
+        <v>122821953</v>
       </c>
       <c r="B49" t="n">
-        <v>78771</v>
+        <v>57481</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6095,42 +6120,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528807</v>
+        <v>528813</v>
       </c>
       <c r="R49" t="n">
-        <v>6998706</v>
+        <v>6998760</v>
       </c>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6164,7 +6189,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Relativt ymnigt på många granar. Fertila bålar finns här.</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6175,31 +6200,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6612,10 +6612,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122820461</v>
+        <v>122820539</v>
       </c>
       <c r="B53" t="n">
-        <v>57481</v>
+        <v>90963</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6628,47 +6628,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>528854</v>
+        <v>528851</v>
       </c>
       <c r="R53" t="n">
-        <v>6998728</v>
+        <v>6998721</v>
       </c>
       <c r="S53" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6700,11 +6695,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Färska ringhack längs ca 3 m på en granstam i barrnaturskog med revir för tretåig hackspett i höga livsmiljövärden.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6731,12 +6721,12 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6754,10 +6744,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122820539</v>
+        <v>122820461</v>
       </c>
       <c r="B54" t="n">
-        <v>90957</v>
+        <v>57481</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6770,42 +6760,47 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Södra Öratjärnknösen, Södra Öratjärnknösen, Jmt</t>
+          <t>Stugubäckmyran, Stugun, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>528851</v>
+        <v>528854</v>
       </c>
       <c r="R54" t="n">
-        <v>6998721</v>
+        <v>6998728</v>
       </c>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6837,6 +6832,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Färska ringhack längs ca 3 m på en granstam i barrnaturskog med revir för tretåig hackspett i höga livsmiljövärden.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6863,12 +6863,12 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6889,7 +6889,7 @@
         <v>122819853</v>
       </c>
       <c r="B55" t="n">
-        <v>79049</v>
+        <v>79050</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>

--- a/artfynd/A 55408-2024 artfynd.xlsx
+++ b/artfynd/A 55408-2024 artfynd.xlsx
@@ -6352,11 +6352,11 @@
         <v>122819915</v>
       </c>
       <c r="B51" t="n">
-        <v>57481</v>
+        <v>57491</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">

--- a/artfynd/A 55408-2024 artfynd.xlsx
+++ b/artfynd/A 55408-2024 artfynd.xlsx
@@ -6352,12 +6352,7 @@
         <v>122819915</v>
       </c>
       <c r="B51" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57864</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
